--- a/apps/web/.qa/テスト仕様書_クライアント版.xlsx
+++ b/apps/web/.qa/テスト仕様書_クライアント版.xlsx
@@ -65,7 +65,7 @@
       <sz val="13"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -75,6 +75,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="007A5C9E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
       </patternFill>
     </fill>
   </fills>
@@ -104,7 +109,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -113,6 +118,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -538,7 +546,7 @@
         <v>16</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -551,7 +559,7 @@
         <v>17</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -564,7 +572,7 @@
         <v>12</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -577,7 +585,7 @@
         <v>11</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -590,7 +598,7 @@
         <v>11</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -603,7 +611,7 @@
         <v>16</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -616,7 +624,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -629,7 +637,7 @@
         <v>13</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -642,7 +650,7 @@
         <v>22</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
@@ -655,7 +663,7 @@
         <v>15</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -668,7 +676,7 @@
         <v>13</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -681,7 +689,7 @@
         <v>20</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -694,7 +702,7 @@
         <v>11</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -707,7 +715,7 @@
         <v>14</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
@@ -720,7 +728,7 @@
         <v>10</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -733,7 +741,7 @@
         <v>15</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -746,7 +754,7 @@
         <v>17</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -759,7 +767,7 @@
         <v>14</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23">
@@ -772,7 +780,7 @@
         <v>11</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -785,7 +793,7 @@
         <v>14</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -798,7 +806,7 @@
         <v>14</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26">
@@ -811,7 +819,7 @@
         <v>15</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27">
@@ -824,7 +832,7 @@
         <v>18</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -837,7 +845,7 @@
         <v>10</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -850,7 +858,7 @@
         <v>10</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -863,7 +871,7 @@
         <v>14</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31">
@@ -953,43 +961,47 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>SG01-001</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>成果物ビューア画面</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>画面表示</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>画面が正常表示（全 UI 要素・モック準拠）</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. 成果物ビューア を開く</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr"/>
-      <c r="I2" s="3" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -1109,43 +1121,47 @@
       <c r="I5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>SG01-005</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>成果物ビューア画面</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>エラー</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>取得失敗の inline error + toast（成果物メタ）</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>/outputs/{id} が 5xx</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>1. API を でモックし開く</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>エラー表示 の inline error 表示 かつ toast 発火</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr"/>
-      <c r="I6" s="3" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -1226,43 +1242,47 @@
       <c r="I8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>SG01-009</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>成果物ビューア画面</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>エラー</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>取得失敗の inline error + toast（署名DL URL）</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>/outputs/{id}/content-url が 5xx</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>1. API を でモックし開く</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>エラー表示 の inline error 表示 かつ toast 発火</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr"/>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -1343,82 +1363,90 @@
       <c r="I11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>SG01-013</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>成果物ビューア画面</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>エラー</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>取得失敗の inline error + toast（コメント）</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>/comments?target=workflow_output が 5xx</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>1. API を でモックし開く</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>エラー表示 の inline error 表示 かつ toast 発火</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr"/>
-      <c r="I12" s="3" t="inlineStr"/>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>SG01-015</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>成果物ビューア画面</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>インタラクション</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>「iframe(署名URL)」を操作すると動作する（ボタンが正しく動作するか）</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>1. 「iframe(署名URL)」を目視</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>html_path を署名URLの iframe で安全表示(XSS回避)（onClick/href/API が実在し、押すと副作用が起きる）</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr"/>
-      <c r="I13" s="3" t="inlineStr"/>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -1616,82 +1644,90 @@
       <c r="I18" s="3" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>SG01-021</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>成果物ビューア画面</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>未生成</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>HTML未生成 409 表示</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>html_path 無し</t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>1. 未生成の成果物を開く</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>『まだ生成されていません』表示</t>
         </is>
       </c>
-      <c r="H19" s="3" t="inlineStr"/>
-      <c r="I19" s="3" t="inlineStr"/>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>SG01-022</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>成果物ビューア画面</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>読み上げ対応</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>axe scan で 0 critical/serious</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>1. axe を実行</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>critical/serious 違反 0（semantic role/aria）</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr"/>
-      <c r="I20" s="3" t="inlineStr"/>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -1772,43 +1808,47 @@
       <c r="I22" s="3" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>SG01-025</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>成果物ビューア画面</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>到達性</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
         </is>
       </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
         <is>
           <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
         </is>
       </c>
-      <c r="G23" s="3" t="inlineStr">
+      <c r="G23" s="4" t="inlineStr">
         <is>
           <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
         </is>
       </c>
-      <c r="H23" s="3" t="inlineStr"/>
-      <c r="I23" s="3" t="inlineStr"/>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1883,43 +1923,47 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>SH01-001</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>モックビューア画面</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>画面表示</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>画面が正常表示（全 UI 要素・モック準拠）</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. モックビューア を開く</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr"/>
-      <c r="I2" s="3" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -2273,82 +2317,90 @@
       <c r="I11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>SH01-013</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>モックビューア画面</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>未設定</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>storage 未設定 503 表示</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>storage 未設定</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>1. 未設定環境で開く</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>『保存先が未設定』表示</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr"/>
-      <c r="I12" s="3" t="inlineStr"/>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>SH01-014</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>モックビューア画面</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>読み上げ対応</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>axe scan で 0 critical/serious</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>1. axe を実行</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>critical/serious 違反 0（semantic role/aria）</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr"/>
-      <c r="I13" s="3" t="inlineStr"/>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -2429,43 +2481,47 @@
       <c r="I15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>SH01-017</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>モックビューア画面</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>到達性</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr"/>
-      <c r="I16" s="3" t="inlineStr"/>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2540,43 +2596,47 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>SI01-001</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>タスクボード画面</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>画面表示</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>画面が正常表示（全 UI 要素・モック準拠）</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. タスクボード を開く</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr"/>
-      <c r="I2" s="3" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -2735,121 +2795,133 @@
       <c r="I6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>SI01-007</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>タスクボード画面</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>インタラクション</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>「▶再生」を操作すると動作する（ボタンが正しく動作するか）</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>1. 「▶再生」をクリック</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>ready/blocked カードで /tasks/{id}/play(dispatcher)（onClick/href/API が実在し、押すと副作用が起きる）</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>SI01-008</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>タスクボード画面</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>インタラクション</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>「6列 lifecycle」を操作すると動作する（ボタンが正しく動作するか）</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>1. 「6列 lifecycle」を目視</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>backlog/ready/in_progress/awaiting/done/blocked にマップ（onClick/href/API が実在し、押すと副作用が起きる）</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>SI01-009</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>タスクボード画面</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>更新</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>再生(play): 送信→反映</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>必須入力済</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>1. 再生(play) を実行</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>/tasks/{id}/play 呼び出し→成功表示→別GET/DBに反映</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr"/>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -2891,43 +2963,47 @@
       <c r="I10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>SI01-011</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>タスクボード画面</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>読み上げ対応</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>axe scan で 0 critical/serious</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>1. axe を実行</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>critical/serious 違反 0（semantic role/aria）</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr"/>
-      <c r="I11" s="3" t="inlineStr"/>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -3008,43 +3084,47 @@
       <c r="I13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>SI01-014</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>タスクボード画面</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>到達性</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr"/>
-      <c r="I14" s="3" t="inlineStr"/>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3119,43 +3199,47 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>SI02-001</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>タスク詳細(6タブ)画面</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>画面表示</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>画面が正常表示（全 UI 要素・モック準拠）</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. タスク詳細(6タブ) を開く</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr"/>
-      <c r="I2" s="3" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -3236,43 +3320,47 @@
       <c r="I4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>SI02-004</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>タスク詳細(6タブ)画面</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>空データ</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>0 件時の空状態（詳細）</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>/tasks/{id} が空配列</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>1. データ0件で開く</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>空状態メッセージを表示（/undefined 参照にならない）</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -3353,43 +3441,47 @@
       <c r="I7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>SI02-008</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>タスク詳細(6タブ)画面</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>空データ</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>0 件時の空状態（受入条件）</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>/tasks/{id}/acceptance-criteria が空配列</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>1. データ0件で開く</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>空状態メッセージを表示（/undefined 参照にならない）</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -3470,43 +3562,47 @@
       <c r="I10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>SI02-012</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>タスク詳細(6タブ)画面</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>空データ</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>0 件時の空状態（実行履歴）</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>/tasks/{id}/executions が空配列</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>1. データ0件で開く</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>空状態メッセージを表示（/undefined 参照にならない）</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr"/>
-      <c r="I11" s="3" t="inlineStr"/>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -3587,43 +3683,47 @@
       <c r="I13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>SI02-016</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>タスク詳細(6タブ)画面</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>空データ</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>0 件時の空状態（コメント）</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>/comments?target=task が空配列</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>1. データ0件で開く</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>空状態メッセージを表示（/undefined 参照にならない）</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr"/>
-      <c r="I14" s="3" t="inlineStr"/>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -3665,43 +3765,47 @@
       <c r="I15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>SI02-019</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>タスク詳細(6タブ)画面</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>インタラクション</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>「概要/仕様/入出力/実行履歴/添付/コメント タブ」を操作すると動作する（ボタンが正しく動作するか）</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>1. 「概要/仕様/入出力/実行履歴/添付/コメント タブ」を各クリック</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>対応タブ内容を表示(aria-selected/controls)（onClick/href/API が実在し、押すと副作用が起きる）</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr"/>
-      <c r="I16" s="3" t="inlineStr"/>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -3743,43 +3847,47 @@
       <c r="I17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>SI02-021</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>タスク詳細(6タブ)画面</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>読み上げ対応</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>axe scan で 0 critical/serious</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
         <is>
           <t>1. axe を実行</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t>critical/serious 違反 0（semantic role/aria）</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr"/>
-      <c r="I18" s="3" t="inlineStr"/>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -3860,43 +3968,47 @@
       <c r="I20" s="3" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>SI02-024</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>タスク詳細(6タブ)画面</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>到達性</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr"/>
-      <c r="I21" s="3" t="inlineStr"/>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3971,43 +4083,47 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>SI03-001</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>実行モニタ(SSE)画面</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>画面表示</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>画面が正常表示（全 UI 要素・モック準拠）</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. 実行モニタ(SSE) を開く</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr"/>
-      <c r="I2" s="3" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -4166,43 +4282,47 @@
       <c r="I6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>SI03-007</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>実行モニタ(SSE)画面</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>インタラクション</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>「ログストリーム」を操作すると動作する（ボタンが正しく動作するか）</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>1. 「ログストリーム」を目視</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>SSE で snapshot/status_change/end/error を逐次表示（onClick/href/API が実在し、押すと副作用が起きる）</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -4361,43 +4481,47 @@
       <c r="I11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>SI03-012</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>実行モニタ(SSE)画面</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>到達性</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr"/>
-      <c r="I12" s="3" t="inlineStr"/>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4472,43 +4596,47 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>SJ01-001</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>承認インボックス画面</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>画面表示</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>画面が正常表示（全 UI 要素・モック準拠）</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. 承認インボックス を開く</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr"/>
-      <c r="I2" s="3" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -4550,43 +4678,47 @@
       <c r="I3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>SJ01-003</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>承認インボックス画面</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>データ取得</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>loading skeleton 表示（承認待ち(5種統合/本人)）</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>取得未完</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. 承認インボックス を開き取得完了前を観察</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -4667,121 +4799,133 @@
       <c r="I6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>SJ01-007</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>承認インボックス画面</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>インタラクション</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>「承認」を操作すると動作する（ボタンが正しく動作するか）</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>1. 「承認」をクリック</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>decide(approve)→インボックスから楽観除外（onClick/href/API が実在し、押すと副作用が起きる）</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>SJ01-008</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>承認インボックス画面</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>インタラクション</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>「差戻」を操作すると動作する（ボタンが正しく動作するか）</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>1. 「差戻」をクリック</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>decide(reject)→楽観除外（onClick/href/API が実在し、押すと副作用が起きる）</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>SJ01-009</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>承認インボックス画面</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>楽観更新</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>承認/差戻(decide): 成功で即時反映</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>対象が存在</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>1. 承認/差戻(decide) を実行</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>/approval-inbox/{id}/decide 呼び出し前にUIへ楽観反映→成功で確定（別GET再取得で反映）</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr"/>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -4862,43 +5006,47 @@
       <c r="I11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>SJ01-012</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>承認インボックス画面</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>読み上げ対応</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>axe scan で 0 critical/serious</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>1. axe を実行</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>critical/serious 違反 0（semantic role/aria）</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr"/>
-      <c r="I12" s="3" t="inlineStr"/>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -4979,43 +5127,47 @@
       <c r="I14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>SJ01-015</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>承認インボックス画面</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>到達性</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr"/>
-      <c r="I15" s="3" t="inlineStr"/>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5090,43 +5242,47 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>SK01-001</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>ナレッジエクスプローラ画面</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>画面表示</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>画面が正常表示（全 UI 要素・モック準拠）</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. ナレッジエクスプローラ を開く</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr"/>
-      <c r="I2" s="3" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -5285,43 +5441,47 @@
       <c r="I6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>SK01-007</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>ナレッジエクスプローラ画面</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>インタラクション</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>「ツリーノード」を操作すると動作する（ボタンが正しく動作するか）</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>1. 「ツリーノード」を展開/クリック</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>子ノード取得/詳細表示（onClick/href/API が実在し、押すと副作用が起きる）</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -5441,43 +5601,47 @@
       <c r="I10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>SK01-011</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>ナレッジエクスプローラ画面</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>到達性</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr"/>
-      <c r="I11" s="3" t="inlineStr"/>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5552,43 +5716,47 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>SK02-001</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>昇格レビュー画面</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>画面表示</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>画面が正常表示（全 UI 要素・モック準拠）</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. 昇格レビュー を開く</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr"/>
-      <c r="I2" s="3" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -5669,43 +5837,47 @@
       <c r="I4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>SK02-004</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>昇格レビュー画面</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>空データ</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>0 件時の空状態（昇格候補）</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>/knowledge/promotions が空配列</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>1. データ0件で開く</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>空状態メッセージを表示（/undefined 参照にならない）</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -6098,43 +6270,47 @@
       <c r="I15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>SK02-016</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>昇格レビュー画面</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>到達性</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr"/>
-      <c r="I16" s="3" t="inlineStr"/>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6209,43 +6385,47 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>SL01-001</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>クライアント招待管理画面</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>画面表示</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>画面が正常表示（全 UI 要素・モック準拠）</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. クライアント招待管理 を開く</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr"/>
-      <c r="I2" s="3" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -6716,43 +6896,47 @@
       <c r="I14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>SL01-015</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>クライアント招待管理画面</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>読み上げ対応</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>axe scan で 0 critical/serious</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>1. axe を実行</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>critical/serious 違反 0（semantic role/aria）</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr"/>
-      <c r="I15" s="3" t="inlineStr"/>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -6833,43 +7017,47 @@
       <c r="I17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>SL01-018</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>クライアント招待管理画面</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>到達性</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
         <is>
           <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr"/>
-      <c r="I18" s="3" t="inlineStr"/>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6944,43 +7132,47 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>SL02-001</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>クライアントサインイン画面</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>画面表示</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>画面が正常表示（全 UI 要素・モック準拠）</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. クライアントサインイン を開く</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr"/>
-      <c r="I2" s="3" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -7022,43 +7214,47 @@
       <c r="I3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>SL02-003</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>クライアントサインイン画面</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>入力フォーム</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>初期値/placeholder（招待トークン）</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. フォームを開く</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>招待トークン の初期値/placeholder が正しい</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -7100,43 +7296,47 @@
       <c r="I5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>SL02-005</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>クライアントサインイン画面</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>入力フォーム</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>初期値/placeholder（表示名）</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>1. フォームを開く</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>表示名 の初期値/placeholder が正しい</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr"/>
-      <c r="I6" s="3" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -7178,82 +7378,90 @@
       <c r="I7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>SL02-007</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>クライアントサインイン画面</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>インタラクション</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>「プロジェクトを開く」を操作すると動作する（ボタンが正しく動作するか）</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>1. 「プロジェクトを開く」をクリック</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>signin→client_portal cookie→/client/s_l03 遷移（onClick/href/API が実在し、押すと副作用が起きる）</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>SL02-008</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>クライアントサインイン画面</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>更新</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>サインイン: 送信→反映</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>必須入力済</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>1. サインイン を実行</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>/client/auth/signin 呼び出し→成功表示→別GET/DBに反映</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr"/>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -7451,43 +7659,47 @@
       <c r="I14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>SL02-014</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>クライアントサインイン画面</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>到達性</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr"/>
-      <c r="I15" s="3" t="inlineStr"/>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7562,43 +7774,47 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>SA01-001</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>サインイン/サインアップ画面</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>画面表示</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>画面が正常表示（全 UI 要素・モック準拠）</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. サインイン/サインアップ を開く</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr"/>
-      <c r="I2" s="3" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -7796,82 +8012,90 @@
       <c r="I7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>SA01-007</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>サインイン/サインアップ画面</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>インタラクション</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>「ログイン」を操作すると動作する（ボタンが正しく動作するか）</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>1. 「ログイン」をクリック</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>signin→atelier_access cookie→redirect（onClick/href/API が実在し、押すと副作用が起きる）</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>SA01-008</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>サインイン/サインアップ画面</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>更新</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>サインイン: 送信→反映</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>必須入力済</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>1. サインイン を実行</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>/auth/signin 呼び出し→成功表示→別GET/DBに反映</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr"/>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -7913,43 +8137,47 @@
       <c r="I10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>SA01-010</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>サインイン/サインアップ画面</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>更新</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>サインアップ: 送信→反映</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>必須入力済</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>1. サインアップ を実行</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>/auth/signup 呼び出し→成功表示→別GET/DBに反映</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr"/>
-      <c r="I11" s="3" t="inlineStr"/>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -8108,82 +8336,90 @@
       <c r="I15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>SA01-015</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>サインイン/サインアップ画面</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>状態永続</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>F5 リロードでログアウトに飛ばない</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>ログイン済</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>1. 画面で F5</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>保護ガードで維持・状態復元（URL クエリ等）</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr"/>
-      <c r="I16" s="3" t="inlineStr"/>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>SA01-016</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>サインイン/サインアップ画面</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>到達性</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr"/>
-      <c r="I17" s="3" t="inlineStr"/>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8258,43 +8494,47 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>SL03-001</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>クライアントプロジェクトビュー画面</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>画面表示</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>画面が正常表示（全 UI 要素・モック準拠）</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. クライアントプロジェクトビュー を開く</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr"/>
-      <c r="I2" s="3" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -8531,43 +8771,47 @@
       <c r="I8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>SL03-009</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>クライアントプロジェクトビュー画面</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>読み上げ対応</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>axe scan で 0 critical/serious</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>1. axe を実行</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>critical/serious 違反 0（semantic role/aria）</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr"/>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -8648,43 +8892,47 @@
       <c r="I11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>SL03-012</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>クライアントプロジェクトビュー画面</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>到達性</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr"/>
-      <c r="I12" s="3" t="inlineStr"/>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8759,43 +9007,47 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>SM01-001</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>議事録アップロード画面</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>画面表示</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>画面が正常表示（全 UI 要素・モック準拠）</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. 議事録アップロード を開く</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr"/>
-      <c r="I2" s="3" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -9266,43 +9518,47 @@
       <c r="I14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>SM01-015</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>議事録アップロード画面</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>到達性</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr"/>
-      <c r="I15" s="3" t="inlineStr"/>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9377,43 +9633,47 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>SO01-001</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>自動スケジュール(cron)画面</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>画面表示</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>画面が正常表示（全 UI 要素・モック準拠）</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. 自動スケジュール(cron) を開く</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr"/>
-      <c r="I2" s="3" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -9572,82 +9832,90 @@
       <c r="I6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>SO01-007</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>自動スケジュール(cron)画面</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>インタラクション</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>「有効/無効トグル」を操作すると動作する（ボタンが正しく動作するか）</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>1. 「有効/無効トグル」をクリック</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>enabled(楽観トグル)（onClick/href/API が実在し、押すと副作用が起きる）</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>SO01-008</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>自動スケジュール(cron)画面</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>楽観更新</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>有効トグル: 成功で即時反映</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>対象が存在</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>1. 有効トグル を実行</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>/cron-schedules/{id} 呼び出し前にUIへ楽観反映→成功で確定（別GET再取得で反映）</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -9767,43 +10035,47 @@
       <c r="I11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>SO01-012</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>自動スケジュール(cron)画面</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>読み上げ対応</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>axe scan で 0 critical/serious</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>1. axe を実行</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>critical/serious 違反 0（semantic role/aria）</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr"/>
-      <c r="I12" s="3" t="inlineStr"/>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -9884,43 +10156,47 @@
       <c r="I14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>SO01-015</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>自動スケジュール(cron)画面</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>到達性</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr"/>
-      <c r="I15" s="3" t="inlineStr"/>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9995,43 +10271,47 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>TUC36-001</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>通知センター画面</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>画面表示</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>画面が正常表示（全 UI 要素・モック準拠）</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. 通知センター を開く</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr"/>
-      <c r="I2" s="3" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -10073,43 +10353,47 @@
       <c r="I3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>TUC36-003</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>通知センター画面</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>データ取得</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>loading skeleton 表示（承認待ち集約）</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>取得未完</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. 通知センター を開き取得完了前を観察</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -10190,82 +10474,90 @@
       <c r="I6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>TUC36-007</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>通知センター画面</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>インタラクション</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>「既読」を操作すると動作する（ボタンが正しく動作するか）</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>1. 「既読」をクリック</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>localStorage に記録→未読数減・未読フィルタ連動（onClick/href/API が実在し、押すと副作用が起きる）</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>TUC36-008</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>通知センター画面</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>インタラクション</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>「すべて/未読のみ タブ」を操作すると動作する（ボタンが正しく動作するか）</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>1. 「すべて/未読のみ タブ」を各クリック</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>フィルタ切替（onClick/href/API が実在し、押すと副作用が起きる）</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -10424,43 +10716,47 @@
       <c r="I12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>TUC36-013</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>通知センター画面</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>読み上げ対応</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>axe scan で 0 critical/serious</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>1. axe を実行</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>critical/serious 違反 0（semantic role/aria）</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr"/>
-      <c r="I13" s="3" t="inlineStr"/>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -10502,82 +10798,90 @@
       <c r="I14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>TUC36-015</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>通知センター画面</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>状態永続</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>F5 リロードでログアウトに飛ばない</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>ログイン済</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>1. 画面で F5</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>保護ガードで維持・状態復元（URL クエリ等）</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr"/>
-      <c r="I15" s="3" t="inlineStr"/>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>TUC36-016</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>通知センター画面</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>到達性</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr"/>
-      <c r="I16" s="3" t="inlineStr"/>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10652,43 +10956,47 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>TUC37-001</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>プロフィール画面</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>画面表示</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>画面が正常表示（全 UI 要素・モック準拠）</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. プロフィール を開く</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr"/>
-      <c r="I2" s="3" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -11198,43 +11506,47 @@
       <c r="I15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>TUC37-016</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>プロフィール画面</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>読み上げ対応</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>axe scan で 0 critical/serious</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>1. axe を実行</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>critical/serious 違反 0（semantic role/aria）</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr"/>
-      <c r="I16" s="3" t="inlineStr"/>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -11315,43 +11627,47 @@
       <c r="I18" s="3" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>TUC37-019</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>プロフィール画面</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>到達性</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
         </is>
       </c>
-      <c r="H19" s="3" t="inlineStr"/>
-      <c r="I19" s="3" t="inlineStr"/>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11426,43 +11742,47 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>TUC38-001</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>ワークスペース切替画面</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>画面表示</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>画面が正常表示（全 UI 要素・モック準拠）</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. ワークスペース切替 を開く</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr"/>
-      <c r="I2" s="3" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -11660,43 +11980,47 @@
       <c r="I7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>TUC38-008</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>ワークスペース切替画面</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>読み上げ対応</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>axe scan で 0 critical/serious</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>1. axe を実行</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>critical/serious 違反 0（semantic role/aria）</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -11777,43 +12101,47 @@
       <c r="I10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>TUC38-011</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>ワークスペース切替画面</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>到達性</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr"/>
-      <c r="I11" s="3" t="inlineStr"/>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11888,43 +12216,47 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>TUC39-001</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>プロジェクト切替画面</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>画面表示</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>画面が正常表示（全 UI 要素・モック準拠）</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. プロジェクト切替 を開く</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr"/>
-      <c r="I2" s="3" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -12122,43 +12454,47 @@
       <c r="I7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>TUC39-008</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>プロジェクト切替画面</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>読み上げ対応</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>axe scan で 0 critical/serious</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>1. axe を実行</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>critical/serious 違反 0（semantic role/aria）</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -12239,43 +12575,47 @@
       <c r="I10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>TUC39-011</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>プロジェクト切替画面</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>到達性</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr"/>
-      <c r="I11" s="3" t="inlineStr"/>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12350,43 +12690,47 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>TUC40-001</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>グローバル検索画面</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>画面表示</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>画面が正常表示（全 UI 要素・モック準拠）</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. グローバル検索 を開く</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr"/>
-      <c r="I2" s="3" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -12428,82 +12772,90 @@
       <c r="I3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>TUC40-003</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>グローバル検索画面</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>データ取得</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>loading skeleton 表示（横断検索）</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>取得未完</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. グローバル検索 を開き取得完了前を観察</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>TUC40-004</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>グローバル検索画面</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>空データ</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>0 件時の空状態（横断検索）</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>/search?q=&amp;kind= が空配列</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>1. データ0件で開く</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>空状態メッセージを表示（/undefined 参照にならない）</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -12623,82 +12975,90 @@
       <c r="I8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>TUC40-009</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>グローバル検索画面</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>インタラクション</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>「種別フィルタ(all/project/task/knowledge/employee)」を操作すると動作する（ボタンが正しく動作するか）</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>1. 「種別フィルタ(all/project/task/knowledge/employee)」を各クリック</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>kind を切替して再検索（onClick/href/API が実在し、押すと副作用が起きる）</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr"/>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>TUC40-010</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>グローバル検索画面</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>インタラクション</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>「検索入力」を操作すると動作する（ボタンが正しく動作するか）</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>1. 「検索入力」を入力(debounce)</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>/search を叩き結果を種別ラベル付きで表示（onClick/href/API が実在し、押すと副作用が起きる）</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr"/>
-      <c r="I10" s="3" t="inlineStr"/>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -12740,43 +13100,47 @@
       <c r="I11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>TUC40-012</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>グローバル検索画面</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>読み上げ対応</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>axe scan で 0 critical/serious</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>1. axe を実行</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>critical/serious 違反 0（semantic role/aria）</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr"/>
-      <c r="I12" s="3" t="inlineStr"/>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -12857,43 +13221,47 @@
       <c r="I14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>TUC40-015</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>グローバル検索画面</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>到達性</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr"/>
-      <c r="I15" s="3" t="inlineStr"/>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12968,43 +13336,47 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>SA03-001</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>ワークスペース設定画面</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>画面表示</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>画面が正常表示（全 UI 要素・モック準拠）</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. ワークスペース設定 を開く</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr"/>
-      <c r="I2" s="3" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -13319,43 +13691,47 @@
       <c r="I10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>SA03-011</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>ワークスペース設定画面</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>楽観更新</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>名称保存(): 成功で即時反映</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>対象が存在</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>1. 名称保存() を実行</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>/workspaces/{id} + /account/ai-learning 呼び出し前にUIへ楽観反映→成功で確定（別GET再取得で反映）</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr"/>
-      <c r="I11" s="3" t="inlineStr"/>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -13397,43 +13773,47 @@
       <c r="I12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>SA03-013</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>ワークスペース設定画面</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>エラー</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>名称保存(): API 失敗時 inline error + toast</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>接続失敗/レート</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>1. 名称保存() を失敗させる</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>エラー表示 + toast、状態は不整合にならない</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr"/>
-      <c r="I13" s="3" t="inlineStr"/>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -13475,43 +13855,47 @@
       <c r="I14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>SA03-015</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>ワークスペース設定画面</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>読み上げ対応</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>axe scan で 0 critical/serious</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>1. axe を実行</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>critical/serious 違反 0（semantic role/aria）</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr"/>
-      <c r="I15" s="3" t="inlineStr"/>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -13592,43 +13976,47 @@
       <c r="I17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>SA03-018</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>ワークスペース設定画面</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>到達性</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
         <is>
           <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr"/>
-      <c r="I18" s="3" t="inlineStr"/>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13703,43 +14091,47 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>SB01-001</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>プロジェクト一覧画面</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>画面表示</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>画面が正常表示（全 UI 要素・モック準拠）</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. プロジェクト一覧 を開く</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr"/>
-      <c r="I2" s="3" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -13781,82 +14173,90 @@
       <c r="I3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>SB01-003</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>プロジェクト一覧画面</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>データ取得</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>loading skeleton 表示（プロジェクト一覧(カーソル)）</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>取得未完</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. プロジェクト一覧 を開き取得完了前を観察</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>SB01-004</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>プロジェクト一覧画面</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>空データ</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>0 件時の空状態（プロジェクト一覧(カーソル)）</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>/projects が空配列</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>1. データ0件で開く</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>空状態メッセージを表示（/undefined 参照にならない）</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -13898,121 +14298,133 @@
       <c r="I6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>SB01-007</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>プロジェクト一覧画面</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>インタラクション</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>「プロジェクト行」を操作すると動作する（ボタンが正しく動作するか）</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>1. 「プロジェクト行」をクリック</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>/projects/s_b02?project=id へ遷移（死リンク修正済）（onClick/href/API が実在し、押すと副作用が起きる）</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>SB01-008</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>プロジェクト一覧画面</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>インタラクション</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>「前へ/次へ」を操作すると動作する（ボタンが正しく動作するか）</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>1. 「前へ/次へ」をクリック</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>カーソルページング（端で無効）（onClick/href/API が実在し、押すと副作用が起きる）</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>SB01-009</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>プロジェクト一覧画面</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>到達性</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>行クリックの遷移先が実在ルート</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>1. 行をクリック</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>s_b02 ダッシュボードが開く（旧 /projects/{id}/dashboard 404 は #245 で修正）</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr"/>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -14132,43 +14544,47 @@
       <c r="I12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>SB01-013</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>プロジェクト一覧画面</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>到達性</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr"/>
-      <c r="I13" s="3" t="inlineStr"/>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -14243,43 +14659,47 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>SB02-001</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>プロジェクトダッシュボード画面</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>画面表示</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>画面が正常表示（全 UI 要素・モック準拠）</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. プロジェクトダッシュボード を開く</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr"/>
-      <c r="I2" s="3" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -14438,121 +14858,133 @@
       <c r="I6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>SB02-007</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>プロジェクトダッシュボード画面</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>インタラクション</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>「KPI タイル」を操作すると動作する（ボタンが正しく動作するか）</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>1. 「KPI タイル」を目視</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>現在フェーズ + タスク状態別件数を表示（onClick/href/API が実在し、押すと副作用が起きる）</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>SB02-008</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>プロジェクトダッシュボード画面</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>整合</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>集計値=DB実数</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>1. task_counts を select count(*) と突合</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>内訳合計=総数・数字が DB と一致</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>SB02-009</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>プロジェクトダッシュボード画面</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>読み上げ対応</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>axe scan で 0 critical/serious</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>1. axe を実行</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>critical/serious 違反 0（semantic role/aria）</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr"/>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -14633,43 +15065,47 @@
       <c r="I11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>SB02-012</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>プロジェクトダッシュボード画面</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>到達性</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr"/>
-      <c r="I12" s="3" t="inlineStr"/>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -14744,43 +15180,47 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>SC01-001</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>AI社員 組織図画面</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>画面表示</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>画面が正常表示（全 UI 要素・モック準拠）</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. AI社員 組織図 を開く</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr"/>
-      <c r="I2" s="3" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -14939,121 +15379,133 @@
       <c r="I6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>SC01-007</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>AI社員 組織図画面</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>インタラクション</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>「社員ボタン」を操作すると動作する（ボタンが正しく動作するか）</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>1. 「社員ボタン」をクリック</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>/employees/s_c02?employee=id へ遷移(編集)（onClick/href/API が実在し、押すと副作用が起きる）</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>SC01-008</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>AI社員 組織図画面</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>インタラクション</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>「部署セクション」を操作すると動作する（ボタンが正しく動作するか）</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>1. 「部署セクション」を目視</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>department 別に section 化（onClick/href/API が実在し、押すと副作用が起きる）</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>SC01-009</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>AI社員 組織図画面</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>読み上げ対応</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>axe scan で 0 critical/serious</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>1. axe を実行</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>critical/serious 違反 0（semantic role/aria）</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr"/>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -15134,43 +15586,47 @@
       <c r="I11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>SC01-012</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>AI社員 組織図画面</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>到達性</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr"/>
-      <c r="I12" s="3" t="inlineStr"/>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15245,43 +15701,47 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>SC02-001</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>AI社員 編集画面</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>画面表示</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>画面が正常表示（全 UI 要素・モック準拠）</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. AI社員 編集 を開く</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr"/>
-      <c r="I2" s="3" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -15440,43 +15900,47 @@
       <c r="I6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>SC02-007</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>AI社員 編集画面</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>入力フォーム</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>初期値/placeholder（display_name）</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>1. フォームを開く</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>display_name の初期値/placeholder が正しい</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -15518,121 +15982,133 @@
       <c r="I8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>SC02-009</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>AI社員 編集画面</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>入力フォーム</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>初期値/placeholder（tone_preset）</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>1. フォームを開く</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>tone_preset の初期値/placeholder が正しい</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr"/>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>SC02-010</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>AI社員 編集画面</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>入力フォーム</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>初期値/placeholder（custom_tone_text）</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>1. フォームを開く</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>custom_tone_text の初期値/placeholder が正しい</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr"/>
-      <c r="I10" s="3" t="inlineStr"/>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>SC02-011</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>AI社員 編集画面</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>更新</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>保存(): 送信→反映</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>必須入力済</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>1. 保存() を実行</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>/ai-employees/{id} 呼び出し→成功表示→別GET/DBに反映</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr"/>
-      <c r="I11" s="3" t="inlineStr"/>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -15830,43 +16306,47 @@
       <c r="I16" s="3" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>SC02-017</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>AI社員 編集画面</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>到達性</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr"/>
-      <c r="I17" s="3" t="inlineStr"/>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15941,43 +16421,47 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>SF01-001</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>工程ワークフロー(司令塔)画面</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>画面表示</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>画面が正常表示（全 UI 要素・モック準拠）</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. 工程ワークフロー(司令塔) を開く</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr"/>
-      <c r="I2" s="3" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -16136,82 +16620,90 @@
       <c r="I6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>SF01-007</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>工程ワークフロー(司令塔)画面</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>インタラクション</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>「工程ノード/依存エッジ」を操作すると動作する（ボタンが正しく動作するか）</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>1. 「工程ノード/依存エッジ」を目視</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>order 順ノード + 隣接エッジを描画（onClick/href/API が実在し、押すと副作用が起きる）</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>SF01-008</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>工程ワークフロー(司令塔)画面</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>読み上げ対応</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>axe scan で 0 critical/serious</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>1. axe を実行</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>critical/serious 違反 0（semantic role/aria）</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -16292,43 +16784,47 @@
       <c r="I10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>SF01-011</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>工程ワークフロー(司令塔)画面</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>到達性</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr"/>
-      <c r="I11" s="3" t="inlineStr"/>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -16403,43 +16899,47 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>SF02-001</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>フェーズ管理画面</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>画面表示</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>画面が正常表示（全 UI 要素・モック準拠）</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. フェーズ管理 を開く</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr"/>
-      <c r="I2" s="3" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -16598,82 +17098,90 @@
       <c r="I6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>SF02-007</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>フェーズ管理画面</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>インタラクション</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>「状態 select」を操作すると動作する（ボタンが正しく動作するか）</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>1. 「状態 select」を変更</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>で状態遷移(done↔completed/blocked↔skipped 変換・楽観)（onClick/href/API が実在し、押すと副作用が起きる）</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>SF02-008</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>フェーズ管理画面</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>楽観更新</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>状態遷移(select): 成功で即時反映</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>対象が存在</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>1. 状態遷移(select) を実行</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>/workflow/phases/{id} 呼び出し前にUIへ楽観反映→成功で確定（別GET再取得で反映）</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -16754,43 +17262,47 @@
       <c r="I10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>SF02-011</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>フェーズ管理画面</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>読み上げ対応</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>axe scan で 0 critical/serious</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>1. axe を実行</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>critical/serious 違反 0（semantic role/aria）</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr"/>
-      <c r="I11" s="3" t="inlineStr"/>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -16871,43 +17383,47 @@
       <c r="I13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>SF02-014</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>フェーズ管理画面</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>到達性</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr"/>
-      <c r="I14" s="3" t="inlineStr"/>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/apps/web/.qa/テスト仕様書_クライアント版.xlsx
+++ b/apps/web/.qa/テスト仕様書_クライアント版.xlsx
@@ -637,7 +637,7 @@
         <v>12</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
@@ -715,7 +715,7 @@
         <v>13</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19">
@@ -806,7 +806,7 @@
         <v>13</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26">
@@ -4733,43 +4733,47 @@
       <c r="I9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>SJ01-010</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>承認インボックス画面</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>楽観更新</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>承認/差戻(decide): 失敗でロールバック</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>サーバ 4xx/5xx</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>1. 承認/差戻(decide) を実行しAPIが失敗</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>楽観反映が元に戻り、inline error + toast を表示</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr"/>
-      <c r="I10" s="3" t="inlineStr"/>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -9411,43 +9415,47 @@
       <c r="I8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>SO01-009</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>自動スケジュール(cron)画面</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>楽観更新</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>有効トグル: 失敗でロールバック</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>サーバ 4xx/5xx</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>1. 有効トグル を実行しAPIが失敗</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>楽観反映が元に戻り、inline error + toast を表示</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr"/>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -16209,43 +16217,47 @@
       <c r="I8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>SF02-009</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>フェーズ管理画面</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>楽観更新</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>状態遷移(select): 失敗でロールバック</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>サーバ 4xx/5xx</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>1. 状態遷移(select) を実行しAPIが失敗</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>楽観反映が元に戻り、inline error + toast を表示</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr"/>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">

--- a/apps/web/.qa/テスト仕様書_クライアント版.xlsx
+++ b/apps/web/.qa/テスト仕様書_クライアント版.xlsx
@@ -1,39 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="概要" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="サインインサインアップ" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ワークスペース設定" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="プロジェクト一覧" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="プロジェクトダッシュボード" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI社員 組織図" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI社員 編集" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工程ワークフロー(司令塔)" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="フェーズ管理" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="成果物ビューア" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="モックビューア" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="タスクボード" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="タスク詳細(6タブ)" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="実行モニタ(SSE)" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="承認インボックス" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ナレッジエクスプローラ" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="昇格レビュー" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="クライアント招待管理" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="クライアントサインイン" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="クライアントプロジェクトビュー" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="議事録アップロード" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="自動スケジュール(cron)" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="通知センター" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="プロフィール" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ワークスペース切替" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="プロジェクト切替" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="グローバル検索" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="概要" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="サインインサインアップ" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ワークスペース設定" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="プロジェクト一覧" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="プロジェクトダッシュボード" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="AI社員 組織図" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="AI社員 編集" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="工程ワークフロー(司令塔)" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="フェーズ管理" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="成果物ビューア" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="モックビューア" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="タスクボード" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="タスク詳細(6タブ)" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="実行モニタ(SSE)" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="承認インボックス" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="ナレッジエクスプローラ" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="昇格レビュー" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="クライアント招待管理" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="クライアントサインイン" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="クライアントプロジェクトビュー" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="議事録アップロード" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="自動スケジュール(cron)" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="通知センター" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="プロフィール" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="ワークスペース切替" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="プロジェクト切替" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="グローバル検索" sheetId="27" state="visible" r:id="rId27"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -559,7 +559,7 @@
         <v>16</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -585,7 +585,7 @@
         <v>10</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -598,7 +598,7 @@
         <v>10</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
@@ -611,7 +611,7 @@
         <v>15</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
@@ -624,7 +624,7 @@
         <v>9</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -637,7 +637,7 @@
         <v>12</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -650,7 +650,7 @@
         <v>21</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14">
@@ -663,7 +663,7 @@
         <v>14</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
@@ -676,7 +676,7 @@
         <v>12</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -689,7 +689,7 @@
         <v>19</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17">
@@ -728,7 +728,7 @@
         <v>9</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -741,7 +741,7 @@
         <v>14</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -754,7 +754,7 @@
         <v>16</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -806,7 +806,7 @@
         <v>13</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26">
@@ -832,7 +832,7 @@
         <v>17</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28">
@@ -845,7 +845,7 @@
         <v>9</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29">
@@ -858,7 +858,7 @@
         <v>9</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30">
@@ -1043,43 +1043,47 @@
       <c r="I3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>SG01-003</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>成果物ビューア画面</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>データ取得</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>loading skeleton 表示（成果物メタ）</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>取得未完</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. 成果物ビューア を開き取得完了前を観察</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -1164,43 +1168,47 @@
       <c r="I6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>SG01-007</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>成果物ビューア画面</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>データ取得</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>loading skeleton 表示（署名DL URL）</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>取得未完</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>1. 成果物ビューア を開き取得完了前を観察</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -1285,43 +1293,47 @@
       <c r="I9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>SG01-011</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>成果物ビューア画面</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>データ取得</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>loading skeleton 表示（コメント）</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>取得未完</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>1. 成果物ビューア を開き取得完了前を観察</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr"/>
-      <c r="I10" s="3" t="inlineStr"/>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -1966,43 +1978,47 @@
       <c r="I3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>SH01-003</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>モックビューア画面</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>データ取得</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>loading skeleton 表示（モック詳細）</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>取得未完</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. モックビューア を開き取得完了前を観察</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -2083,43 +2099,47 @@
       <c r="I6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>SH01-007</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>モックビューア画面</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>データ取得</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>loading skeleton 表示（署名DL URL）</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>取得未完</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>1. モックビューア を開き取得完了前を観察</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -2600,43 +2620,47 @@
       <c r="I3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>SI01-003</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>タスクボード画面</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>データ取得</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>loading skeleton 表示（タスク一覧）</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>取得未完</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. タスクボード を開き取得完了前を観察</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -3164,43 +3188,47 @@
       <c r="I3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>SI02-003</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>タスク詳細(6タブ)画面</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>データ取得</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>loading skeleton 表示（詳細）</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>取得未完</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. タスク詳細(6タブ) を開き取得完了前を観察</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -3285,43 +3313,47 @@
       <c r="I6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>SI02-007</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>タスク詳細(6タブ)画面</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>データ取得</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>loading skeleton 表示（受入条件）</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>取得未完</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>1. タスク詳細(6タブ) を開き取得完了前を観察</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -3406,43 +3438,47 @@
       <c r="I9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>SI02-011</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>タスク詳細(6タブ)画面</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>データ取得</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>loading skeleton 表示（実行履歴）</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>取得未完</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>1. タスク詳細(6タブ) を開き取得完了前を観察</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr"/>
-      <c r="I10" s="3" t="inlineStr"/>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -3527,43 +3563,47 @@
       <c r="I12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>SI02-015</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>タスク詳細(6タブ)画面</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>データ取得</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>loading skeleton 表示（コメント）</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>取得未完</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>1. タスク詳細(6タブ) を開き取得完了前を観察</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr"/>
-      <c r="I13" s="3" t="inlineStr"/>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -5094,43 +5134,47 @@
       <c r="I3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>SK01-003</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>ナレッジエクスプローラ画面</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>データ取得</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>loading skeleton 表示（ナレッジツリー）</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>取得未完</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. ナレッジエクスプローラ を開き取得完了前を観察</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -5529,43 +5573,47 @@
       <c r="I3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>SK02-003</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>昇格レビュー画面</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>データ取得</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>loading skeleton 表示（昇格候補）</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>取得未完</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. 昇格レビュー を開き取得完了前を観察</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -6159,43 +6207,47 @@
       <c r="I3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>SL01-003</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>クライアント招待管理画面</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>データ取得</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>loading skeleton 表示（招待一覧）</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>取得未完</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. クライアント招待管理 を開き取得完了前を観察</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -9212,43 +9264,47 @@
       <c r="I3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>SO01-003</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>自動スケジュール(cron)画面</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>データ取得</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>loading skeleton 表示（スケジュール一覧）</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>取得未完</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. 自動スケジュール(cron) を開き取得完了前を観察</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -10461,43 +10517,47 @@
       <c r="I3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>TUC37-003</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>プロフィール画面</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>データ取得</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>loading skeleton 表示（自己プロフィール）</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>取得未完</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. プロフィール を開き取得完了前を観察</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -11208,43 +11268,47 @@
       <c r="I3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>TUC38-003</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>ワークスペース切替画面</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>データ取得</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>loading skeleton 表示（所属 WS 一覧）</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>取得未完</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. ワークスペース切替 を開き取得完了前を観察</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -11643,43 +11707,47 @@
       <c r="I3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>TUC39-003</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>プロジェクト切替画面</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>データ取得</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>loading skeleton 表示（現在WS内プロジェクト）</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>取得未完</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. プロジェクト切替 を開き取得完了前を観察</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -12685,43 +12753,47 @@
       <c r="I3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>SA03-003</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>ワークスペース設定画面</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>データ取得</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>loading skeleton 表示（WS 詳細）</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>取得未完</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. ワークスペース設定 を開き取得完了前を観察</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -13930,43 +14002,47 @@
       <c r="I3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>SB02-003</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>プロジェクトダッシュボード画面</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>データ取得</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>loading skeleton 表示（KPI ダッシュボード）</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>取得未完</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. プロジェクトダッシュボード を開き取得完了前を観察</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -14412,43 +14488,47 @@
       <c r="I3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>SC01-003</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>AI社員 組織図画面</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>データ取得</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>loading skeleton 表示（AI 社員一覧）</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>取得未完</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. AI社員 組織図 を開き取得完了前を観察</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -14894,43 +14974,47 @@
       <c r="I3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>SC02-003</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>AI社員 編集画面</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>データ取得</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>loading skeleton 表示（社員詳細）</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>取得未完</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. AI社員 編集 を開き取得完了前を観察</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -15575,43 +15659,47 @@
       <c r="I3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>SF01-003</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>工程ワークフロー(司令塔)画面</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>データ取得</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>loading skeleton 表示（工程一覧）</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>取得未完</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. 工程ワークフロー(司令塔) を開き取得完了前を観察</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -16014,43 +16102,47 @@
       <c r="I3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>SF02-003</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>フェーズ管理画面</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>データ取得</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>loading skeleton 表示（工程一覧）</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>取得未完</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. フェーズ管理 を開き取得完了前を観察</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">

--- a/apps/web/.qa/テスト仕様書_クライアント版.xlsx
+++ b/apps/web/.qa/テスト仕様書_クライアント版.xlsx
@@ -546,7 +546,7 @@
         <v>15</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -767,7 +767,7 @@
         <v>13</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23">
@@ -6962,43 +6962,47 @@
       <c r="I4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>SL02-004</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>クライアントサインイン画面</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>バリデーション</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>招待トークン: 必須/最小10</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>1. 招待トークン に不正値/未入力を入れる</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>エラー表示 かつ 送信ボタン無効</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -7044,43 +7048,47 @@
       <c r="I6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>SL02-006</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>クライアントサインイン画面</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>バリデーション</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>表示名: 任意</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>1. 表示名 に不正値/未入力を入れる</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>エラー表示 かつ 送信ボタン無効</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -7561,43 +7569,47 @@
       <c r="I4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>SA01-004</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>サインイン/サインアップ画面</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>バリデーション</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>email: 必須/型/最大200</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>1. email に不正値/未入力を入れる</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>エラー表示 かつ 送信ボタン無効</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -7639,43 +7651,47 @@
       <c r="I6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>SA01-006</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>サインイン/サインアップ画面</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>バリデーション</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>password: 必須/型</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>1. password に不正値/未入力を入れる</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>エラー表示 かつ 送信ボタン無効</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">

--- a/apps/web/.qa/テスト仕様書_クライアント版.xlsx
+++ b/apps/web/.qa/テスト仕様書_クライアント版.xlsx
@@ -1,39 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="概要" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="サインインサインアップ" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="ワークスペース設定" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="プロジェクト一覧" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="プロジェクトダッシュボード" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="AI社員 組織図" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="AI社員 編集" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="工程ワークフロー(司令塔)" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="フェーズ管理" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="成果物ビューア" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="モックビューア" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="タスクボード" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="タスク詳細(6タブ)" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="実行モニタ(SSE)" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="承認インボックス" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="ナレッジエクスプローラ" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="昇格レビュー" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="クライアント招待管理" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="クライアントサインイン" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="クライアントプロジェクトビュー" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="議事録アップロード" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="自動スケジュール(cron)" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="通知センター" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="プロフィール" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="ワークスペース切替" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="プロジェクト切替" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="グローバル検索" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="概要" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="サインインサインアップ" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ワークスペース設定" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="プロジェクト一覧" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="プロジェクトダッシュボード" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI社員 組織図" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI社員 編集" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工程ワークフロー(司令塔)" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="フェーズ管理" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="成果物ビューア" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="モックビューア" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="タスクボード" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="タスク詳細(6タブ)" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="実行モニタ(SSE)" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="承認インボックス" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ナレッジエクスプローラ" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="昇格レビュー" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="クライアント招待管理" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="クライアントサインイン" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="クライアントプロジェクトビュー" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="議事録アップロード" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="自動スケジュール(cron)" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="通知センター" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="プロフィール" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ワークスペース切替" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="プロジェクト切替" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="グローバル検索" sheetId="27" state="visible" r:id="rId27"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -546,7 +546,7 @@
         <v>15</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>16</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
@@ -572,7 +572,7 @@
         <v>11</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
@@ -585,7 +585,7 @@
         <v>10</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
@@ -598,7 +598,7 @@
         <v>10</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
@@ -611,7 +611,7 @@
         <v>15</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
@@ -624,7 +624,7 @@
         <v>9</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
@@ -637,7 +637,7 @@
         <v>12</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13">
@@ -650,7 +650,7 @@
         <v>21</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14">
@@ -663,7 +663,7 @@
         <v>14</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -676,7 +676,7 @@
         <v>12</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16">
@@ -689,7 +689,7 @@
         <v>19</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17">
@@ -702,7 +702,7 @@
         <v>10</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18">
@@ -715,7 +715,7 @@
         <v>13</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19">
@@ -728,7 +728,7 @@
         <v>9</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -741,7 +741,7 @@
         <v>14</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21">
@@ -754,7 +754,7 @@
         <v>16</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22">
@@ -767,7 +767,7 @@
         <v>13</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23">
@@ -780,7 +780,7 @@
         <v>10</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24">
@@ -793,7 +793,7 @@
         <v>13</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25">
@@ -806,7 +806,7 @@
         <v>13</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="26">
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="27">
@@ -832,7 +832,7 @@
         <v>17</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
     </row>
     <row r="28">
@@ -845,7 +845,7 @@
         <v>9</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29">
@@ -858,7 +858,7 @@
         <v>9</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30">
@@ -871,7 +871,7 @@
         <v>13</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="31">
@@ -882,7 +882,7 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>完全性: 全393件 ＝ クライアント可視337件 ＋ 技術専用56件（画面で見えない裏取り=エンジニア版）</t>
+          <t>完全性: 全391件 ＝ クライアント可視335件 ＋ 技術専用56件（画面で見えない裏取り=エンジニア版）</t>
         </is>
       </c>
       <c r="B32" s="3" t="n"/>
@@ -1004,43 +1004,47 @@
       <c r="I2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>SG01-002</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>成果物ビューア画面</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>視覚忠実度</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>配色/角丸/タイポが design token 準拠</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>1. 画面を目視</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr"/>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -1086,43 +1090,47 @@
       <c r="I4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>SG01-004</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>成果物ビューア画面</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>空データ</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>0 件時の空状態（成果物メタ）</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>/outputs/{id} が空配列</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>1. データ0件で開く</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>空状態メッセージを表示（/undefined 参照にならない）</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -1211,43 +1219,47 @@
       <c r="I7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>SG01-008</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>成果物ビューア画面</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>空データ</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>0 件時の空状態（署名DL URL）</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>/outputs/{id}/content-url が空配列</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>1. データ0件で開く</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>空状態メッセージを表示（/undefined 参照にならない）</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -1336,43 +1348,47 @@
       <c r="I10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>SG01-012</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>成果物ビューア画面</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>空データ</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>0 件時の空状態（コメント）</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>/comments?target=workflow_output が空配列</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>1. データ0件で開く</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>空状態メッセージを表示（/undefined 参照にならない）</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr"/>
-      <c r="I11" s="3" t="inlineStr"/>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -1461,199 +1477,219 @@
       <c r="I13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>SG01-016</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>成果物ビューア画面</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>インタラクション</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>「コメント追加 textarea」を操作すると動作する（ボタンが正しく動作するか）</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>1. 「コメント追加 textarea」を入力→コメント</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>/comments→楽観追加→別GETで反映（onClick/href/API が実在し、押すと副作用が起きる）</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr"/>
-      <c r="I14" s="3" t="inlineStr"/>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>SG01-017</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>成果物ビューア画面</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>楽観更新</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>コメント追加: 成功で即時反映</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>対象が存在</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>1. コメント追加 を実行</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>/comments 呼び出し前にUIへ楽観反映→成功で確定（別GET再取得で反映）</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr"/>
-      <c r="I15" s="3" t="inlineStr"/>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>SG01-018</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>成果物ビューア画面</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>楽観更新</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>コメント追加: 失敗でロールバック</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>サーバ 4xx/5xx</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>1. コメント追加 を実行しAPIが失敗</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>楽観反映が元に戻り、inline error + toast を表示</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr"/>
-      <c r="I16" s="3" t="inlineStr"/>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>SG01-019</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>成果物ビューア画面</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>エラー</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>コメント追加: API 失敗時 inline error + toast</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>接続失敗/レート</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>1. コメント追加 を失敗させる</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>エラー表示 + toast、状態は不整合にならない</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr"/>
-      <c r="I17" s="3" t="inlineStr"/>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>SG01-020</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>成果物ビューア画面</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>受容差分</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>座標ピン/スレッド返信/承認却下は非対象</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="F18" s="4" t="inlineStr">
         <is>
           <t>1. コメント節を確認</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t>comments API に座標/返信/承認が無く一覧+追加のみ(honest)</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr"/>
-      <c r="I18" s="3" t="inlineStr"/>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -1742,43 +1778,47 @@
       <c r="I20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>SG01-024</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>成果物ビューア画面</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>状態永続</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>F5 リロードでログアウトに飛ばない</t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>ログイン済</t>
         </is>
       </c>
-      <c r="F21" s="3" t="inlineStr">
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>1. 画面で F5</t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>保護ガードで維持・状態復元（URL クエリ等）</t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr"/>
-      <c r="I21" s="3" t="inlineStr"/>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -1939,43 +1979,47 @@
       <c r="I2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>SH01-002</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>モックビューア画面</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>視覚忠実度</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>配色/角丸/タイポが design token 準拠</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>1. 画面を目視</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr"/>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -2021,82 +2065,90 @@
       <c r="I4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>SH01-004</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>モックビューア画面</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>空データ</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>0 件時の空状態（モック詳細）</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>/mocks/{id} が空配列</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>1. データ0件で開く</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>空状態メッセージを表示（/undefined 参照にならない）</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>SH01-005</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>モックビューア画面</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>エラー</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>取得失敗の inline error + toast（モック詳細）</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>/mocks/{id} が 5xx</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>1. API を でモックし開く</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>エラー表示 の inline error 表示 かつ toast 発火</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr"/>
-      <c r="I6" s="3" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -2142,160 +2194,176 @@
       <c r="I7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>SH01-008</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>モックビューア画面</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>空データ</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>0 件時の空状態（署名DL URL）</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>/mocks/{id}/content-url が空配列</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>1. データ0件で開く</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>空状態メッセージを表示（/undefined 参照にならない）</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>SH01-009</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>モックビューア画面</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>エラー</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>取得失敗の inline error + toast（署名DL URL）</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>/mocks/{id}/content-url が 5xx</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>1. API を でモックし開く</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>エラー表示 の inline error 表示 かつ toast 発火</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr"/>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>SH01-011</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>モックビューア画面</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>インタラクション</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>「ビューポート切替(320/768/1024/1440)」を操作すると動作する（ボタンが正しく動作するか）</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>1. 「ビューポート切替(320/768/1024/1440)」を各クリック</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>iframe 幅が切替(aria-pressed)（onClick/href/API が実在し、押すと副作用が起きる）</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr"/>
-      <c r="I10" s="3" t="inlineStr"/>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>SH01-012</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>モックビューア画面</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>インタラクション</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>「iframe(署名URL)」を操作すると動作する（ボタンが正しく動作するか）</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>1. 「iframe(署名URL)」を目視</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>html_storage_path を署名URL iframe で表示（onClick/href/API が実在し、押すと副作用が起きる）</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr"/>
-      <c r="I11" s="3" t="inlineStr"/>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -2384,43 +2452,47 @@
       <c r="I13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>SH01-016</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>モックビューア画面</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>状態永続</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>F5 リロードでログアウトに飛ばない</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>ログイン済</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>1. 画面で F5</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>保護ガードで維持・状態復元（URL クエリ等）</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr"/>
-      <c r="I14" s="3" t="inlineStr"/>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -2581,43 +2653,47 @@
       <c r="I2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>SI01-002</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>タスクボード画面</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>視覚忠実度</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>配色/角丸/タイポが design token 準拠</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>1. 画面を目視</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr"/>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -2663,82 +2739,90 @@
       <c r="I4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>SI01-004</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>タスクボード画面</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>空データ</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>0 件時の空状態（タスク一覧）</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>/tasks?project_id が空配列</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>1. データ0件で開く</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>空状態メッセージを表示（/undefined 参照にならない）</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>SI01-005</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>タスクボード画面</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>エラー</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>取得失敗の inline error + toast（タスク一覧）</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>/tasks?project_id が 5xx</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>1. API を でモックし開く</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>エラー表示 の inline error 表示 かつ toast 発火</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr"/>
-      <c r="I6" s="3" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -2870,43 +2954,47 @@
       <c r="I9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>SI01-010</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>タスクボード画面</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>エラー</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>再生(play): API 失敗時 inline error + toast</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>接続失敗/レート</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>1. 再生(play) を失敗させる</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>エラー表示 + toast、状態は不整合にならない</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr"/>
-      <c r="I10" s="3" t="inlineStr"/>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -2952,43 +3040,47 @@
       <c r="I11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>SI01-013</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>タスクボード画面</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>状態永続</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>F5 リロードでログアウトに飛ばない</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>ログイン済</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>1. 画面で F5</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>保護ガードで維持・状態復元（URL クエリ等）</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr"/>
-      <c r="I12" s="3" t="inlineStr"/>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -3149,43 +3241,47 @@
       <c r="I2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>SI02-002</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>タスク詳細(6タブ)画面</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>視覚忠実度</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>配色/角丸/タイポが design token 準拠</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>1. 画面を目視</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr"/>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -3274,43 +3370,47 @@
       <c r="I5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>SI02-005</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>タスク詳細(6タブ)画面</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>エラー</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>取得失敗の inline error + toast（詳細）</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>/tasks/{id} が 5xx</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>1. API を でモックし開く</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>エラー表示 の inline error 表示 かつ toast 発火</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr"/>
-      <c r="I6" s="3" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -3399,43 +3499,47 @@
       <c r="I8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>SI02-009</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>タスク詳細(6タブ)画面</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>エラー</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>取得失敗の inline error + toast（受入条件）</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>/tasks/{id}/acceptance-criteria が 5xx</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>1. API を でモックし開く</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>エラー表示 の inline error 表示 かつ toast 発火</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr"/>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -3524,43 +3628,47 @@
       <c r="I11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>SI02-013</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>タスク詳細(6タブ)画面</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>エラー</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>取得失敗の inline error + toast（実行履歴）</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>/tasks/{id}/executions が 5xx</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>1. API を でモックし開く</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>エラー表示 の inline error 表示 かつ toast 発火</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr"/>
-      <c r="I12" s="3" t="inlineStr"/>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -3649,43 +3757,47 @@
       <c r="I14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>SI02-017</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>タスク詳細(6タブ)画面</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>エラー</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>取得失敗の inline error + toast（コメント）</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>/comments?target=task が 5xx</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>1. API を でモックし開く</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>エラー表示 の inline error 表示 かつ toast 発火</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr"/>
-      <c r="I15" s="3" t="inlineStr"/>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -3731,43 +3843,47 @@
       <c r="I16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>SI02-020</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>タスク詳細(6タブ)画面</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>受容差分</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>入出力/添付は情報なし表示</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>1. 各タブ</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>単一の裏付けAPI無しのため『情報なし』(honest)</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr"/>
-      <c r="I17" s="3" t="inlineStr"/>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -3813,43 +3929,47 @@
       <c r="I18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>SI02-023</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>タスク詳細(6タブ)画面</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>状態永続</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>F5 リロードでログアウトに飛ばない</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>ログイン済</t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>1. 画面で F5</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>保護ガードで維持・状態復元（URL クエリ等）</t>
         </is>
       </c>
-      <c r="H19" s="3" t="inlineStr"/>
-      <c r="I19" s="3" t="inlineStr"/>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -4010,43 +4130,47 @@
       <c r="I2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>SI03-002</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>実行モニタ(SSE)画面</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>視覚忠実度</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>配色/角丸/タイポが design token 準拠</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>1. 画面を目視</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr"/>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -4248,82 +4372,90 @@
       <c r="I8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>SI03-009</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>実行モニタ(SSE)画面</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>読み上げ対応</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>axe scan で 0 critical/serious</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>1. axe を実行</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>critical/serious 違反 0（semantic role/aria）</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr"/>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>SI03-011</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>実行モニタ(SSE)画面</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>状態永続</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>F5 リロードでログアウトに飛ばない</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>ログイン済</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>1. 画面で F5</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>保護ガードで維持・状態復元（URL クエリ等）</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr"/>
-      <c r="I10" s="3" t="inlineStr"/>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -4484,43 +4616,47 @@
       <c r="I2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>SJ01-002</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>承認インボックス画面</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>視覚忠実度</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>配色/角丸/タイポが design token 準拠</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>1. 画面を目視</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr"/>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -4566,82 +4702,90 @@
       <c r="I4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>SJ01-004</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>承認インボックス画面</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>空データ</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>0 件時の空状態（承認待ち(5種統合/本人)）</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>/approval-inbox が空配列</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>1. データ0件で開く</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>空状態メッセージを表示（/undefined 参照にならない）</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>SJ01-005</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>承認インボックス画面</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>エラー</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>取得失敗の inline error + toast（承認待ち(5種統合/本人)）</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>/approval-inbox が 5xx</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>1. API を でモックし開く</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>エラー表示 の inline error 表示 かつ toast 発火</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr"/>
-      <c r="I6" s="3" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -4816,43 +4960,47 @@
       <c r="I10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>SJ01-011</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>承認インボックス画面</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>エラー</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>承認/差戻(decide): API 失敗時 inline error + toast</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>接続失敗/レート</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>1. 承認/差戻(decide) を失敗させる</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>エラー表示 + toast、状態は不整合にならない</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr"/>
-      <c r="I11" s="3" t="inlineStr"/>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -4898,43 +5046,47 @@
       <c r="I12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>SJ01-014</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>承認インボックス画面</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>状態永続</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>F5 リロードでログアウトに飛ばない</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>ログイン済</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>1. 画面で F5</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>保護ガードで維持・状態復元（URL クエリ等）</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr"/>
-      <c r="I13" s="3" t="inlineStr"/>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -5095,43 +5247,47 @@
       <c r="I2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>SK01-002</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>ナレッジエクスプローラ画面</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>視覚忠実度</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>配色/角丸/タイポが design token 準拠</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>1. 画面を目視</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr"/>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -5177,82 +5333,90 @@
       <c r="I4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>SK01-004</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>ナレッジエクスプローラ画面</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>空データ</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>0 件時の空状態（ナレッジツリー）</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>/knowledge が空配列</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>1. データ0件で開く</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>空状態メッセージを表示（/undefined 参照にならない）</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>SK01-005</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>ナレッジエクスプローラ画面</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>エラー</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>取得失敗の inline error + toast（ナレッジツリー）</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>/knowledge が 5xx</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>1. API を でモックし開く</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>エラー表示 の inline error 表示 かつ toast 発火</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr"/>
-      <c r="I6" s="3" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -5298,82 +5462,90 @@
       <c r="I7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>SK01-008</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>ナレッジエクスプローラ画面</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>読み上げ対応</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>axe scan で 0 critical/serious</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>1. axe を実行</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>critical/serious 違反 0（semantic role/aria）</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>SK01-010</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>ナレッジエクスプローラ画面</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>状態永続</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>F5 リロードでログアウトに飛ばない</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>ログイン済</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>1. 画面で F5</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>保護ガードで維持・状態復元（URL クエリ等）</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr"/>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -5534,43 +5706,47 @@
       <c r="I2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>SK02-002</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>昇格レビュー画面</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>視覚忠実度</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>配色/角丸/タイポが design token 準拠</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>1. 画面を目視</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr"/>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -5659,355 +5835,391 @@
       <c r="I5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>SK02-005</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>昇格レビュー画面</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>エラー</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>取得失敗の inline error + toast（昇格候補）</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>/knowledge/promotions が 5xx</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>1. API を でモックし開く</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>エラー表示 の inline error 表示 かつ toast 発火</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr"/>
-      <c r="I6" s="3" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>SK02-007</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>昇格レビュー画面</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>インタラクション</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>「承認」を操作すると動作する（ボタンが正しく動作するか）</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>1. 「承認」をクリック</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>昇格処理→楽観除外（onClick/href/API が実在し、押すと副作用が起きる）</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>SK02-008</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>昇格レビュー画面</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>インタラクション</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>「却下」を操作すると動作する（ボタンが正しく動作するか）</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>1. 「却下」をクリック</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>却下 API 無し→クライアント側 dismiss（onClick/href/API が実在し、押すと副作用が起きる）</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>SK02-009</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>昇格レビュー画面</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>楽観更新</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>承認: 成功で即時反映</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>対象が存在</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>1. 承認 を実行</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>昇格承認 呼び出し前にUIへ楽観反映→成功で確定（別GET再取得で反映）</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr"/>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>SK02-010</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>昇格レビュー画面</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>楽観更新</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>承認: 失敗でロールバック</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>サーバ 4xx/5xx</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>1. 承認 を実行しAPIが失敗</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>楽観反映が元に戻り、inline error + toast を表示</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr"/>
-      <c r="I10" s="3" t="inlineStr"/>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>SK02-011</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>昇格レビュー画面</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>エラー</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>承認: API 失敗時 inline error + toast</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>接続失敗/レート</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>1. 承認 を失敗させる</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>エラー表示 + toast、状態は不整合にならない</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr"/>
-      <c r="I11" s="3" t="inlineStr"/>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>SK02-012</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>昇格レビュー画面</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>受容差分</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>却下はクライアント dismiss</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>1. 却下</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>reject API 無しのため一覧から即時除去(honest)</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr"/>
-      <c r="I12" s="3" t="inlineStr"/>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>SK02-013</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>昇格レビュー画面</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>読み上げ対応</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>axe scan で 0 critical/serious</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>1. axe を実行</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>critical/serious 違反 0（semantic role/aria）</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr"/>
-      <c r="I13" s="3" t="inlineStr"/>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>SK02-015</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>昇格レビュー画面</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>状態永続</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>F5 リロードでログアウトに飛ばない</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>ログイン済</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>1. 画面で F5</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>保護ガードで維持・状態復元（URL クエリ等）</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr"/>
-      <c r="I14" s="3" t="inlineStr"/>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -6168,43 +6380,47 @@
       <c r="I2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>SL01-002</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>クライアント招待管理画面</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>視覚忠実度</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>配色/角丸/タイポが design token 準拠</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>1. 画面を目視</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr"/>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -6250,394 +6466,434 @@
       <c r="I4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>SL01-004</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>クライアント招待管理画面</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>空データ</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>0 件時の空状態（招待一覧）</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>/client-invitations?project_id が空配列</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>1. データ0件で開く</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>空状態メッセージを表示（/undefined 参照にならない）</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>SL01-005</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>クライアント招待管理画面</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>エラー</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>取得失敗の inline error + toast（招待一覧）</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>/client-invitations?project_id が 5xx</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>1. API を でモックし開く</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>エラー表示 の inline error 表示 かつ toast 発火</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr"/>
-      <c r="I6" s="3" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>SL01-007</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>クライアント招待管理画面</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>インタラクション</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>「招待を発行」を操作すると動作する（ボタンが正しく動作するか）</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>1. 「招待を発行」をクリック</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>→raw token を1度だけバナー表示(R-T08 再取得不可)（onClick/href/API が実在し、押すと副作用が起きる）</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>SL01-008</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>クライアント招待管理画面</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>インタラクション</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>「失効」を操作すると動作する（ボタンが正しく動作するか）</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>1. 「失効」をクリック</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>revoke(楽観)（onClick/href/API が実在し、押すと副作用が起きる）</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>SL01-009</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>クライアント招待管理画面</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>更新</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>発行(): 送信→反映</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>必須入力済</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>1. 発行() を実行</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>/client-invitations 呼び出し→成功表示→別GET/DBに反映</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr"/>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>SL01-010</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>クライアント招待管理画面</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>エラー</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>発行(): API 失敗時 inline error + toast</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>接続失敗/レート</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>1. 発行() を失敗させる</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>エラー表示 + toast、状態は不整合にならない</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr"/>
-      <c r="I10" s="3" t="inlineStr"/>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>SL01-011</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>クライアント招待管理画面</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>楽観更新</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>失効(revoke): 成功で即時反映</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>対象が存在</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>1. 失効(revoke) を実行</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>/client-invitations/{id}/revoke 呼び出し前にUIへ楽観反映→成功で確定（別GET再取得で反映）</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr"/>
-      <c r="I11" s="3" t="inlineStr"/>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>SL01-012</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>クライアント招待管理画面</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>楽観更新</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>失効(revoke): 失敗でロールバック</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>サーバ 4xx/5xx</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>1. 失効(revoke) を実行しAPIが失敗</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>楽観反映が元に戻り、inline error + toast を表示</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr"/>
-      <c r="I12" s="3" t="inlineStr"/>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>SL01-013</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>クライアント招待管理画面</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>エラー</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>失効(revoke): API 失敗時 inline error + toast</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>接続失敗/レート</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>1. 失効(revoke) を失敗させる</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>エラー表示 + toast、状態は不整合にならない</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr"/>
-      <c r="I13" s="3" t="inlineStr"/>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>SL01-014</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>クライアント招待管理画面</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>受容差分</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>再送ボタンは非表示</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>1. 一覧確認</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>resend API 無しのため非表示(honest)</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr"/>
-      <c r="I14" s="3" t="inlineStr"/>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -6683,43 +6939,47 @@
       <c r="I15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>SL01-017</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>クライアント招待管理画面</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>状態永続</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>F5 リロードでログアウトに飛ばない</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>ログイン済</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>1. 画面で F5</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>保護ガードで維持・状態復元（URL クエリ等）</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr"/>
-      <c r="I16" s="3" t="inlineStr"/>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -6880,43 +7140,47 @@
       <c r="I2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>SL02-002</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>クライアントサインイン画面</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>視覚忠実度</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>配色/角丸/タイポが design token 準拠</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>1. 画面を目視</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr"/>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -7177,160 +7441,176 @@
       <c r="I9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>SL02-009</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>クライアントサインイン画面</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>エラー</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>サインイン: API 失敗時 inline error + toast</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>接続失敗/レート</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>1. サインイン を失敗させる</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>エラー表示 + toast、状態は不整合にならない</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr"/>
-      <c r="I10" s="3" t="inlineStr"/>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>SL02-010</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>クライアントサインイン画面</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>認証</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>invalid/410 expired 文言化</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>無効/期限切れトークン</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>1. 無効トークンで送信</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>→『招待トークンが無効』/410→『有効期限切れ』</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr"/>
-      <c r="I11" s="3" t="inlineStr"/>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>SL02-011</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>クライアントサインイン画面</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>読み上げ対応</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>axe scan で 0 critical/serious</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>1. axe を実行</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>critical/serious 違反 0（semantic role/aria）</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr"/>
-      <c r="I12" s="3" t="inlineStr"/>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>SL02-013</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>クライアントサインイン画面</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>状態永続</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>F5 リロードでログアウトに飛ばない</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>ログイン済</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>1. 画面で F5</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>保護ガードで維持・状態復元（URL クエリ等）</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr"/>
-      <c r="I13" s="3" t="inlineStr"/>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -7491,82 +7771,90 @@
       <c r="I2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>SA01-002</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>サインイン/サインアップ画面</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>視覚忠実度</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>配色/角丸/タイポが design token 準拠</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>1. 画面を目視</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr"/>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>SA01-003</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>サインイン/サインアップ画面</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>入力フォーム</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>初期値/placeholder（email）</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. フォームを開く</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>email の初期値/placeholder が正しい</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -7612,43 +7900,47 @@
       <c r="I5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>SA01-005</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>サインイン/サインアップ画面</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>入力フォーム</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>初期値/placeholder（password）</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>1. フォームを開く</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>password の初期値/placeholder が正しい</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr"/>
-      <c r="I6" s="3" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -7780,43 +8072,47 @@
       <c r="I9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>SA01-009</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>サインイン/サインアップ画面</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>エラー</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>サインイン: API 失敗時 inline error + toast</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>接続失敗/レート</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>1. サインイン を失敗させる</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>エラー表示 + toast、状態は不整合にならない</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr"/>
-      <c r="I10" s="3" t="inlineStr"/>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -7862,121 +8158,133 @@
       <c r="I11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>SA01-011</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>サインイン/サインアップ画面</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>エラー</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>サインアップ: API 失敗時 inline error + toast</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>接続失敗/レート</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>1. サインアップ を失敗させる</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>エラー表示 + toast、状態は不整合にならない</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr"/>
-      <c r="I12" s="3" t="inlineStr"/>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>SA01-012</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>サインイン/サインアップ画面</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>AI学習</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>signup で ai_training_optin=false 既定</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>1. サインアップ</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>AI学習デフォルトOFF(rule#6)で consents 送信</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr"/>
-      <c r="I13" s="3" t="inlineStr"/>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>SA01-013</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>サインイン/サインアップ画面</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>読み上げ対応</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>axe scan で 0 critical/serious</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>1. axe を実行</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>critical/serious 違反 0（semantic role/aria）</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr"/>
-      <c r="I14" s="3" t="inlineStr"/>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -8180,238 +8488,262 @@
       <c r="I2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>SL03-002</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>クライアントプロジェクトビュー画面</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>視覚忠実度</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>配色/角丸/タイポが design token 準拠</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>1. 画面を目視</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr"/>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>SL03-003</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>クライアントプロジェクトビュー画面</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>データ取得</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>loading skeleton 表示（限定ビュー(client JWT)）</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>取得未完</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. クライアントプロジェクトビュー を開き取得完了前を観察</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>SL03-004</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>クライアントプロジェクトビュー画面</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>空データ</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>0 件時の空状態（限定ビュー(client JWT)）</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>/client/projects/{id} が空配列</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>1. データ0件で開く</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>空状態メッセージを表示（/undefined 参照にならない）</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>SL03-005</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>クライアントプロジェクトビュー画面</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>エラー</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>取得失敗の inline error + toast（限定ビュー(client JWT)）</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>/client/projects/{id} が 5xx</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>1. API を でモックし開く</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>エラー表示 の inline error 表示 かつ toast 発火</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr"/>
-      <c r="I6" s="3" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>SL03-007</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>クライアントプロジェクトビュー画面</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>R-T08越境</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>他プロジェクトは 拒否</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>他プロジェクトの id</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>1. 越境 id でアクセス</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>API が cross_project→拒否表示(越境不可)</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>SL03-008</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>クライアントプロジェクトビュー画面</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>認証</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>token 未保有→サインイン誘導</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>cookie 無し</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>1. token 無しで開く</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>『サインインが必要』表示</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -8457,43 +8789,47 @@
       <c r="I9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>SL03-011</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>クライアントプロジェクトビュー画面</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>状態永続</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>F5 リロードでログアウトに飛ばない</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>ログイン済</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>1. 画面で F5</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>保護ガードで維持・状態復元（URL クエリ等）</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr"/>
-      <c r="I10" s="3" t="inlineStr"/>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -8654,43 +8990,47 @@
       <c r="I2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>SM01-002</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>議事録アップロード画面</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>視覚忠実度</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>配色/角丸/タイポが design token 準拠</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>1. 画面を目視</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr"/>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -8810,43 +9150,47 @@
       <c r="I6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>SM01-007</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>議事録アップロード画面</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>インタラクション</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>「ファイル選択」を操作すると動作する（ボタンが正しく動作するか）</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>1. 「ファイル選択」を選択</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>署名URL発行→実PUT→登録→transcribe キュー→polling→本文表示（onClick/href/API が実在し、押すと副作用が起きる）</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -9005,82 +9349,90 @@
       <c r="I11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>SM01-012</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>議事録アップロード画面</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>読み上げ対応</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>axe scan で 0 critical/serious</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>1. axe を実行</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>critical/serious 違反 0（semantic role/aria）</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr"/>
-      <c r="I12" s="3" t="inlineStr"/>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>SM01-014</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>議事録アップロード画面</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>状態永続</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>F5 リロードでログアウトに飛ばない</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>ログイン済</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>1. 画面で F5</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>保護ガードで維持・状態復元（URL クエリ等）</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr"/>
-      <c r="I13" s="3" t="inlineStr"/>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -9241,43 +9593,47 @@
       <c r="I2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>SO01-002</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>自動スケジュール(cron)画面</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>視覚忠実度</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>配色/角丸/タイポが design token 準拠</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>1. 画面を目視</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr"/>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -9323,82 +9679,90 @@
       <c r="I4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>SO01-004</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>自動スケジュール(cron)画面</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>空データ</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>0 件時の空状態（スケジュール一覧）</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>/cron-schedules?project_id が空配列</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>1. データ0件で開く</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>空状態メッセージを表示（/undefined 参照にならない）</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>SO01-005</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>自動スケジュール(cron)画面</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>エラー</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>取得失敗の inline error + toast（スケジュール一覧）</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>/cron-schedules?project_id が 5xx</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>1. API を でモックし開く</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>エラー表示 の inline error 表示 かつ toast 発火</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr"/>
-      <c r="I6" s="3" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -9530,82 +9894,90 @@
       <c r="I9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>SO01-010</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>自動スケジュール(cron)画面</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>エラー</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>有効トグル: API 失敗時 inline error + toast</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>接続失敗/レート</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>1. 有効トグル を失敗させる</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>エラー表示 + toast、状態は不整合にならない</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr"/>
-      <c r="I10" s="3" t="inlineStr"/>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>SO01-011</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>自動スケジュール(cron)画面</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>受容差分</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>即時実行ボタンは非表示</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>1. 一覧確認</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>run-now API 無しのため列非表示(honest)</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr"/>
-      <c r="I11" s="3" t="inlineStr"/>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -9651,43 +10023,47 @@
       <c r="I12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>SO01-014</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>自動スケジュール(cron)画面</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>状態永続</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>F5 リロードでログアウトに飛ばない</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>ログイン済</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>1. 画面で F5</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>保護ガードで維持・状態復元（URL クエリ等）</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr"/>
-      <c r="I13" s="3" t="inlineStr"/>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -9743,7 +10119,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9848,43 +10224,47 @@
       <c r="I2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>TUC36-002</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>通知センター画面</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>視覚忠実度</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>配色/角丸/タイポが design token 準拠</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>1. 画面を目視</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr"/>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -9930,82 +10310,90 @@
       <c r="I4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>TUC36-004</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>通知センター画面</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>空データ</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>0 件時の空状態（承認待ち集約）</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>/approval-inbox が空配列</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>1. データ0件で開く</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>空状態メッセージを表示（/undefined 参照にならない）</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>TUC36-005</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>通知センター画面</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>エラー</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>取得失敗の inline error + toast（承認待ち集約）</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>/approval-inbox が 5xx</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>1. API を でモックし開く</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>エラー表示 の inline error 表示 かつ toast 発火</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr"/>
-      <c r="I6" s="3" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -10094,165 +10482,181 @@
       <c r="I8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>TUC36-009</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>通知センター画面</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>楽観更新</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>既読(localStorage): 成功で即時反映</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>対象が存在</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>1. 既読(localStorage) を実行</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>localStorage 更新 呼び出し前にUIへ楽観反映→成功で確定（別GET再取得で反映）</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr"/>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>TUC36-010</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>TUC36-012</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>通知センター画面</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>楽観更新</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>既読(localStorage): 失敗でロールバック</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>サーバ 4xx/5xx</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>1. 既読(localStorage) を実行しAPIが失敗</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>楽観反映が元に戻り、inline error + toast を表示</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr"/>
-      <c r="I10" s="3" t="inlineStr"/>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>受容差分</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>永続既読/承認以外の種別は別migration</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>1. 既読挙動</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>専用テーブル(R-T08致命級)が無く localStorage 管理(MVP)</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>TUC36-011</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>TUC36-013</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>通知センター画面</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>エラー</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>既読(localStorage): API 失敗時 inline error + toast</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>接続失敗/レート</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>1. 既読(localStorage) を失敗させる</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>エラー表示 + toast、状態は不整合にならない</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr"/>
-      <c r="I11" s="3" t="inlineStr"/>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>読み上げ対応</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>axe scan で 0 critical/serious</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>1. axe を実行</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>critical/serious 違反 0（semantic role/aria）</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>TUC36-012</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>TUC36-015</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>通知センター画面</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>受容差分</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>永続既読/承認以外の種別は別migration</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>1. 既読挙動</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>専用テーブル(R-T08致命級)が無く localStorage 管理(MVP)</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr"/>
-      <c r="I12" s="3" t="inlineStr"/>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>状態永続</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>F5 リロードでログアウトに飛ばない</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>ログイン済</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面で F5</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>保護ガードで維持・状態復元（URL クエリ等）</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>TUC36-013</t>
+          <t>TUC36-016</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -10262,12 +10666,12 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>読み上げ対応</t>
+          <t>到達性</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>axe scan で 0 critical/serious</t>
+          <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -10277,12 +10681,12 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>1. axe を実行</t>
+          <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>critical/serious 違反 0（semantic role/aria）</t>
+          <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -10291,92 +10695,6 @@
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>TUC36-015</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>通知センター画面</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>状態永続</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>F5 リロードでログアウトに飛ばない</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>ログイン済</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>1. 画面で F5</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>保護ガードで維持・状態復元（URL クエリ等）</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I14" s="4" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>TUC36-016</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>通知センター画面</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>到達性</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I15" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10494,43 +10812,47 @@
       <c r="I2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>TUC37-002</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>プロフィール画面</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>視覚忠実度</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>配色/角丸/タイポが design token 準拠</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>1. 画面を目視</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr"/>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -10576,433 +10898,477 @@
       <c r="I4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>TUC37-004</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>プロフィール画面</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>空データ</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>0 件時の空状態（自己プロフィール）</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>/me が空配列</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>1. データ0件で開く</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>空状態メッセージを表示（/undefined 参照にならない）</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>TUC37-005</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>プロフィール画面</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>エラー</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>取得失敗の inline error + toast（自己プロフィール）</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>/me が 5xx</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>1. API を でモックし開く</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>エラー表示 の inline error 表示 かつ toast 発火</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr"/>
-      <c r="I6" s="3" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>TUC37-007</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>プロフィール画面</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>入力フォーム</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>初期値/placeholder（display_name）</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>1. フォームを開く</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>display_name の初期値/placeholder が正しい</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>TUC37-008</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>プロフィール画面</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>バリデーション</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>display_name: 必須/最大100</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>1. display_name に不正値/未入力を入れる</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>エラー表示 かつ 送信ボタン無効</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>TUC37-009</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>プロフィール画面</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>入力フォーム</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>初期値/placeholder（email）</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>1. フォームを開く</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>email の初期値/placeholder が正しい</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr"/>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>TUC37-010</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>プロフィール画面</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>バリデーション</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>email: readonly</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>1. email に不正値/未入力を入れる</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>エラー表示 かつ 送信ボタン無効</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr"/>
-      <c r="I10" s="3" t="inlineStr"/>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>TUC37-011</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>プロフィール画面</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>インタラクション</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>「保存」を操作すると動作する（ボタンが正しく動作するか）</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>1. 「保存」をクリック</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>/me(楽観)→保存表示（onClick/href/API が実在し、押すと副作用が起きる）</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr"/>
-      <c r="I11" s="3" t="inlineStr"/>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>TUC37-012</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>プロフィール画面</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>楽観更新</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>表示名保存(): 成功で即時反映</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>対象が存在</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>1. 表示名保存() を実行</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>/me 呼び出し前にUIへ楽観反映→成功で確定（別GET再取得で反映）</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr"/>
-      <c r="I12" s="3" t="inlineStr"/>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>TUC37-013</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>プロフィール画面</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>楽観更新</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>表示名保存(): 失敗でロールバック</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>サーバ 4xx/5xx</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>1. 表示名保存() を実行しAPIが失敗</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>楽観反映が元に戻り、inline error + toast を表示</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr"/>
-      <c r="I13" s="3" t="inlineStr"/>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>TUC37-014</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>プロフィール画面</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>エラー</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>表示名保存(): API 失敗時 inline error + toast</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>接続失敗/レート</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>1. 表示名保存() を失敗させる</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>エラー表示 + toast、状態は不整合にならない</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr"/>
-      <c r="I14" s="3" t="inlineStr"/>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>TUC37-015</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>プロフィール画面</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>受容差分</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>email は readonly</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>1. email 欄を確認</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>Auth 紐付けのため変更不可(readonly)</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr"/>
-      <c r="I15" s="3" t="inlineStr"/>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -11048,43 +11414,47 @@
       <c r="I16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>TUC37-018</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>プロフィール画面</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>状態永続</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>F5 リロードでログアウトに飛ばない</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>ログイン済</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>1. 画面で F5</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>保護ガードで維持・状態復元（URL クエリ等）</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr"/>
-      <c r="I17" s="3" t="inlineStr"/>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -11245,43 +11615,47 @@
       <c r="I2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>TUC38-002</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>ワークスペース切替画面</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>視覚忠実度</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>配色/角丸/タイポが design token 準拠</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>1. 画面を目視</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr"/>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -11327,121 +11701,133 @@
       <c r="I4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>TUC38-004</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>ワークスペース切替画面</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>空データ</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>0 件時の空状態（所属 WS 一覧）</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>/workspaces が空配列</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>1. データ0件で開く</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>空状態メッセージを表示（/undefined 参照にならない）</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>TUC38-005</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>ワークスペース切替画面</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>エラー</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>取得失敗の inline error + toast（所属 WS 一覧）</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>/workspaces が 5xx</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>1. API を でモックし開く</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>エラー表示 の inline error 表示 かつ toast 発火</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr"/>
-      <c r="I6" s="3" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>TUC38-007</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>ワークスペース切替画面</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>インタラクション</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>「WS picker」を操作すると動作する（ボタンが正しく動作するか）</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>1. 「WS picker」を選択</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>localStorage(atelier_current_workspace) 永続化（onClick/href/API が実在し、押すと副作用が起きる）</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -11487,43 +11873,47 @@
       <c r="I8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>TUC38-010</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>ワークスペース切替画面</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>状態永続</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>F5 リロードでログアウトに飛ばない</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>ログイン済</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>1. 画面で F5</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>保護ガードで維持・状態復元（URL クエリ等）</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr"/>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -11684,43 +12074,47 @@
       <c r="I2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>TUC39-002</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>プロジェクト切替画面</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>視覚忠実度</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>配色/角丸/タイポが design token 準拠</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>1. 画面を目視</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr"/>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -11766,121 +12160,133 @@
       <c r="I4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>TUC39-004</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>プロジェクト切替画面</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>空データ</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>0 件時の空状態（現在WS内プロジェクト）</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>/projects?workspace_id が空配列</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>1. データ0件で開く</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>空状態メッセージを表示（/undefined 参照にならない）</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>TUC39-005</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>プロジェクト切替画面</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>エラー</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>取得失敗の inline error + toast（現在WS内プロジェクト）</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>/projects?workspace_id が 5xx</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>1. API を でモックし開く</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>エラー表示 の inline error 表示 かつ toast 発火</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr"/>
-      <c r="I6" s="3" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>TUC39-007</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>プロジェクト切替画面</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>インタラクション</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>「Project picker」を操作すると動作する（ボタンが正しく動作するか）</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>1. 「Project picker」を選択</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>localStorage(atelier_current_project) 永続化（onClick/href/API が実在し、押すと副作用が起きる）</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -11926,43 +12332,47 @@
       <c r="I8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>TUC39-010</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>プロジェクト切替画面</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>状態永続</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>F5 リロードでログアウトに飛ばない</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>ログイン済</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>1. 画面で F5</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>保護ガードで維持・状態復元（URL クエリ等）</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr"/>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -12123,43 +12533,47 @@
       <c r="I2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>TUC40-002</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>グローバル検索画面</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>視覚忠実度</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>配色/角丸/タイポが design token 準拠</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>1. 画面を目視</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr"/>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -12248,121 +12662,133 @@
       <c r="I5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>TUC40-005</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>グローバル検索画面</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>エラー</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>取得失敗の inline error + toast（横断検索）</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>/search?q=&amp;kind= が 5xx</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>1. API を でモックし開く</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>エラー表示 の inline error 表示 かつ toast 発火</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr"/>
-      <c r="I6" s="3" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>TUC40-007</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>グローバル検索画面</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>入力フォーム</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>初期値/placeholder（キーワード）</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>1. フォームを開く</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>キーワード の初期値/placeholder が正しい</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>TUC40-008</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>グローバル検索画面</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>バリデーション</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>キーワード: 必須(空で未検索)</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>1. キーワード に不正値/未入力を入れる</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>エラー表示 かつ 送信ボタン無効</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -12451,43 +12877,47 @@
       <c r="I10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>TUC40-011</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>グローバル検索画面</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>R-T08</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>他人のデータが見えない権限 で可視性担保</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>1. 検索実行</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>他人のデータが見えない権限 内のみヒット(越境自動除外)</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr"/>
-      <c r="I11" s="3" t="inlineStr"/>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -12533,43 +12963,47 @@
       <c r="I12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>TUC40-014</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>グローバル検索画面</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>状態永続</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>F5 リロードでログアウトに飛ばない</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>ログイン済</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>1. 画面で F5</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>保護ガードで維持・状態復元（URL クエリ等）</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr"/>
-      <c r="I13" s="3" t="inlineStr"/>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -12730,43 +13164,47 @@
       <c r="I2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>SA03-002</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>ワークスペース設定画面</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>視覚忠実度</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>配色/角丸/タイポが design token 準拠</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>1. 画面を目視</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr"/>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -12812,238 +13250,262 @@
       <c r="I4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>SA03-004</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>ワークスペース設定画面</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>空データ</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>0 件時の空状態（WS 詳細）</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>/workspaces/{id} が空配列</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>1. データ0件で開く</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>空状態メッセージを表示（/undefined 参照にならない）</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>SA03-005</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>ワークスペース設定画面</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>エラー</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>取得失敗の inline error + toast（WS 詳細）</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>/workspaces/{id} が 5xx</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>1. API を でモックし開く</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>エラー表示 の inline error 表示 かつ toast 発火</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr"/>
-      <c r="I6" s="3" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>SA03-007</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>ワークスペース設定画面</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>入力フォーム</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>初期値/placeholder（表示名）</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>1. フォームを開く</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>表示名 の初期値/placeholder が正しい</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>SA03-008</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>ワークスペース設定画面</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>バリデーション</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>表示名: 必須/最大100</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>1. 表示名 に不正値/未入力を入れる</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>エラー表示 かつ 送信ボタン無効</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>SA03-009</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>ワークスペース設定画面</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>入力フォーム</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>初期値/placeholder（AI学習オプトアウト）</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>1. フォームを開く</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>AI学習オプトアウト の初期値/placeholder が正しい</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr"/>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>SA03-010</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>ワークスペース設定画面</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>インタラクション</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>「保存」を操作すると動作する（ボタンが正しく動作するか）</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>1. 「保存」をクリック</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>名称 + ai-learning（楽観）（onClick/href/API が実在し、押すと副作用が起きる）</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr"/>
-      <c r="I10" s="3" t="inlineStr"/>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -13089,43 +13551,47 @@
       <c r="I11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>SA03-012</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>ワークスペース設定画面</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>楽観更新</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>名称保存(): 失敗でロールバック</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>サーバ 4xx/5xx</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>1. 名称保存() を実行しAPIが失敗</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>楽観反映が元に戻り、inline error + toast を表示</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr"/>
-      <c r="I12" s="3" t="inlineStr"/>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -13171,43 +13637,47 @@
       <c r="I13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>SA03-014</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>ワークスペース設定画面</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>受容差分</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>WS削除ボタンは非表示</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>1. 画面を確認</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>削除 API が無いため削除ボタンを出さない(honest)</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr"/>
-      <c r="I14" s="3" t="inlineStr"/>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -13253,43 +13723,47 @@
       <c r="I15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>SA03-017</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>ワークスペース設定画面</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>状態永続</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>F5 リロードでログアウトに飛ばない</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>ログイン済</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>1. 画面で F5</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>保護ガードで維持・状態復元（URL クエリ等）</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr"/>
-      <c r="I16" s="3" t="inlineStr"/>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -13450,43 +13924,47 @@
       <c r="I2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>SB01-002</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>プロジェクト一覧画面</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>視覚忠実度</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>配色/角丸/タイポが design token 準拠</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>1. 画面を目視</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr"/>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -13575,43 +14053,47 @@
       <c r="I5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>SB01-005</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>プロジェクト一覧画面</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>エラー</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>取得失敗の inline error + toast（プロジェクト一覧(カーソル)）</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>/projects が 5xx</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>1. API を でモックし開く</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>エラー表示 の inline error 表示 かつ toast 発火</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr"/>
-      <c r="I6" s="3" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -13743,82 +14225,90 @@
       <c r="I9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>SB01-010</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>プロジェクト一覧画面</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>読み上げ対応</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>axe scan で 0 critical/serious</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>1. axe を実行</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>critical/serious 違反 0（semantic role/aria）</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr"/>
-      <c r="I10" s="3" t="inlineStr"/>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>SB01-012</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>プロジェクト一覧画面</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>状態永続</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>F5 リロードでログアウトに飛ばない</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>ログイン済</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>1. 画面で F5</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>保護ガードで維持・状態復元（URL クエリ等）</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr"/>
-      <c r="I11" s="3" t="inlineStr"/>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -13979,43 +14469,47 @@
       <c r="I2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>SB02-002</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>プロジェクトダッシュボード画面</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>視覚忠実度</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>配色/角丸/タイポが design token 準拠</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>1. 画面を目視</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr"/>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -14061,82 +14555,90 @@
       <c r="I4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>SB02-004</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>プロジェクトダッシュボード画面</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>空データ</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>0 件時の空状態（KPI ダッシュボード）</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>/projects/{id}/dashboard が空配列</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>1. データ0件で開く</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>空状態メッセージを表示（/undefined 参照にならない）</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>SB02-005</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>プロジェクトダッシュボード画面</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>エラー</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>取得失敗の inline error + toast（KPI ダッシュボード）</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>/projects/{id}/dashboard が 5xx</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>1. API を でモックし開く</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>エラー表示 の inline error 表示 かつ toast 発火</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr"/>
-      <c r="I6" s="3" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -14268,43 +14770,47 @@
       <c r="I9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>SB02-011</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>プロジェクトダッシュボード画面</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>状態永続</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>F5 リロードでログアウトに飛ばない</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>ログイン済</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>1. 画面で F5</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>保護ガードで維持・状態復元（URL クエリ等）</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr"/>
-      <c r="I10" s="3" t="inlineStr"/>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -14465,43 +14971,47 @@
       <c r="I2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>SC01-002</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>AI社員 組織図画面</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>視覚忠実度</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>配色/角丸/タイポが design token 準拠</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>1. 画面を目視</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr"/>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -14547,82 +15057,90 @@
       <c r="I4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>SC01-004</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>AI社員 組織図画面</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>空データ</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>0 件時の空状態（AI 社員一覧）</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>/ai-employees が空配列</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>1. データ0件で開く</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>空状態メッセージを表示（/undefined 参照にならない）</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>SC01-005</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>AI社員 組織図画面</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>エラー</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>取得失敗の inline error + toast（AI 社員一覧）</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>/ai-employees が 5xx</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>1. API を でモックし開く</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>エラー表示 の inline error 表示 かつ toast 発火</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr"/>
-      <c r="I6" s="3" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -14754,43 +15272,47 @@
       <c r="I9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>SC01-011</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>AI社員 組織図画面</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>状態永続</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>F5 リロードでログアウトに飛ばない</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>ログイン済</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>1. 画面で F5</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>保護ガードで維持・状態復元（URL クエリ等）</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr"/>
-      <c r="I10" s="3" t="inlineStr"/>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -14951,43 +15473,47 @@
       <c r="I2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>SC02-002</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>AI社員 編集画面</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>視覚忠実度</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>配色/角丸/タイポが design token 準拠</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>1. 画面を目視</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr"/>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -15033,82 +15559,90 @@
       <c r="I4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>SC02-004</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>AI社員 編集画面</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>空データ</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>0 件時の空状態（社員詳細）</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>/ai-employees/{id} が空配列</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>1. データ0件で開く</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>空状態メッセージを表示（/undefined 参照にならない）</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>SC02-005</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>AI社員 編集画面</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>エラー</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>取得失敗の inline error + toast（社員詳細）</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>/ai-employees/{id} が 5xx</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>1. API を でモックし開く</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>エラー表示 の inline error 表示 かつ toast 発火</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr"/>
-      <c r="I6" s="3" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -15154,43 +15688,47 @@
       <c r="I7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>SC02-008</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>AI社員 編集画面</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>バリデーション</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>display_name: 必須</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>1. display_name に不正値/未入力を入れる</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>エラー表示 かつ 送信ボタン無効</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -15322,160 +15860,176 @@
       <c r="I11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>SC02-012</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>AI社員 編集画面</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>エラー</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>保存(): API 失敗時 inline error + toast</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>接続失敗/レート</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>1. 保存() を失敗させる</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>エラー表示 + toast、状態は不整合にならない</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr"/>
-      <c r="I12" s="3" t="inlineStr"/>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>SC02-013</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>AI社員 編集画面</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>受容差分</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>role/system_prompt は非対象</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>1. フォーム確認</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>API が持つ display_name/tone のみ編集(モック準拠)</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr"/>
-      <c r="I13" s="3" t="inlineStr"/>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>SC02-014</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>AI社員 編集画面</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>読み上げ対応</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>axe scan で 0 critical/serious</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>1. axe を実行</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>critical/serious 違反 0（semantic role/aria）</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr"/>
-      <c r="I14" s="3" t="inlineStr"/>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>SC02-016</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>AI社員 編集画面</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>状態永続</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>F5 リロードでログアウトに飛ばない</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>ログイン済</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>1. 画面で F5</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>保護ガードで維持・状態復元（URL クエリ等）</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr"/>
-      <c r="I15" s="3" t="inlineStr"/>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -15636,43 +16190,47 @@
       <c r="I2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>SF01-002</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>工程ワークフロー(司令塔)画面</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>視覚忠実度</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>配色/角丸/タイポが design token 準拠</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>1. 画面を目視</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr"/>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -15718,82 +16276,90 @@
       <c r="I4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>SF01-004</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>工程ワークフロー(司令塔)画面</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>空データ</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>0 件時の空状態（工程一覧）</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>/workflow/phases?project_id が空配列</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>1. データ0件で開く</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>空状態メッセージを表示（/undefined 参照にならない）</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>SF01-005</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>工程ワークフロー(司令塔)画面</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>エラー</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>取得失敗の inline error + toast（工程一覧）</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>/workflow/phases?project_id が 5xx</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>1. API を でモックし開く</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>エラー表示 の inline error 表示 かつ toast 発火</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr"/>
-      <c r="I6" s="3" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -15882,43 +16448,47 @@
       <c r="I8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>SF01-010</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>工程ワークフロー(司令塔)画面</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>状態永続</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>F5 リロードでログアウトに飛ばない</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>ログイン済</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>1. 画面で F5</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>保護ガードで維持・状態復元（URL クエリ等）</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr"/>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -16079,43 +16649,47 @@
       <c r="I2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>SF02-002</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>フェーズ管理画面</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>視覚忠実度</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>配色/角丸/タイポが design token 準拠</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>1. 画面を目視</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr"/>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -16161,82 +16735,90 @@
       <c r="I4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>SF02-004</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>フェーズ管理画面</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>空データ</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>0 件時の空状態（工程一覧）</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>/workflow/phases?project_id が空配列</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>1. データ0件で開く</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>空状態メッセージを表示（/undefined 参照にならない）</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>SF02-005</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>フェーズ管理画面</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>エラー</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>取得失敗の inline error + toast（工程一覧）</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>/workflow/phases?project_id が 5xx</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>1. API を でモックし開く</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>エラー表示 の inline error 表示 かつ toast 発火</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr"/>
-      <c r="I6" s="3" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -16368,43 +16950,47 @@
       <c r="I9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>SF02-010</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>フェーズ管理画面</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>エラー</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>状態遷移(select): API 失敗時 inline error + toast</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>接続失敗/レート</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>1. 状態遷移(select) を失敗させる</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>エラー表示 + toast、状態は不整合にならない</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr"/>
-      <c r="I10" s="3" t="inlineStr"/>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -16450,43 +17036,47 @@
       <c r="I11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>SF02-013</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>フェーズ管理画面</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>状態永続</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>F5 リロードでログアウトに飛ばない</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>ログイン済</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>1. 画面で F5</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>保護ガードで維持・状態復元（URL クエリ等）</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr"/>
-      <c r="I12" s="3" t="inlineStr"/>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">

--- a/apps/web/.qa/テスト仕様書_クライアント版.xlsx
+++ b/apps/web/.qa/テスト仕様書_クライアント版.xlsx
@@ -1,39 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="概要" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="サインインサインアップ" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ワークスペース設定" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="プロジェクト一覧" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="プロジェクトダッシュボード" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI社員 組織図" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI社員 編集" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工程ワークフロー(司令塔)" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="フェーズ管理" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="成果物ビューア" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="モックビューア" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="タスクボード" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="タスク詳細(6タブ)" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="実行モニタ(SSE)" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="承認インボックス" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ナレッジエクスプローラ" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="昇格レビュー" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="クライアント招待管理" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="クライアントサインイン" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="クライアントプロジェクトビュー" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="議事録アップロード" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="自動スケジュール(cron)" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="通知センター" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="プロフィール" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ワークスペース切替" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="プロジェクト切替" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="グローバル検索" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="概要" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="サインインサインアップ" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ワークスペース設定" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="プロジェクト一覧" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="プロジェクトダッシュボード" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="AI社員 組織図" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="AI社員 編集" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="チャット" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="工程ワークフロー(司令塔)" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="フェーズ管理" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="成果物ビューア" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="モックビューア" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="タスクボード" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="タスク詳細(6タブ)" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="実行モニタ(SSE)" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="承認インボックス" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="ナレッジエクスプローラ" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="昇格レビュー" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="クライアント招待管理" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="クライアントサインイン" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="クライアントプロジェクトビュー" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="議事録アップロード" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="自動スケジュール(cron)" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="通知センター" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="プロフィール" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="ワークスペース切替" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="プロジェクト切替" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="グローバル検索" sheetId="28" state="visible" r:id="rId28"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -488,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -569,10 +570,10 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
@@ -582,10 +583,10 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
@@ -617,241 +618,241 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>工程ワークフロー(司令塔)画面</t>
+          <t>チャット画面</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>フェーズ管理画面</t>
+          <t>工程ワークフロー(司令塔)画面</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>成果物ビューア画面</t>
+          <t>フェーズ管理画面</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>モックビューア画面</t>
+          <t>成果物ビューア画面</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>タスクボード画面</t>
+          <t>モックビューア画面</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>タスク詳細(6タブ)画面</t>
+          <t>タスクボード画面</t>
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>実行モニタ(SSE)画面</t>
+          <t>タスク詳細(6タブ)画面</t>
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>承認インボックス画面</t>
+          <t>実行モニタ(SSE)画面</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>ナレッジエクスプローラ画面</t>
+          <t>承認インボックス画面</t>
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>昇格レビュー画面</t>
+          <t>ナレッジエクスプローラ画面</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>クライアント招待管理画面</t>
+          <t>昇格レビュー画面</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>クライアントサインイン画面</t>
+          <t>クライアント招待管理画面</t>
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>クライアントプロジェクトビュー画面</t>
+          <t>クライアントサインイン画面</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>議事録アップロード画面</t>
+          <t>クライアントプロジェクトビュー画面</t>
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>自動スケジュール(cron)画面</t>
+          <t>議事録アップロード画面</t>
         </is>
       </c>
       <c r="B25" s="3" t="n">
         <v>13</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>通知センター画面</t>
+          <t>自動スケジュール(cron)画面</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>プロフィール画面</t>
+          <t>通知センター画面</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>ワークスペース切替画面</t>
+          <t>プロフィール画面</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>プロジェクト切替画面</t>
+          <t>ワークスペース切替画面</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
@@ -864,29 +865,42 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
+          <t>プロジェクト切替画面</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
           <t>グローバル検索画面</t>
         </is>
       </c>
-      <c r="B30" s="3" t="n">
+      <c r="B31" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="C30" s="3" t="n">
+      <c r="C31" s="3" t="n">
         <v>13</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="3" t="n"/>
-      <c r="B31" s="3" t="n"/>
-      <c r="C31" s="3" t="n"/>
-    </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>完全性: 全391件 ＝ クライアント可視335件 ＋ 技術専用56件（画面で見えない裏取り=エンジニア版）</t>
-        </is>
-      </c>
+      <c r="A32" s="3" t="n"/>
       <c r="B32" s="3" t="n"/>
       <c r="C32" s="3" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>完全性: 全429件 ＝ クライアント可視369件 ＋ 技術専用60件（画面で見えない裏取り=エンジニア版）</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n"/>
+      <c r="C33" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -894,6 +908,594 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>画面</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>テスト観点</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>テスト項目</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>前提条件</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>操作手順</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>期待結果</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>SF02-001</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>フェーズ管理画面</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>画面表示</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>画面が正常表示（全 UI 要素・モック準拠）</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>1. フェーズ管理 を開く</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>SF02-002</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>フェーズ管理画面</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>視覚忠実度</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>配色/角丸/タイポが design token 準拠</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面を目視</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>SF02-003</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>フェーズ管理画面</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>データ取得</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>loading skeleton 表示（工程一覧）</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>取得未完</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>1. フェーズ管理 を開き取得完了前を観察</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>SF02-004</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>フェーズ管理画面</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>空データ</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>0 件時の空状態（工程一覧）</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>/workflow/phases?project_id が空配列</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1. データ0件で開く</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>空状態メッセージを表示（/undefined 参照にならない）</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>SF02-005</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>フェーズ管理画面</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>取得失敗の inline error + toast（工程一覧）</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>/workflow/phases?project_id が 5xx</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1. API を でモックし開く</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>エラー表示 の inline error 表示 かつ toast 発火</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>SF02-007</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>フェーズ管理画面</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>「状態 select」を操作すると動作する（ボタンが正しく動作するか）</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. 「状態 select」を変更</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>で状態遷移(done↔completed/blocked↔skipped 変換・楽観)（onClick/href/API が実在し、押すと副作用が起きる）</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>SF02-008</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>フェーズ管理画面</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>楽観更新</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>状態遷移(select): 成功で即時反映</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>対象が存在</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>1. 状態遷移(select) を実行</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>/workflow/phases/{id} 呼び出し前にUIへ楽観反映→成功で確定（別GET再取得で反映）</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>SF02-009</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>フェーズ管理画面</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>楽観更新</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>状態遷移(select): 失敗でロールバック</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>サーバ 4xx/5xx</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>1. 状態遷移(select) を実行しAPIが失敗</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>楽観反映が元に戻り、inline error + toast を表示</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>SF02-010</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>フェーズ管理画面</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>状態遷移(select): API 失敗時 inline error + toast</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>接続失敗/レート</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>1. 状態遷移(select) を失敗させる</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>エラー表示 + toast、状態は不整合にならない</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>SF02-011</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>フェーズ管理画面</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>読み上げ対応</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>axe scan で 0 critical/serious</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>1. axe を実行</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>critical/serious 違反 0（semantic role/aria）</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>SF02-013</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>フェーズ管理画面</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>状態永続</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>F5 リロードでログアウトに飛ばない</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>ログイン済</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面で F5</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>保護ガードで維持・状態復元（URL クエリ等）</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>SF02-014</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>フェーズ管理画面</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>到達性</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1868,7 +2470,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2542,13 +3144,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3125,12 +3727,227 @@
       </c>
       <c r="I13" s="4" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>SI01-101</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>タスクボード画面</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>画面表示</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>モック準拠の全領域 (選択バー/ツールバー/機能別グループ×6レーン/凡例一致レーン名)</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>design-audit R5</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>1. /tasks を開く</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>選択バー(選択時)・表示/分類/絞込ツールバー・グループごとの6レーンが表示。レーン名=凡例と同一語 (旧: バックログ/実行可/進行中/ブロックの不一致を修正)</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>SI01-103</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>タスクボード画面</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>タスクを追加モーダル（ボタンが正しく動作するか）</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>1. タスクを追加→入力→作成</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>実 /tasks → 新分類グループ (requirements) が即出現</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>SI01-104</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>タスクボード画面</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>かんばん/リスト切替・分類切替 (機能別/担当AI別/フェーズ別/なし)・絞り込み</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>1. 各トグルを操作</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>リスト=テーブル表示・分類ごとに再グルーピング・絞込で実フィルタ</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>SI01-105</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>タスクボード画面</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>表示</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>カードに見積時間 (未見積)・ID・担当・blocked_reason・dispatch 状態</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>1. 各カード確認</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>実フィールドを表示。捏造値なし</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>SI01-106</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>タスクボード画面</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>受容差分</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>モックの「依存グラフ」ビューは非表示</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>1. 表示トグル確認</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>タスク依存 API が無いため出さない (GAP-006 起票)</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4019,7 +4836,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4505,7 +5322,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5136,7 +5953,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5595,7 +6412,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6269,7 +7086,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7023,637 +7840,6 @@
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="7" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>画面</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>テスト観点</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>テスト項目</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>前提条件</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>操作手順</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>期待結果</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>結果</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>SL02-001</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>クライアントサインイン画面</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>画面表示</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>画面が正常表示（全 UI 要素・モック準拠）</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>1. クライアントサインイン を開く</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I2" s="4" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>SL02-002</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>クライアントサインイン画面</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>視覚忠実度</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>配色/角丸/タイポが design token 準拠</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>1. 画面を目視</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>SL02-003</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>クライアントサインイン画面</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>入力フォーム</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>初期値/placeholder（招待トークン）</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>1. フォームを開く</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>招待トークン の初期値/placeholder が正しい</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>SL02-004</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>クライアントサインイン画面</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>バリデーション</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>招待トークン: 必須/最小10</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>1. 招待トークン に不正値/未入力を入れる</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>エラー表示 かつ 送信ボタン無効</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>SL02-005</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>クライアントサインイン画面</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>入力フォーム</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>初期値/placeholder（表示名）</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>1. フォームを開く</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>表示名 の初期値/placeholder が正しい</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>SL02-006</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>クライアントサインイン画面</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>バリデーション</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>表示名: 任意</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>1. 表示名 に不正値/未入力を入れる</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>エラー表示 かつ 送信ボタン無効</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>SL02-007</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>クライアントサインイン画面</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>インタラクション</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>「プロジェクトを開く」を操作すると動作する（ボタンが正しく動作するか）</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>1. 「プロジェクトを開く」をクリック</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>signin→client_portal cookie→/client/s_l03 遷移（onClick/href/API が実在し、押すと副作用が起きる）</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>SL02-008</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>クライアントサインイン画面</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>サインイン: 送信→反映</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>必須入力済</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>1. サインイン を実行</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>/client/auth/signin 呼び出し→成功表示→別GET/DBに反映</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>SL02-009</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>クライアントサインイン画面</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>エラー</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>サインイン: API 失敗時 inline error + toast</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>接続失敗/レート</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>1. サインイン を失敗させる</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>エラー表示 + toast、状態は不整合にならない</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>SL02-010</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>クライアントサインイン画面</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>認証</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>invalid/410 expired 文言化</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>無効/期限切れトークン</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>1. 無効トークンで送信</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>→『招待トークンが無効』/410→『有効期限切れ』</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>SL02-011</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>クライアントサインイン画面</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>読み上げ対応</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>axe scan で 0 critical/serious</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>1. axe を実行</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>critical/serious 違反 0（semantic role/aria）</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>SL02-013</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>クライアントサインイン画面</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>状態永続</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>F5 リロードでログアウトに飛ばない</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>ログイン済</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>1. 画面で F5</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>保護ガードで維持・状態復元（URL クエリ等）</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I13" s="4" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>SL02-014</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>クライアントサインイン画面</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>到達性</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I14" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8383,6 +8569,637 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>画面</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>テスト観点</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>テスト項目</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>前提条件</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>操作手順</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>期待結果</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>SL02-001</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>クライアントサインイン画面</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>画面表示</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>画面が正常表示（全 UI 要素・モック準拠）</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>1. クライアントサインイン を開く</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>SL02-002</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>クライアントサインイン画面</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>視覚忠実度</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>配色/角丸/タイポが design token 準拠</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面を目視</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>SL02-003</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>クライアントサインイン画面</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>入力フォーム</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>初期値/placeholder（招待トークン）</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>1. フォームを開く</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>招待トークン の初期値/placeholder が正しい</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>SL02-004</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>クライアントサインイン画面</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>バリデーション</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>招待トークン: 必須/最小10</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1. 招待トークン に不正値/未入力を入れる</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>エラー表示 かつ 送信ボタン無効</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>SL02-005</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>クライアントサインイン画面</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>入力フォーム</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>初期値/placeholder（表示名）</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1. フォームを開く</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>表示名 の初期値/placeholder が正しい</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>SL02-006</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>クライアントサインイン画面</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>バリデーション</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>表示名: 任意</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. 表示名 に不正値/未入力を入れる</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>エラー表示 かつ 送信ボタン無効</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>SL02-007</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>クライアントサインイン画面</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>「プロジェクトを開く」を操作すると動作する（ボタンが正しく動作するか）</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>1. 「プロジェクトを開く」をクリック</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>signin→client_portal cookie→/client/s_l03 遷移（onClick/href/API が実在し、押すと副作用が起きる）</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>SL02-008</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>クライアントサインイン画面</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>サインイン: 送信→反映</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>必須入力済</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>1. サインイン を実行</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>/client/auth/signin 呼び出し→成功表示→別GET/DBに反映</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>SL02-009</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>クライアントサインイン画面</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>サインイン: API 失敗時 inline error + toast</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>接続失敗/レート</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>1. サインイン を失敗させる</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>エラー表示 + toast、状態は不整合にならない</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>SL02-010</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>クライアントサインイン画面</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>認証</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>invalid/410 expired 文言化</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>無効/期限切れトークン</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>1. 無効トークンで送信</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>→『招待トークンが無効』/410→『有効期限切れ』</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>SL02-011</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>クライアントサインイン画面</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>読み上げ対応</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>axe scan で 0 critical/serious</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>1. axe を実行</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>critical/serious 違反 0（semantic role/aria）</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>SL02-013</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>クライアントサインイン画面</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>状態永続</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>F5 リロードでログアウトに飛ばない</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>ログイン済</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面で F5</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>保護ガードで維持・状態復元（URL クエリ等）</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>SL02-014</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>クライアントサインイン画面</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>到達性</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -8873,609 +9690,6 @@
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="7" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>画面</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>テスト観点</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>テスト項目</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>前提条件</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>操作手順</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>期待結果</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>結果</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>SM01-001</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>議事録アップロード画面</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>画面表示</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>画面が正常表示（全 UI 要素・モック準拠）</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>1. 議事録アップロード を開く</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I2" s="4" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>SM01-002</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>議事録アップロード画面</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>視覚忠実度</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>配色/角丸/タイポが design token 準拠</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>1. 画面を目視</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>SM01-003</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>議事録アップロード画面</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>データ取得</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>loading skeleton 表示（状態ポーリング）</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>取得未完</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>1. 議事録アップロード を開き取得完了前を観察</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>SM01-004</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>議事録アップロード画面</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>空データ</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>0 件時の空状態（状態ポーリング）</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>/meetings/{id} が空配列</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>1. データ0件で開く</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>空状態メッセージを表示（/undefined 参照にならない）</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>SM01-005</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>議事録アップロード画面</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>エラー</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>取得失敗の inline error + toast（状態ポーリング）</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>/meetings/{id} が 5xx</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>1. API を でモックし開く</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>エラー表示 の inline error 表示 かつ toast 発火</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr"/>
-      <c r="I6" s="3" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>SM01-007</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>議事録アップロード画面</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>インタラクション</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>「ファイル選択」を操作すると動作する（ボタンが正しく動作するか）</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>1. 「ファイル選択」を選択</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>署名URL発行→実PUT→登録→transcribe キュー→polling→本文表示（onClick/href/API が実在し、押すと副作用が起きる）</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>SM01-008</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>議事録アップロード画面</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>アップロード→transcription: 送信→反映</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>必須入力済</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>1. アップロード→transcription を実行</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>upload-url→→ /meetings→transcribe→poll→transcript-url 呼び出し→成功表示→別GET/DBに反映</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>SM01-009</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>議事録アップロード画面</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>エラー</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>アップロード→transcription: API 失敗時 inline error + toast</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>接続失敗/レート</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>1. アップロード→transcription を失敗させる</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>エラー表示 + toast、状態は不整合にならない</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>SM01-010</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>議事録アップロード画面</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>G3実副作用</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>実 storage/Whisper 副作用(BLOCKED)</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>実DB/実storage</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>1. 実ファイルをアップロード</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>storage にオブジェクト作成・parse_result_path 生成を実API照会で確認</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr"/>
-      <c r="I10" s="3" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>SM01-011</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>議事録アップロード画面</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>マルチターン</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>queued→parsing→done の状態継続</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>アップロード後</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>1. 完了までポーリングを観察</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>parsed_at/parse_error まで状態が継続遷移し本文取得</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr"/>
-      <c r="I11" s="3" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>SM01-012</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>議事録アップロード画面</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>読み上げ対応</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>axe scan で 0 critical/serious</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>1. axe を実行</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>critical/serious 違反 0（semantic role/aria）</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>SM01-014</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>議事録アップロード画面</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>状態永続</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>F5 リロードでログアウトに飛ばない</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>ログイン済</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>1. 画面で F5</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>保護ガードで維持・状態復元（URL クエリ等）</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I13" s="4" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>SM01-015</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>議事録アップロード画面</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>到達性</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I14" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9552,12 +9766,12 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>SO01-001</t>
+          <t>SM01-001</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>自動スケジュール(cron)画面</t>
+          <t>議事録アップロード画面</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -9577,7 +9791,7 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>1. 自動スケジュール(cron) を開く</t>
+          <t>1. 議事録アップロード を開く</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
@@ -9595,12 +9809,12 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>SO01-002</t>
+          <t>SM01-002</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>自動スケジュール(cron)画面</t>
+          <t>議事録アップロード画面</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -9636,143 +9850,131 @@
       <c r="I3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>SO01-003</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>自動スケジュール(cron)画面</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>SM01-003</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>議事録アップロード画面</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>データ取得</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>loading skeleton 表示（スケジュール一覧）</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>loading skeleton 表示（状態ポーリング）</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>取得未完</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>1. 自動スケジュール(cron) を開き取得完了前を観察</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>1. 議事録アップロード を開き取得完了前を観察</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr"/>
+      <c r="I4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>SO01-004</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>自動スケジュール(cron)画面</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>SM01-004</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>議事録アップロード画面</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>空データ</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>0 件時の空状態（スケジュール一覧）</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>/cron-schedules?project_id が空配列</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>0 件時の空状態（状態ポーリング）</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>/meetings/{id} が空配列</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>1. データ0件で開く</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>空状態メッセージを表示（/undefined 参照にならない）</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>SO01-005</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>自動スケジュール(cron)画面</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>SM01-005</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>議事録アップロード画面</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>エラー</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>取得失敗の inline error + toast（スケジュール一覧）</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>/cron-schedules?project_id が 5xx</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>取得失敗の inline error + toast（状態ポーリング）</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>/meetings/{id} が 5xx</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>1. API を でモックし開く</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>エラー表示 の inline error 表示 かつ toast 発火</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr"/>
+      <c r="I6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>SO01-007</t>
+          <t>SM01-007</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>自動スケジュール(cron)画面</t>
+          <t>議事録アップロード画面</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -9782,7 +9984,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>「有効/無効トグル」を操作すると動作する（ボタンが正しく動作するか）</t>
+          <t>「ファイル選択」を操作すると動作する（ボタンが正しく動作するか）</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -9792,12 +9994,12 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>1. 「有効/無効トグル」をクリック</t>
+          <t>1. 「ファイル選択」を選択</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>enabled(楽観トグル)（onClick/href/API が実在し、押すと副作用が起きる）</t>
+          <t>署名URL発行→実PUT→登録→transcribe キュー→polling→本文表示（onClick/href/API が実在し、押すと副作用が起きる）</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -9808,186 +10010,170 @@
       <c r="I7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>SO01-008</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>自動スケジュール(cron)画面</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>楽観更新</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>有効トグル: 成功で即時反映</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>対象が存在</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>1. 有効トグル を実行</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>/cron-schedules/{id} 呼び出し前にUIへ楽観反映→成功で確定（別GET再取得で反映）</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="inlineStr"/>
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>SM01-008</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>議事録アップロード画面</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>アップロード→transcription: 送信→反映</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>必須入力済</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>1. アップロード→transcription を実行</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>upload-url→→ /meetings→transcribe→poll→transcript-url 呼び出し→成功表示→別GET/DBに反映</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr"/>
+      <c r="I8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>SO01-009</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>自動スケジュール(cron)画面</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>楽観更新</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>有効トグル: 失敗でロールバック</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>サーバ 4xx/5xx</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>1. 有効トグル を実行しAPIが失敗</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>楽観反映が元に戻り、inline error + toast を表示</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr"/>
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>SM01-009</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>議事録アップロード画面</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>アップロード→transcription: API 失敗時 inline error + toast</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>接続失敗/レート</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>1. アップロード→transcription を失敗させる</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>エラー表示 + toast、状態は不整合にならない</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>SO01-010</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>自動スケジュール(cron)画面</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>エラー</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>有効トグル: API 失敗時 inline error + toast</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>接続失敗/レート</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>1. 有効トグル を失敗させる</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>エラー表示 + toast、状態は不整合にならない</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr"/>
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>SM01-010</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>議事録アップロード画面</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>G3実副作用</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>実 storage/Whisper 副作用(BLOCKED)</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>実DB/実storage</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>1. 実ファイルをアップロード</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>storage にオブジェクト作成・parse_result_path 生成を実API照会で確認</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr"/>
+      <c r="I10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>SO01-011</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>自動スケジュール(cron)画面</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>受容差分</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>即時実行ボタンは非表示</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>1. 一覧確認</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>run-now API 無しのため列非表示(honest)</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr"/>
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>SM01-011</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>議事録アップロード画面</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>マルチターン</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>queued→parsing→done の状態継続</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>アップロード後</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>1. 完了までポーリングを観察</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>parsed_at/parse_error まで状態が継続遷移し本文取得</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr"/>
+      <c r="I11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>SO01-012</t>
+          <t>SM01-012</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>自動スケジュール(cron)画面</t>
+          <t>議事録アップロード画面</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -10025,12 +10211,12 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>SO01-014</t>
+          <t>SM01-014</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>自動スケジュール(cron)画面</t>
+          <t>議事録アップロード画面</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -10068,12 +10254,12 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>SO01-015</t>
+          <t>SM01-015</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>自動スケジュール(cron)画面</t>
+          <t>議事録アップロード画面</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -10114,6 +10300,637 @@
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>画面</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>テスト観点</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>テスト項目</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>前提条件</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>操作手順</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>期待結果</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>SO01-001</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)画面</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>画面表示</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>画面が正常表示（全 UI 要素・モック準拠）</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>1. 自動スケジュール(cron) を開く</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>SO01-002</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)画面</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>視覚忠実度</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>配色/角丸/タイポが design token 準拠</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面を目視</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>SO01-003</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)画面</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>データ取得</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>loading skeleton 表示（スケジュール一覧）</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>取得未完</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>1. 自動スケジュール(cron) を開き取得完了前を観察</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>SO01-004</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)画面</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>空データ</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>0 件時の空状態（スケジュール一覧）</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>/cron-schedules?project_id が空配列</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1. データ0件で開く</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>空状態メッセージを表示（/undefined 参照にならない）</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>SO01-005</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)画面</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>取得失敗の inline error + toast（スケジュール一覧）</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>/cron-schedules?project_id が 5xx</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1. API を でモックし開く</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>エラー表示 の inline error 表示 かつ toast 発火</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>SO01-007</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)画面</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>「有効/無効トグル」を操作すると動作する（ボタンが正しく動作するか）</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. 「有効/無効トグル」をクリック</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>enabled(楽観トグル)（onClick/href/API が実在し、押すと副作用が起きる）</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>SO01-008</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)画面</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>楽観更新</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>有効トグル: 成功で即時反映</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>対象が存在</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>1. 有効トグル を実行</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>/cron-schedules/{id} 呼び出し前にUIへ楽観反映→成功で確定（別GET再取得で反映）</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>SO01-009</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)画面</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>楽観更新</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>有効トグル: 失敗でロールバック</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>サーバ 4xx/5xx</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>1. 有効トグル を実行しAPIが失敗</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>楽観反映が元に戻り、inline error + toast を表示</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>SO01-010</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)画面</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>有効トグル: API 失敗時 inline error + toast</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>接続失敗/レート</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>1. 有効トグル を失敗させる</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>エラー表示 + toast、状態は不整合にならない</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>SO01-011</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)画面</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>受容差分</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>即時実行ボタンは非表示</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>1. 一覧確認</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>run-now API 無しのため列非表示(honest)</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>SO01-012</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)画面</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>読み上げ対応</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>axe scan で 0 critical/serious</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>1. axe を実行</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>critical/serious 違反 0（semantic role/aria）</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>SO01-014</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)画面</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>状態永続</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>F5 リロードでログアウトに飛ばない</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>ログイン済</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面で F5</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>保護ガードで維持・状態復元（URL クエリ等）</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>SO01-015</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)画面</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>到達性</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10701,7 +11518,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11498,465 +12315,6 @@
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="7" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>画面</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>テスト観点</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>テスト項目</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>前提条件</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>操作手順</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>期待結果</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>結果</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-001</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替画面</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>画面表示</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>画面が正常表示（全 UI 要素・モック準拠）</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>1. ワークスペース切替 を開く</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I2" s="4" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-002</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替画面</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>視覚忠実度</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>配色/角丸/タイポが design token 準拠</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>1. 画面を目視</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-003</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替画面</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>データ取得</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>loading skeleton 表示（所属 WS 一覧）</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>取得未完</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>1. ワークスペース切替 を開き取得完了前を観察</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-004</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替画面</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>空データ</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>0 件時の空状態（所属 WS 一覧）</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>/workspaces が空配列</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>1. データ0件で開く</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>空状態メッセージを表示（/undefined 参照にならない）</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-005</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替画面</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>エラー</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>取得失敗の inline error + toast（所属 WS 一覧）</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>/workspaces が 5xx</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>1. API を でモックし開く</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>エラー表示 の inline error 表示 かつ toast 発火</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-007</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替画面</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>インタラクション</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>「WS picker」を操作すると動作する（ボタンが正しく動作するか）</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>1. 「WS picker」を選択</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>localStorage(atelier_current_workspace) 永続化（onClick/href/API が実在し、押すと副作用が起きる）</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-008</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替画面</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>読み上げ対応</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>axe scan で 0 critical/serious</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>1. axe を実行</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>critical/serious 違反 0（semantic role/aria）</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-010</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替画面</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>状態永続</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>F5 リロードでログアウトに飛ばない</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>ログイン済</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>1. 画面で F5</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>保護ガードで維持・状態復元（URL クエリ等）</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-011</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替画面</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>到達性</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12033,12 +12391,12 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>TUC39-001</t>
+          <t>TUC38-001</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替画面</t>
+          <t>ワークスペース切替画面</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -12058,7 +12416,7 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>1. プロジェクト切替 を開く</t>
+          <t>1. ワークスペース切替 を開く</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
@@ -12076,12 +12434,12 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>TUC39-002</t>
+          <t>TUC38-002</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替画面</t>
+          <t>ワークスペース切替画面</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -12119,12 +12477,12 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>TUC39-003</t>
+          <t>TUC38-003</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替画面</t>
+          <t>ワークスペース切替画面</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -12134,7 +12492,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>loading skeleton 表示（現在WS内プロジェクト）</t>
+          <t>loading skeleton 表示（所属 WS 一覧）</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -12144,7 +12502,7 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>1. プロジェクト切替 を開き取得完了前を観察</t>
+          <t>1. ワークスペース切替 を開き取得完了前を観察</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
@@ -12162,12 +12520,12 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>TUC39-004</t>
+          <t>TUC38-004</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替画面</t>
+          <t>ワークスペース切替画面</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -12177,12 +12535,12 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>0 件時の空状態（現在WS内プロジェクト）</t>
+          <t>0 件時の空状態（所属 WS 一覧）</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>/projects?workspace_id が空配列</t>
+          <t>/workspaces が空配列</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -12205,12 +12563,12 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>TUC39-005</t>
+          <t>TUC38-005</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替画面</t>
+          <t>ワークスペース切替画面</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -12220,12 +12578,12 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>取得失敗の inline error + toast（現在WS内プロジェクト）</t>
+          <t>取得失敗の inline error + toast（所属 WS 一覧）</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>/projects?workspace_id が 5xx</t>
+          <t>/workspaces が 5xx</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -12248,12 +12606,12 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>TUC39-007</t>
+          <t>TUC38-007</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替画面</t>
+          <t>ワークスペース切替画面</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -12263,7 +12621,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>「Project picker」を操作すると動作する（ボタンが正しく動作するか）</t>
+          <t>「WS picker」を操作すると動作する（ボタンが正しく動作するか）</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -12273,12 +12631,12 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>1. 「Project picker」を選択</t>
+          <t>1. 「WS picker」を選択</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>localStorage(atelier_current_project) 永続化（onClick/href/API が実在し、押すと副作用が起きる）</t>
+          <t>localStorage(atelier_current_workspace) 永続化（onClick/href/API が実在し、押すと副作用が起きる）</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -12291,12 +12649,12 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>TUC39-008</t>
+          <t>TUC38-008</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替画面</t>
+          <t>ワークスペース切替画面</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -12334,12 +12692,12 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>TUC39-010</t>
+          <t>TUC38-010</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替画面</t>
+          <t>ワークスペース切替画面</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -12377,12 +12735,12 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>TUC39-011</t>
+          <t>TUC38-011</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替画面</t>
+          <t>ワークスペース切替画面</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -12423,6 +12781,465 @@
 </file>
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>画面</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>テスト観点</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>テスト項目</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>前提条件</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>操作手順</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>期待結果</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-001</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替画面</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>画面表示</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>画面が正常表示（全 UI 要素・モック準拠）</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>1. プロジェクト切替 を開く</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-002</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替画面</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>視覚忠実度</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>配色/角丸/タイポが design token 準拠</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面を目視</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-003</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替画面</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>データ取得</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>loading skeleton 表示（現在WS内プロジェクト）</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>取得未完</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>1. プロジェクト切替 を開き取得完了前を観察</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-004</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替画面</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>空データ</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>0 件時の空状態（現在WS内プロジェクト）</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>/projects?workspace_id が空配列</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1. データ0件で開く</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>空状態メッセージを表示（/undefined 参照にならない）</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-005</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替画面</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>取得失敗の inline error + toast（現在WS内プロジェクト）</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>/projects?workspace_id が 5xx</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1. API を でモックし開く</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>エラー表示 の inline error 表示 かつ toast 発火</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-007</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替画面</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>「Project picker」を操作すると動作する（ボタンが正しく動作するか）</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. 「Project picker」を選択</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>localStorage(atelier_current_project) 永続化（onClick/href/API が実在し、押すと副作用が起きる）</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-008</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替画面</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>読み上げ対応</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>axe scan で 0 critical/serious</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>1. axe を実行</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>critical/serious 違反 0（semantic role/aria）</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-010</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替画面</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>状態永続</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>F5 リロードでログアウトに飛ばない</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>ログイン済</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面で F5</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>保護ガードで維持・状態復元（URL クエリ等）</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-011</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替画面</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>到達性</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13819,7 +14636,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -14353,6 +15170,178 @@
       </c>
       <c r="I12" s="4" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>SB01-102</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト一覧画面</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>新規プロジェクト作成モーダル（ボタンが正しく動作するか）</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>1. 新規プロジェクト→名前入力→作成</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>実 /projects → 一覧に即出現・工程 seed 済 (工程1/9・たった今更新)</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>SB01-103</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト一覧画面</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>検索フィルタ + すべて/進行中/アーカイブ タブ（ボタンが正しく動作するか）</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>2件以上</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>1. 「EC」を入力 2. タブ切替</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>名前/クライアント/フェーズで実絞込・クリア×ボタン表示</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>SB01-104</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト一覧画面</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>カードクリック → ダッシュボード遷移</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>1. カードをクリック</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>/projects/dashboard?project=&lt;id&gt; へ遷移 (project 文脈維持)</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>SB01-105</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト一覧画面</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>表示</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>更新時刻がモック準拠の相対表記</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>1. カード右下を確認</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>「9 時間前更新」「たった今更新」(旧: 絶対日付)</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14364,7 +15353,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -14854,6 +15843,264 @@
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>SB02-101</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクトダッシュボード画面</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>画面表示</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>モック準拠の全領域再構築 (kicker+h1+サブタイトル / KPI4枚 / 工程+リンク / 活動タイムライン / 右レール3カード)</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>design-audit R3</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>1. /projects/dashboard を開く</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>モック S-B02-dashboard.html の全領域が実データで表示</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>SB02-103</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクトダッシュボード画面</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>承認リクエストの「承認」ボタン（ボタンが正しく動作するか）</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>pending 承認有</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>1. 承認をクリック</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>/approval-inbox/{id}/decide が発火し DB status=approved・カード消滅・INBOX KPI が 1→0 に即時反映</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>SB02-104</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクトダッシュボード画面</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>「工程画面で確定事項・成果物を見る」「フェーズ管理」「チャットで依頼」「成果物」各リンク（ボタンが正しく動作するか）</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>1. 各リンクを確認</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>?project= 付きの実ルートへの href が存在 (画面の導線が切れていないか無し)</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>SB02-105</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクトダッシュボード画面</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>表示</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>最新の活動 = decisions/outputs/threads/工程完了 の実タイムスタンプ降順合成</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>実データ有</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>1. タイムラインを確認</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>実データ 8 件が時刻降順・社員アバター付きで表示。捏造行なし</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>SB02-106</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクトダッシュボード画面</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>スマホ・タブレットでも崩れない</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>390/768/1440 で崩れない</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>1. 3 幅で撮影</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>単一カラム積層・横スクロールなし (工程のみ意図的横スクロール)</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>SB02-107</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクトダッシュボード画面</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>受容差分</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>モックの「未解決コメント」KPI は「確定事項」に置換</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>1. KPI 4 枚目を確認</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト横断コメント API 不在のため実データ KPI に置換 (GAP-005 起票)</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -16085,6 +17332,891 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>画面</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>テスト観点</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>テスト項目</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>前提条件</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>操作手順</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>期待結果</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>SE01-001</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>チャット画面</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>画面表示</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>3ペイン構成が正常表示（モック S-E01-thread.html 準拠: 左260px スレッド/中央チャット/右340px コンテキスト）</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>ログイン済+スレッド有</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>1. /chat を開く</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>3ペインが描画され、モックの主要領域(スレッド検索/新規スレッド/工程グルーピング/工程文脈バー/社員ヘッダー/コンポーザ/右タブ)が全て存在</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>SE01-002</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>チャット画面</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>視覚忠実度</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>配色/角丸/タイポが design token 準拠</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面を目視</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>--color-*/--rounded-* トークン準拠・社員カラーはモック avatar-* 準拠</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>SE01-003</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>チャット画面</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>データ取得</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>スレッド一覧が実 API ( /chat/threads?project_id) から描画</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>1. 開いて一覧を確認</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>実スレッドが工程グルーピング(現在→完了→横断)で表示・message_count/相対時刻付き</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>SE01-004</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>チャット画面</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>空データ</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>スレッド0件時の空状態</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>スレッド0件</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>1. 空プロジェクトで開く</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>「スレッドがありません…」の empty state ( にならない)</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>SE01-005</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>チャット画面</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>送信失敗時のエラーバナー(単一・dismiss可)</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>LLM 未設定 or API 5xx</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1. メッセージ送信</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>コンポーザ直上に エラー表示 バナー1箇所のみ・✕で閉じる・スレッド切替でリセット</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>SE01-006</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>チャット画面</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>スレッド検索フィルタ（ボタンが正しく動作するか）</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>スレッド複数</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. 検索欄に「競合」入力</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>タイトル/社員名/最終メッセージで絞り込まれる</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>SE01-007</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>チャット画面</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>スレッド切替・新規スレッド作成（ボタンが正しく動作するか）</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>1. 別スレッドをクリック 2. 新規スレッドで作成</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>メッセージが切替わる/ /chat/threads (phase_id 任意) で作成され選択される</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>SE01-008</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>チャット画面</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>ペイン開閉トグル（ボタンが正しく動作するか）</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>1. 左右トグルを各クリック</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>左ペイン/右ペインが開閉し grid が追従・aria-pressed 反映</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>SE01-009</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>チャット画面</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>メッセージ送信 (Enter=送信 / Shift+Enter=改行 / IME 変換中は送信しない)</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>スレッド選択済</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>1. 入力して Enter</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>user バブル即時表示→SSE 応答 (LLM 無環境では誠実なエラー表示)・IME 変換確定 Enter で誤送信しない</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>SE01-010</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>チャット画面</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>@メンション ピッカー（ボタンが正しく動作するか）</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>AI 社員複数</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>1. @メンション をクリック 2. 社員を選択</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>実 AI 社員一覧(対話相手は除外)が出て、カーソル位置に「@名前 」が挿入される</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>SE01-011</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>チャット画面</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>ナレッジ参照ピッカー（ボタンが正しく動作するか）</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>1. ナレッジ参照をクリック</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>実ナレッジ一覧から選択で「[ナレッジ: title] 」挿入。0件時は「まだありません+自動RAGは常時有効」の誠実表示</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>SE01-012</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>チャット画面</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>死に要素ゼロ</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>コンポーザに非機能ボタンが存在しない</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>1. コンポーザの全ボタンを列挙</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>添付・/コマンドのボタンは**描画されない**(gap tracker 起票済)。表示される全ボタンが機能する</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>SE01-013</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>チャット画面</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>表示</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>tool ロールメッセージのツールカード描画</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>tool メッセージ有</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>1. 該当スレッドを開く</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>monospace ツール名ヘッダ+本文カード (モック .tool-card 準拠)</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>SE01-014</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>チャット画面</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>表示</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>工程文脈バー (現在の工程・Stage n/9・工程画面リンク)</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>1. ヘッダーを確認 2. リンクをクリック</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>実 current_phase を表示し /workflow?project= へ遷移</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>SE01-015</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>チャット画面</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>表示</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>右ペイン: 主力決定/コンテキスト/参照タブ</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>decisions 有</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>1. 各タブをクリック</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>実 /decisions の確定カード(反映先付)・F-CTX01 実測値(SSE context)・実 /knowledge 一覧</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>SE01-016</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>チャット画面</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>履歴</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>リロードで会話が消えない (既存メッセージロード)</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>メッセージ有</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>1. F5</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>過去メッセージが created_at 付きで再表示</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>SE01-017</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>チャット画面</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>スマホ・タブレットでも崩れない</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>390/768/1440 で崩れない・モバイルは一覧⇄チャット切替</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>1. 各幅で開く 2. モバイルで戻るボタン</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>横スクロール無し・モバイルで戻る→一覧表示・右ペインは重ね表示トグル</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>SE01-018</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>チャット画面</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>読み上げ対応</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>axe 0 critical/serious・log role/aria-live/label 契約</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>1. axe 実行</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>違反0・role=log aria-live=polite・「メッセージを入力」label</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>SE01-020</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>チャット画面</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>状態永続</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>?thread= URL で直接スレッドを開ける</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>1. /chat?thread=&lt;id&gt; を開く</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>該当スレッドが選択状態で開く</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -16536,592 +18668,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="7" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>画面</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>テスト観点</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>テスト項目</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>前提条件</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>操作手順</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>期待結果</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>結果</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>SF02-001</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>フェーズ管理画面</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>画面表示</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>画面が正常表示（全 UI 要素・モック準拠）</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>1. フェーズ管理 を開く</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I2" s="4" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>SF02-002</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>フェーズ管理画面</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>視覚忠実度</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>配色/角丸/タイポが design token 準拠</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>1. 画面を目視</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>SF02-003</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>フェーズ管理画面</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>データ取得</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>loading skeleton 表示（工程一覧）</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>取得未完</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>1. フェーズ管理 を開き取得完了前を観察</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>SF02-004</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>フェーズ管理画面</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>空データ</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>0 件時の空状態（工程一覧）</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>/workflow/phases?project_id が空配列</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>1. データ0件で開く</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>空状態メッセージを表示（/undefined 参照にならない）</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>SF02-005</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>フェーズ管理画面</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>エラー</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>取得失敗の inline error + toast（工程一覧）</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>/workflow/phases?project_id が 5xx</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>1. API を でモックし開く</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>エラー表示 の inline error 表示 かつ toast 発火</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>SF02-007</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>フェーズ管理画面</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>インタラクション</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>「状態 select」を操作すると動作する（ボタンが正しく動作するか）</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>1. 「状態 select」を変更</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>で状態遷移(done↔completed/blocked↔skipped 変換・楽観)（onClick/href/API が実在し、押すと副作用が起きる）</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>SF02-008</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>フェーズ管理画面</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>楽観更新</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>状態遷移(select): 成功で即時反映</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>対象が存在</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>1. 状態遷移(select) を実行</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>/workflow/phases/{id} 呼び出し前にUIへ楽観反映→成功で確定（別GET再取得で反映）</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>SF02-009</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>フェーズ管理画面</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>楽観更新</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>状態遷移(select): 失敗でロールバック</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>サーバ 4xx/5xx</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>1. 状態遷移(select) を実行しAPIが失敗</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>楽観反映が元に戻り、inline error + toast を表示</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>SF02-010</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>フェーズ管理画面</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>エラー</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>状態遷移(select): API 失敗時 inline error + toast</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>接続失敗/レート</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>1. 状態遷移(select) を失敗させる</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>エラー表示 + toast、状態は不整合にならない</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>SF02-011</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>フェーズ管理画面</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>読み上げ対応</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>axe scan で 0 critical/serious</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>1. axe を実行</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>critical/serious 違反 0（semantic role/aria）</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>SF02-013</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>フェーズ管理画面</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>状態永続</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>F5 リロードでログアウトに飛ばない</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>ログイン済</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>1. 画面で F5</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>保護ガードで維持・状態復元（URL クエリ等）</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>SF02-014</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>フェーズ管理画面</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>到達性</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I13" s="4" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/apps/web/.qa/テスト仕様書_クライアント版.xlsx
+++ b/apps/web/.qa/テスト仕様書_クライアント版.xlsx
@@ -12,29 +12,30 @@
     <sheet name="ワークスペース設定" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="プロジェクト一覧" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="プロジェクトダッシュボード" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="AI社員 組織図" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="AI社員 編集" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="チャット" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="工程ワークフロー(司令塔)" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="フェーズ管理" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="成果物ビューア" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="モックビューア" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="タスクボード" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="タスク詳細(6タブ)" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="実行モニタ(SSE)" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="承認インボックス" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="ナレッジエクスプローラ" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="昇格レビュー" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="クライアント招待管理" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="クライアントサインイン" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="クライアントプロジェクトビュー" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="議事録アップロード" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="自動スケジュール(cron)" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="通知センター" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="プロフィール" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="ワークスペース切替" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="プロジェクト切替" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="グローバル検索" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="プロジェクト設定" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="AI社員 組織図" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="AI社員 編集" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="チャット" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="工程ワークフロー(司令塔)" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="フェーズ管理" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="成果物ビューア" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="モックビューア" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="タスクボード" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="タスク詳細(6タブ)" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="実行モニタ(SSE)" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="承認インボックス" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="ナレッジエクスプローラ" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="昇格レビュー" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="クライアント招待管理" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="クライアントサインイン" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="クライアントプロジェクトビュー" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="議事録アップロード" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="自動スケジュール(cron)" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="通知センター" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="プロフィール" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="ワークスペース切替" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="プロジェクト切替" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="グローバル検索" sheetId="29" state="visible" r:id="rId29"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -592,280 +593,280 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>AI社員 組織図画面</t>
+          <t>プロジェクト設定画面</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>AI社員 編集画面</t>
+          <t>AI社員 組織図画面</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>チャット画面</t>
+          <t>AI社員 編集画面</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>工程ワークフロー(司令塔)画面</t>
+          <t>チャット画面</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>フェーズ管理画面</t>
+          <t>工程ワークフロー(司令塔)画面</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>成果物ビューア画面</t>
+          <t>フェーズ管理画面</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>モックビューア画面</t>
+          <t>成果物ビューア画面</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>タスクボード画面</t>
+          <t>モックビューア画面</t>
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>タスク詳細(6タブ)画面</t>
+          <t>タスクボード画面</t>
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>実行モニタ(SSE)画面</t>
+          <t>タスク詳細(6タブ)画面</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>承認インボックス画面</t>
+          <t>実行モニタ(SSE)画面</t>
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>ナレッジエクスプローラ画面</t>
+          <t>承認インボックス画面</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>昇格レビュー画面</t>
+          <t>ナレッジエクスプローラ画面</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>クライアント招待管理画面</t>
+          <t>昇格レビュー画面</t>
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>クライアントサインイン画面</t>
+          <t>クライアント招待管理画面</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>クライアントプロジェクトビュー画面</t>
+          <t>クライアントサインイン画面</t>
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>議事録アップロード画面</t>
+          <t>クライアントプロジェクトビュー画面</t>
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>自動スケジュール(cron)画面</t>
+          <t>議事録アップロード画面</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
         <v>13</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>通知センター画面</t>
+          <t>自動スケジュール(cron)画面</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>プロフィール画面</t>
+          <t>通知センター画面</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>ワークスペース切替画面</t>
+          <t>プロフィール画面</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>プロジェクト切替画面</t>
+          <t>ワークスペース切替画面</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
@@ -878,29 +879,42 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
+          <t>プロジェクト切替画面</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
           <t>グローバル検索画面</t>
         </is>
       </c>
-      <c r="B31" s="3" t="n">
+      <c r="B32" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="C31" s="3" t="n">
+      <c r="C32" s="3" t="n">
         <v>13</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="3" t="n"/>
-      <c r="B32" s="3" t="n"/>
-      <c r="C32" s="3" t="n"/>
-    </row>
     <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>完全性: 全429件 ＝ クライアント可視369件 ＋ 技術専用60件（画面で見えない裏取り=エンジニア版）</t>
-        </is>
-      </c>
+      <c r="A33" s="3" t="n"/>
       <c r="B33" s="3" t="n"/>
       <c r="C33" s="3" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>完全性: 全449件 ＝ クライアント可視385件 ＋ 技術専用64件（画面で見えない裏取り=エンジニア版）</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n"/>
+      <c r="C34" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -908,6 +922,465 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>画面</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>テスト観点</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>テスト項目</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>前提条件</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>操作手順</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>期待結果</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>SF01-001</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>工程ワークフロー(司令塔)画面</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>画面表示</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>画面が正常表示（全 UI 要素・モック準拠）</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>1. 工程ワークフロー(司令塔) を開く</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>SF01-002</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>工程ワークフロー(司令塔)画面</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>視覚忠実度</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>配色/角丸/タイポが design token 準拠</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面を目視</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>SF01-003</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>工程ワークフロー(司令塔)画面</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>データ取得</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>loading skeleton 表示（工程一覧）</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>取得未完</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>1. 工程ワークフロー(司令塔) を開き取得完了前を観察</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>SF01-004</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>工程ワークフロー(司令塔)画面</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>空データ</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>0 件時の空状態（工程一覧）</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>/workflow/phases?project_id が空配列</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1. データ0件で開く</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>空状態メッセージを表示（/undefined 参照にならない）</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>SF01-005</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>工程ワークフロー(司令塔)画面</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>取得失敗の inline error + toast（工程一覧）</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>/workflow/phases?project_id が 5xx</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1. API を でモックし開く</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>エラー表示 の inline error 表示 かつ toast 発火</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>SF01-007</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>工程ワークフロー(司令塔)画面</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>「工程ノード/依存エッジ」を操作すると動作する（ボタンが正しく動作するか）</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. 「工程ノード/依存エッジ」を目視</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>order 順ノード + 隣接エッジを描画（onClick/href/API が実在し、押すと副作用が起きる）</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>SF01-008</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>工程ワークフロー(司令塔)画面</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>読み上げ対応</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>axe scan で 0 critical/serious</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>1. axe を実行</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>critical/serious 違反 0（semantic role/aria）</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>SF01-010</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>工程ワークフロー(司令塔)画面</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>状態永続</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>F5 リロードでログアウトに飛ばない</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>ログイン済</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面で F5</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>保護ガードで維持・状態復元（URL クエリ等）</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>SF01-011</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>工程ワークフロー(司令塔)画面</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>到達性</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1495,7 +1968,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2470,7 +2943,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3144,7 +3617,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3947,7 +4420,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4836,7 +5309,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5322,7 +5795,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5953,7 +6426,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6412,7 +6885,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7080,766 +7553,6 @@
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="7" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>画面</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>テスト観点</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>テスト項目</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>前提条件</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>操作手順</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>期待結果</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>結果</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>SL01-001</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>クライアント招待管理画面</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>画面表示</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>画面が正常表示（全 UI 要素・モック準拠）</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>1. クライアント招待管理 を開く</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I2" s="4" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>SL01-002</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>クライアント招待管理画面</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>視覚忠実度</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>配色/角丸/タイポが design token 準拠</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>1. 画面を目視</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>SL01-003</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>クライアント招待管理画面</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>データ取得</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>loading skeleton 表示（招待一覧）</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>取得未完</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>1. クライアント招待管理 を開き取得完了前を観察</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>SL01-004</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>クライアント招待管理画面</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>空データ</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>0 件時の空状態（招待一覧）</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>/client-invitations?project_id が空配列</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>1. データ0件で開く</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>空状態メッセージを表示（/undefined 参照にならない）</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>SL01-005</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>クライアント招待管理画面</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>エラー</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>取得失敗の inline error + toast（招待一覧）</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>/client-invitations?project_id が 5xx</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>1. API を でモックし開く</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>エラー表示 の inline error 表示 かつ toast 発火</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>SL01-007</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>クライアント招待管理画面</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>インタラクション</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>「招待を発行」を操作すると動作する（ボタンが正しく動作するか）</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>1. 「招待を発行」をクリック</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>→raw token を1度だけバナー表示(R-T08 再取得不可)（onClick/href/API が実在し、押すと副作用が起きる）</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>SL01-008</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>クライアント招待管理画面</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>インタラクション</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>「失効」を操作すると動作する（ボタンが正しく動作するか）</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>1. 「失効」をクリック</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>revoke(楽観)（onClick/href/API が実在し、押すと副作用が起きる）</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>SL01-009</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>クライアント招待管理画面</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>発行(): 送信→反映</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>必須入力済</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>1. 発行() を実行</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>/client-invitations 呼び出し→成功表示→別GET/DBに反映</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>SL01-010</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>クライアント招待管理画面</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>エラー</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>発行(): API 失敗時 inline error + toast</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>接続失敗/レート</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>1. 発行() を失敗させる</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>エラー表示 + toast、状態は不整合にならない</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>SL01-011</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>クライアント招待管理画面</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>楽観更新</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>失効(revoke): 成功で即時反映</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>対象が存在</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>1. 失効(revoke) を実行</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>/client-invitations/{id}/revoke 呼び出し前にUIへ楽観反映→成功で確定（別GET再取得で反映）</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>SL01-012</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>クライアント招待管理画面</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>楽観更新</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>失効(revoke): 失敗でロールバック</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>サーバ 4xx/5xx</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>1. 失効(revoke) を実行しAPIが失敗</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>楽観反映が元に戻り、inline error + toast を表示</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>SL01-013</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>クライアント招待管理画面</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>エラー</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>失効(revoke): API 失敗時 inline error + toast</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>接続失敗/レート</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>1. 失効(revoke) を失敗させる</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>エラー表示 + toast、状態は不整合にならない</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I13" s="4" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>SL01-014</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>クライアント招待管理画面</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>受容差分</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>再送ボタンは非表示</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>1. 一覧確認</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>resend API 無しのため非表示(honest)</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I14" s="4" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>SL01-015</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>クライアント招待管理画面</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>読み上げ対応</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>axe scan で 0 critical/serious</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>1. axe を実行</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>critical/serious 違反 0（semantic role/aria）</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I15" s="4" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>SL01-017</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>クライアント招待管理画面</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>状態永続</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>F5 リロードでログアウトに飛ばない</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>ログイン済</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>1. 画面で F5</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>保護ガードで維持・状態復元（URL クエリ等）</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I16" s="4" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>SL01-018</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>クライアント招待管理画面</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>到達性</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I17" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8569,6 +8282,766 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>画面</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>テスト観点</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>テスト項目</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>前提条件</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>操作手順</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>期待結果</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>SL01-001</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>クライアント招待管理画面</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>画面表示</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>画面が正常表示（全 UI 要素・モック準拠）</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>1. クライアント招待管理 を開く</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>SL01-002</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>クライアント招待管理画面</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>視覚忠実度</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>配色/角丸/タイポが design token 準拠</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面を目視</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>SL01-003</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>クライアント招待管理画面</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>データ取得</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>loading skeleton 表示（招待一覧）</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>取得未完</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>1. クライアント招待管理 を開き取得完了前を観察</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>SL01-004</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>クライアント招待管理画面</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>空データ</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>0 件時の空状態（招待一覧）</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>/client-invitations?project_id が空配列</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1. データ0件で開く</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>空状態メッセージを表示（/undefined 参照にならない）</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>SL01-005</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>クライアント招待管理画面</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>取得失敗の inline error + toast（招待一覧）</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>/client-invitations?project_id が 5xx</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1. API を でモックし開く</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>エラー表示 の inline error 表示 かつ toast 発火</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>SL01-007</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>クライアント招待管理画面</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>「招待を発行」を操作すると動作する（ボタンが正しく動作するか）</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. 「招待を発行」をクリック</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>→raw token を1度だけバナー表示(R-T08 再取得不可)（onClick/href/API が実在し、押すと副作用が起きる）</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>SL01-008</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>クライアント招待管理画面</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>「失効」を操作すると動作する（ボタンが正しく動作するか）</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>1. 「失効」をクリック</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>revoke(楽観)（onClick/href/API が実在し、押すと副作用が起きる）</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>SL01-009</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>クライアント招待管理画面</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>発行(): 送信→反映</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>必須入力済</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>1. 発行() を実行</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>/client-invitations 呼び出し→成功表示→別GET/DBに反映</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>SL01-010</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>クライアント招待管理画面</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>発行(): API 失敗時 inline error + toast</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>接続失敗/レート</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>1. 発行() を失敗させる</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>エラー表示 + toast、状態は不整合にならない</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>SL01-011</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>クライアント招待管理画面</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>楽観更新</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>失効(revoke): 成功で即時反映</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>対象が存在</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>1. 失効(revoke) を実行</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>/client-invitations/{id}/revoke 呼び出し前にUIへ楽観反映→成功で確定（別GET再取得で反映）</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>SL01-012</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>クライアント招待管理画面</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>楽観更新</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>失効(revoke): 失敗でロールバック</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>サーバ 4xx/5xx</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>1. 失効(revoke) を実行しAPIが失敗</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>楽観反映が元に戻り、inline error + toast を表示</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>SL01-013</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>クライアント招待管理画面</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>失効(revoke): API 失敗時 inline error + toast</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>接続失敗/レート</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>1. 失効(revoke) を失敗させる</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>エラー表示 + toast、状態は不整合にならない</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>SL01-014</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>クライアント招待管理画面</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>受容差分</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>再送ボタンは非表示</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>1. 一覧確認</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>resend API 無しのため非表示(honest)</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>SL01-015</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>クライアント招待管理画面</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>読み上げ対応</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>axe scan で 0 critical/serious</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>1. axe を実行</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>critical/serious 違反 0（semantic role/aria）</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>SL01-017</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>クライアント招待管理画面</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>状態永続</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>F5 リロードでログアウトに飛ばない</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>ログイン済</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面で F5</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>保護ガードで維持・状態復元（URL クエリ等）</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>SL01-018</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>クライアント招待管理画面</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>到達性</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -9194,7 +9667,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9690,609 +10163,6 @@
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="7" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>画面</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>テスト観点</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>テスト項目</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>前提条件</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>操作手順</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>期待結果</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>結果</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>SM01-001</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>議事録アップロード画面</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>画面表示</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>画面が正常表示（全 UI 要素・モック準拠）</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>1. 議事録アップロード を開く</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I2" s="4" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>SM01-002</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>議事録アップロード画面</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>視覚忠実度</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>配色/角丸/タイポが design token 準拠</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>1. 画面を目視</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>SM01-003</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>議事録アップロード画面</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>データ取得</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>loading skeleton 表示（状態ポーリング）</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>取得未完</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>1. 議事録アップロード を開き取得完了前を観察</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>SM01-004</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>議事録アップロード画面</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>空データ</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>0 件時の空状態（状態ポーリング）</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>/meetings/{id} が空配列</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>1. データ0件で開く</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>空状態メッセージを表示（/undefined 参照にならない）</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>SM01-005</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>議事録アップロード画面</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>エラー</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>取得失敗の inline error + toast（状態ポーリング）</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>/meetings/{id} が 5xx</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>1. API を でモックし開く</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>エラー表示 の inline error 表示 かつ toast 発火</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr"/>
-      <c r="I6" s="3" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>SM01-007</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>議事録アップロード画面</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>インタラクション</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>「ファイル選択」を操作すると動作する（ボタンが正しく動作するか）</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>1. 「ファイル選択」を選択</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>署名URL発行→実PUT→登録→transcribe キュー→polling→本文表示（onClick/href/API が実在し、押すと副作用が起きる）</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>SM01-008</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>議事録アップロード画面</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>アップロード→transcription: 送信→反映</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>必須入力済</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>1. アップロード→transcription を実行</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>upload-url→→ /meetings→transcribe→poll→transcript-url 呼び出し→成功表示→別GET/DBに反映</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>SM01-009</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>議事録アップロード画面</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>エラー</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>アップロード→transcription: API 失敗時 inline error + toast</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>接続失敗/レート</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>1. アップロード→transcription を失敗させる</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>エラー表示 + toast、状態は不整合にならない</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>SM01-010</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>議事録アップロード画面</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>G3実副作用</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>実 storage/Whisper 副作用(BLOCKED)</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>実DB/実storage</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>1. 実ファイルをアップロード</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>storage にオブジェクト作成・parse_result_path 生成を実API照会で確認</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr"/>
-      <c r="I10" s="3" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>SM01-011</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>議事録アップロード画面</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>マルチターン</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>queued→parsing→done の状態継続</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>アップロード後</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>1. 完了までポーリングを観察</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>parsed_at/parse_error まで状態が継続遷移し本文取得</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr"/>
-      <c r="I11" s="3" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>SM01-012</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>議事録アップロード画面</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>読み上げ対応</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>axe scan で 0 critical/serious</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>1. axe を実行</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>critical/serious 違反 0（semantic role/aria）</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>SM01-014</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>議事録アップロード画面</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>状態永続</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>F5 リロードでログアウトに飛ばない</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>ログイン済</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>1. 画面で F5</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>保護ガードで維持・状態復元（URL クエリ等）</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I13" s="4" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>SM01-015</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>議事録アップロード画面</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>到達性</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I14" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10369,12 +10239,12 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>SO01-001</t>
+          <t>SM01-001</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>自動スケジュール(cron)画面</t>
+          <t>議事録アップロード画面</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -10394,7 +10264,7 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>1. 自動スケジュール(cron) を開く</t>
+          <t>1. 議事録アップロード を開く</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
@@ -10412,12 +10282,12 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>SO01-002</t>
+          <t>SM01-002</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>自動スケジュール(cron)画面</t>
+          <t>議事録アップロード画面</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -10453,143 +10323,131 @@
       <c r="I3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>SO01-003</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>自動スケジュール(cron)画面</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>SM01-003</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>議事録アップロード画面</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>データ取得</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>loading skeleton 表示（スケジュール一覧）</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>loading skeleton 表示（状態ポーリング）</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>取得未完</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>1. 自動スケジュール(cron) を開き取得完了前を観察</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>1. 議事録アップロード を開き取得完了前を観察</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr"/>
+      <c r="I4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>SO01-004</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>自動スケジュール(cron)画面</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>SM01-004</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>議事録アップロード画面</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>空データ</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>0 件時の空状態（スケジュール一覧）</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>/cron-schedules?project_id が空配列</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>0 件時の空状態（状態ポーリング）</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>/meetings/{id} が空配列</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>1. データ0件で開く</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>空状態メッセージを表示（/undefined 参照にならない）</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>SO01-005</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>自動スケジュール(cron)画面</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>SM01-005</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>議事録アップロード画面</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>エラー</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>取得失敗の inline error + toast（スケジュール一覧）</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>/cron-schedules?project_id が 5xx</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>取得失敗の inline error + toast（状態ポーリング）</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>/meetings/{id} が 5xx</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>1. API を でモックし開く</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>エラー表示 の inline error 表示 かつ toast 発火</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr"/>
+      <c r="I6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>SO01-007</t>
+          <t>SM01-007</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>自動スケジュール(cron)画面</t>
+          <t>議事録アップロード画面</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -10599,7 +10457,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>「有効/無効トグル」を操作すると動作する（ボタンが正しく動作するか）</t>
+          <t>「ファイル選択」を操作すると動作する（ボタンが正しく動作するか）</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -10609,12 +10467,12 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>1. 「有効/無効トグル」をクリック</t>
+          <t>1. 「ファイル選択」を選択</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>enabled(楽観トグル)（onClick/href/API が実在し、押すと副作用が起きる）</t>
+          <t>署名URL発行→実PUT→登録→transcribe キュー→polling→本文表示（onClick/href/API が実在し、押すと副作用が起きる）</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -10625,186 +10483,170 @@
       <c r="I7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>SO01-008</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>自動スケジュール(cron)画面</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>楽観更新</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>有効トグル: 成功で即時反映</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>対象が存在</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>1. 有効トグル を実行</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>/cron-schedules/{id} 呼び出し前にUIへ楽観反映→成功で確定（別GET再取得で反映）</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="inlineStr"/>
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>SM01-008</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>議事録アップロード画面</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>アップロード→transcription: 送信→反映</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>必須入力済</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>1. アップロード→transcription を実行</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>upload-url→→ /meetings→transcribe→poll→transcript-url 呼び出し→成功表示→別GET/DBに反映</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr"/>
+      <c r="I8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>SO01-009</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>自動スケジュール(cron)画面</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>楽観更新</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>有効トグル: 失敗でロールバック</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>サーバ 4xx/5xx</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>1. 有効トグル を実行しAPIが失敗</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>楽観反映が元に戻り、inline error + toast を表示</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr"/>
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>SM01-009</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>議事録アップロード画面</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>アップロード→transcription: API 失敗時 inline error + toast</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>接続失敗/レート</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>1. アップロード→transcription を失敗させる</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>エラー表示 + toast、状態は不整合にならない</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>SO01-010</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>自動スケジュール(cron)画面</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>エラー</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>有効トグル: API 失敗時 inline error + toast</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>接続失敗/レート</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>1. 有効トグル を失敗させる</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>エラー表示 + toast、状態は不整合にならない</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr"/>
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>SM01-010</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>議事録アップロード画面</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>G3実副作用</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>実 storage/Whisper 副作用(BLOCKED)</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>実DB/実storage</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>1. 実ファイルをアップロード</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>storage にオブジェクト作成・parse_result_path 生成を実API照会で確認</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr"/>
+      <c r="I10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>SO01-011</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>自動スケジュール(cron)画面</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>受容差分</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>即時実行ボタンは非表示</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>1. 一覧確認</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>run-now API 無しのため列非表示(honest)</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr"/>
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>SM01-011</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>議事録アップロード画面</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>マルチターン</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>queued→parsing→done の状態継続</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>アップロード後</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>1. 完了までポーリングを観察</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>parsed_at/parse_error まで状態が継続遷移し本文取得</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr"/>
+      <c r="I11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>SO01-012</t>
+          <t>SM01-012</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>自動スケジュール(cron)画面</t>
+          <t>議事録アップロード画面</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -10842,12 +10684,12 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>SO01-014</t>
+          <t>SM01-014</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>自動スケジュール(cron)画面</t>
+          <t>議事録アップロード画面</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -10885,12 +10727,12 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>SO01-015</t>
+          <t>SM01-015</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>自動スケジュール(cron)画面</t>
+          <t>議事録アップロード画面</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -10931,6 +10773,637 @@
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>画面</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>テスト観点</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>テスト項目</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>前提条件</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>操作手順</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>期待結果</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>SO01-001</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)画面</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>画面表示</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>画面が正常表示（全 UI 要素・モック準拠）</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>1. 自動スケジュール(cron) を開く</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>SO01-002</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)画面</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>視覚忠実度</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>配色/角丸/タイポが design token 準拠</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面を目視</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>SO01-003</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)画面</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>データ取得</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>loading skeleton 表示（スケジュール一覧）</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>取得未完</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>1. 自動スケジュール(cron) を開き取得完了前を観察</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>SO01-004</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)画面</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>空データ</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>0 件時の空状態（スケジュール一覧）</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>/cron-schedules?project_id が空配列</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1. データ0件で開く</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>空状態メッセージを表示（/undefined 参照にならない）</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>SO01-005</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)画面</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>取得失敗の inline error + toast（スケジュール一覧）</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>/cron-schedules?project_id が 5xx</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1. API を でモックし開く</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>エラー表示 の inline error 表示 かつ toast 発火</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>SO01-007</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)画面</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>「有効/無効トグル」を操作すると動作する（ボタンが正しく動作するか）</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. 「有効/無効トグル」をクリック</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>enabled(楽観トグル)（onClick/href/API が実在し、押すと副作用が起きる）</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>SO01-008</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)画面</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>楽観更新</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>有効トグル: 成功で即時反映</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>対象が存在</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>1. 有効トグル を実行</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>/cron-schedules/{id} 呼び出し前にUIへ楽観反映→成功で確定（別GET再取得で反映）</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>SO01-009</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)画面</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>楽観更新</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>有効トグル: 失敗でロールバック</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>サーバ 4xx/5xx</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>1. 有効トグル を実行しAPIが失敗</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>楽観反映が元に戻り、inline error + toast を表示</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>SO01-010</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)画面</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>有効トグル: API 失敗時 inline error + toast</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>接続失敗/レート</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>1. 有効トグル を失敗させる</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>エラー表示 + toast、状態は不整合にならない</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>SO01-011</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)画面</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>受容差分</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>即時実行ボタンは非表示</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>1. 一覧確認</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>run-now API 無しのため列非表示(honest)</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>SO01-012</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)画面</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>読み上げ対応</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>axe scan で 0 critical/serious</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>1. axe を実行</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>critical/serious 違反 0（semantic role/aria）</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>SO01-014</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)画面</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>状態永続</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>F5 リロードでログアウトに飛ばない</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>ログイン済</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面で F5</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>保護ガードで維持・状態復元（URL クエリ等）</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>SO01-015</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)画面</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>到達性</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11518,7 +11991,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12315,465 +12788,6 @@
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="7" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>画面</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>テスト観点</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>テスト項目</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>前提条件</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>操作手順</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>期待結果</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>結果</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-001</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替画面</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>画面表示</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>画面が正常表示（全 UI 要素・モック準拠）</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>1. ワークスペース切替 を開く</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I2" s="4" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-002</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替画面</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>視覚忠実度</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>配色/角丸/タイポが design token 準拠</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>1. 画面を目視</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-003</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替画面</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>データ取得</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>loading skeleton 表示（所属 WS 一覧）</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>取得未完</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>1. ワークスペース切替 を開き取得完了前を観察</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-004</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替画面</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>空データ</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>0 件時の空状態（所属 WS 一覧）</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>/workspaces が空配列</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>1. データ0件で開く</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>空状態メッセージを表示（/undefined 参照にならない）</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-005</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替画面</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>エラー</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>取得失敗の inline error + toast（所属 WS 一覧）</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>/workspaces が 5xx</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>1. API を でモックし開く</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>エラー表示 の inline error 表示 かつ toast 発火</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-007</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替画面</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>インタラクション</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>「WS picker」を操作すると動作する（ボタンが正しく動作するか）</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>1. 「WS picker」を選択</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>localStorage(atelier_current_workspace) 永続化（onClick/href/API が実在し、押すと副作用が起きる）</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-008</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替画面</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>読み上げ対応</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>axe scan で 0 critical/serious</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>1. axe を実行</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>critical/serious 違反 0（semantic role/aria）</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-010</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替画面</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>状態永続</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>F5 リロードでログアウトに飛ばない</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>ログイン済</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>1. 画面で F5</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>保護ガードで維持・状態復元（URL クエリ等）</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-011</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替画面</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>到達性</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12850,12 +12864,12 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>TUC39-001</t>
+          <t>TUC38-001</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替画面</t>
+          <t>ワークスペース切替画面</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -12875,7 +12889,7 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>1. プロジェクト切替 を開く</t>
+          <t>1. ワークスペース切替 を開く</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
@@ -12893,12 +12907,12 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>TUC39-002</t>
+          <t>TUC38-002</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替画面</t>
+          <t>ワークスペース切替画面</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -12936,12 +12950,12 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>TUC39-003</t>
+          <t>TUC38-003</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替画面</t>
+          <t>ワークスペース切替画面</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -12951,7 +12965,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>loading skeleton 表示（現在WS内プロジェクト）</t>
+          <t>loading skeleton 表示（所属 WS 一覧）</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -12961,7 +12975,7 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>1. プロジェクト切替 を開き取得完了前を観察</t>
+          <t>1. ワークスペース切替 を開き取得完了前を観察</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
@@ -12979,12 +12993,12 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>TUC39-004</t>
+          <t>TUC38-004</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替画面</t>
+          <t>ワークスペース切替画面</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -12994,12 +13008,12 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>0 件時の空状態（現在WS内プロジェクト）</t>
+          <t>0 件時の空状態（所属 WS 一覧）</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>/projects?workspace_id が空配列</t>
+          <t>/workspaces が空配列</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -13022,12 +13036,12 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>TUC39-005</t>
+          <t>TUC38-005</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替画面</t>
+          <t>ワークスペース切替画面</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -13037,12 +13051,12 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>取得失敗の inline error + toast（現在WS内プロジェクト）</t>
+          <t>取得失敗の inline error + toast（所属 WS 一覧）</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>/projects?workspace_id が 5xx</t>
+          <t>/workspaces が 5xx</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -13065,12 +13079,12 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>TUC39-007</t>
+          <t>TUC38-007</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替画面</t>
+          <t>ワークスペース切替画面</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -13080,7 +13094,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>「Project picker」を操作すると動作する（ボタンが正しく動作するか）</t>
+          <t>「WS picker」を操作すると動作する（ボタンが正しく動作するか）</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -13090,12 +13104,12 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>1. 「Project picker」を選択</t>
+          <t>1. 「WS picker」を選択</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>localStorage(atelier_current_project) 永続化（onClick/href/API が実在し、押すと副作用が起きる）</t>
+          <t>localStorage(atelier_current_workspace) 永続化（onClick/href/API が実在し、押すと副作用が起きる）</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -13108,12 +13122,12 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>TUC39-008</t>
+          <t>TUC38-008</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替画面</t>
+          <t>ワークスペース切替画面</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -13151,12 +13165,12 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>TUC39-010</t>
+          <t>TUC38-010</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替画面</t>
+          <t>ワークスペース切替画面</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -13194,12 +13208,12 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>TUC39-011</t>
+          <t>TUC38-011</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替画面</t>
+          <t>ワークスペース切替画面</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -13240,6 +13254,465 @@
 </file>
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>画面</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>テスト観点</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>テスト項目</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>前提条件</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>操作手順</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>期待結果</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-001</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替画面</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>画面表示</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>画面が正常表示（全 UI 要素・モック準拠）</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>1. プロジェクト切替 を開く</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-002</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替画面</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>視覚忠実度</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>配色/角丸/タイポが design token 準拠</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面を目視</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-003</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替画面</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>データ取得</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>loading skeleton 表示（現在WS内プロジェクト）</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>取得未完</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>1. プロジェクト切替 を開き取得完了前を観察</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-004</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替画面</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>空データ</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>0 件時の空状態（現在WS内プロジェクト）</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>/projects?workspace_id が空配列</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1. データ0件で開く</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>空状態メッセージを表示（/undefined 参照にならない）</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-005</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替画面</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>取得失敗の inline error + toast（現在WS内プロジェクト）</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>/projects?workspace_id が 5xx</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1. API を でモックし開く</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>エラー表示 の inline error 表示 かつ toast 発火</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-007</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替画面</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>「Project picker」を操作すると動作する（ボタンが正しく動作するか）</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. 「Project picker」を選択</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>localStorage(atelier_current_project) 永続化（onClick/href/API が実在し、押すと副作用が起きる）</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-008</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替画面</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>読み上げ対応</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>axe scan で 0 critical/serious</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>1. axe を実行</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>critical/serious 違反 0（semantic role/aria）</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-010</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替画面</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>状態永続</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>F5 リロードでログアウトに飛ばない</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>ログイン済</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面で F5</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>保護ガードで維持・状態復元（URL クエリ等）</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-011</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替画面</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>到達性</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -16113,6 +16586,766 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>画面</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>テスト観点</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>テスト項目</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>前提条件</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>操作手順</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>期待結果</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>SB03-001</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト設定画面</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>画面表示</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>画面が正常表示（全 UI 要素・モック準拠）</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>1. サイドバー「設定」から開く</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>モックの全セクション（基本情報/AI学習設定/クライアント招待/エクスポート/危険な操作）が表示</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>SB03-002</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト設定画面</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>データ取得</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>/projects/{id} の実値がフォーム初期値に入る</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>project 選択済</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面を開く 2. 各欄を目視</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>名前/クライアント名/説明/種別/ステータスが API 実値</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>SB03-003</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト設定画面</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>入力フォーム</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト名の必須バリデーション</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>1. 名前を空にし保存</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>「入力必須」エラーが表示され は飛ばない</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>SB03-005</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト設定画面</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>登録・編集</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>種別 (自社/クライアント/個人) を変更→保存→DB enum 変換</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1. 種別変更 2. 保存</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>契約 enum (client_project 等) → DB enum (client_work 等) にマップされ永続</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>SB03-006</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト設定画面</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>登録・編集</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>ステータス「下書き」が丸められず往復する</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>status=draft の project</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1. draft のまま保存</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>draft のまま維持（旧実装は active へ化けた実バグ）</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>SB03-007</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト設定画面</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>AI 学習トグルが の実値で初期化される</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>ai_learning_opt_out=true</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面を開く</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>トグル OFF（許可しない）。opt_out=false なら ON</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>SB03-009</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト設定画面</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>楽観更新</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>AI 学習トグル失敗時ロールバック + エラー表示</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>API 5xx</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>1. トグル操作を失敗させる</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>表示が元に戻り「変更に失敗しました」</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>SB03-010</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト設定画面</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>エクスポート 5 ボタン (ヒアリング〜機能分解) が実 API を叩く</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>1. 各ボタンをクリック</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>/outputs?project_id&amp;stage → content-url → 署名 URL を新タブで開く</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>SB03-011</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト設定画面</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>空データ</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>成果物 0 件の工程は明示メッセージ</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>outputs 0 件</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>1. 要件定義をクリック</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>「『要件定義』の成果物はまだありません。」</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>SB03-012</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト設定画面</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>storage 未設定 (503) を明示</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>dev 環境</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>1. 成果物ありの工程をクリック</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>「storage が未設定です」と原因を明示（握り潰さない）</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>SB03-014</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト設定画面</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>登録・編集</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>削除確定 → /projects/{id} → 一覧へ遷移</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>1. 削除→確定</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>soft-delete（30日 grace）+ onDeleted で /projects へ</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>SB03-015</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト設定画面</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>到達性</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>「招待管理を開く」→ S-L01 へ project 文脈つき遷移</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>1. リンククリック</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>/portal/invitations?project={id} へ遷移（意味的 URL）</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>SB03-017</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト設定画面</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>取得失敗時 inline error</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>5xx</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>1. API 失敗で開く</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>「取得に失敗しました」(エラー表示)</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>SB03-018</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト設定画面</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>スマホ・タブレットでも崩れない</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>390/768/1440 で崩れない・操作できる</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>1. 各幅で開き操作</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>横スクロール無し、種別/ステータスは 390 で縦積み、全操作可能</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>SB03-019</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト設定画面</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>状態永続</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>リロードでログアウトに飛ばず ?project= 文脈維持</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>ログイン済</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>1. F5</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>フォームが再取得され表示継続</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>SB03-020</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト設定画面</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>受容差分</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>project 未選択時は案内メッセージ</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>?project= なし</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>1. /projects/settings を直接開く</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>「プロジェクトを選択すると設定を表示します。」</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -16609,7 +17842,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -17326,7 +18559,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -17523,43 +18756,47 @@
       <c r="I4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>SE01-004</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>チャット画面</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>空データ</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>スレッド0件時の空状態</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>スレッド0件</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>1. 空プロジェクトで開く</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>「スレッドがありません…」の empty state ( にならない)</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -18205,465 +19442,6 @@
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="7" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>画面</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>テスト観点</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>テスト項目</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>前提条件</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>操作手順</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>期待結果</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>結果</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>SF01-001</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>工程ワークフロー(司令塔)画面</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>画面表示</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>画面が正常表示（全 UI 要素・モック準拠）</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>1. 工程ワークフロー(司令塔) を開く</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I2" s="4" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>SF01-002</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>工程ワークフロー(司令塔)画面</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>視覚忠実度</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>配色/角丸/タイポが design token 準拠</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>1. 画面を目視</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>SF01-003</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>工程ワークフロー(司令塔)画面</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>データ取得</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>loading skeleton 表示（工程一覧）</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>取得未完</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>1. 工程ワークフロー(司令塔) を開き取得完了前を観察</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>SF01-004</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>工程ワークフロー(司令塔)画面</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>空データ</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>0 件時の空状態（工程一覧）</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>/workflow/phases?project_id が空配列</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>1. データ0件で開く</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>空状態メッセージを表示（/undefined 参照にならない）</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>SF01-005</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>工程ワークフロー(司令塔)画面</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>エラー</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>取得失敗の inline error + toast（工程一覧）</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>/workflow/phases?project_id が 5xx</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>1. API を でモックし開く</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>エラー表示 の inline error 表示 かつ toast 発火</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>SF01-007</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>工程ワークフロー(司令塔)画面</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>インタラクション</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>「工程ノード/依存エッジ」を操作すると動作する（ボタンが正しく動作するか）</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>1. 「工程ノード/依存エッジ」を目視</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>order 順ノード + 隣接エッジを描画（onClick/href/API が実在し、押すと副作用が起きる）</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>SF01-008</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>工程ワークフロー(司令塔)画面</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>読み上げ対応</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>axe scan で 0 critical/serious</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>1. axe を実行</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>critical/serious 違反 0（semantic role/aria）</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>SF01-010</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>工程ワークフロー(司令塔)画面</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>状態永続</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>F5 リロードでログアウトに飛ばない</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>ログイン済</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>1. 画面で F5</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>保護ガードで維持・状態復元（URL クエリ等）</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>SF01-011</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>工程ワークフロー(司令塔)画面</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>到達性</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/apps/web/.qa/テスト仕様書_クライアント版.xlsx
+++ b/apps/web/.qa/テスト仕様書_クライアント版.xlsx
@@ -13,29 +13,30 @@
     <sheet name="プロジェクト一覧" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="プロジェクトダッシュボード" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="プロジェクト設定" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="AI社員 組織図" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="AI社員 編集" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="チャット" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="工程ワークフロー(司令塔)" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="フェーズ管理" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="成果物ビューア" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="モックビューア" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="タスクボード" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="タスク詳細(6タブ)" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="実行モニタ(SSE)" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="承認インボックス" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="ナレッジエクスプローラ" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="昇格レビュー" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="クライアント招待管理" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="クライアントサインイン" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="クライアントプロジェクトビュー" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="議事録アップロード" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="自動スケジュール(cron)" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="通知センター" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="プロフィール" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="ワークスペース切替" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="プロジェクト切替" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="グローバル検索" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="プロジェクト・シークレット" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="AI社員 組織図" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="AI社員 編集" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="チャット" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="工程ワークフロー(司令塔)" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="フェーズ管理" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="成果物ビューア" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="モックビューア" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="タスクボード" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="タスク詳細(6タブ)" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="実行モニタ(SSE)" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="承認インボックス" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="ナレッジエクスプローラ" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="昇格レビュー" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="クライアント招待管理" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="クライアントサインイン" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="クライアントプロジェクトビュー" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="議事録アップロード" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="自動スケジュール(cron)" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="通知センター" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="プロフィール" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="ワークスペース切替" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="プロジェクト切替" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="グローバル検索" sheetId="30" state="visible" r:id="rId30"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -490,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -606,280 +607,280 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>AI社員 組織図画面</t>
+          <t>プロジェクト・シークレット画面</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>AI社員 編集画面</t>
+          <t>AI社員 組織図画面</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>チャット画面</t>
+          <t>AI社員 編集画面</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>工程ワークフロー(司令塔)画面</t>
+          <t>チャット画面</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>フェーズ管理画面</t>
+          <t>工程ワークフロー(司令塔)画面</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>成果物ビューア画面</t>
+          <t>フェーズ管理画面</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>モックビューア画面</t>
+          <t>成果物ビューア画面</t>
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>タスクボード画面</t>
+          <t>モックビューア画面</t>
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>タスク詳細(6タブ)画面</t>
+          <t>タスクボード画面</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>実行モニタ(SSE)画面</t>
+          <t>タスク詳細(6タブ)画面</t>
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>承認インボックス画面</t>
+          <t>実行モニタ(SSE)画面</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>ナレッジエクスプローラ画面</t>
+          <t>承認インボックス画面</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>昇格レビュー画面</t>
+          <t>ナレッジエクスプローラ画面</t>
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>クライアント招待管理画面</t>
+          <t>昇格レビュー画面</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>クライアントサインイン画面</t>
+          <t>クライアント招待管理画面</t>
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>クライアントプロジェクトビュー画面</t>
+          <t>クライアントサインイン画面</t>
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>議事録アップロード画面</t>
+          <t>クライアントプロジェクトビュー画面</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>自動スケジュール(cron)画面</t>
+          <t>議事録アップロード画面</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
         <v>13</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>通知センター画面</t>
+          <t>自動スケジュール(cron)画面</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>プロフィール画面</t>
+          <t>通知センター画面</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>ワークスペース切替画面</t>
+          <t>プロフィール画面</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>プロジェクト切替画面</t>
+          <t>ワークスペース切替画面</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
@@ -892,29 +893,42 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
+          <t>プロジェクト切替画面</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
           <t>グローバル検索画面</t>
         </is>
       </c>
-      <c r="B32" s="3" t="n">
+      <c r="B33" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="C32" s="3" t="n">
+      <c r="C33" s="3" t="n">
         <v>13</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="3" t="n"/>
-      <c r="B33" s="3" t="n"/>
-      <c r="C33" s="3" t="n"/>
-    </row>
     <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>完全性: 全449件 ＝ クライアント可視385件 ＋ 技術専用64件（画面で見えない裏取り=エンジニア版）</t>
-        </is>
-      </c>
+      <c r="A34" s="3" t="n"/>
       <c r="B34" s="3" t="n"/>
       <c r="C34" s="3" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>完全性: 全469件 ＝ クライアント可視404件 ＋ 技術専用65件（画面で見えない裏取り=エンジニア版）</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n"/>
+      <c r="C35" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -922,6 +936,895 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>画面</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>テスト観点</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>テスト項目</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>前提条件</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>操作手順</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>期待結果</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>SE01-001</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>チャット画面</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>画面表示</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>3ペイン構成が正常表示（モック S-E01-thread.html 準拠: 左260px スレッド/中央チャット/右340px コンテキスト）</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>ログイン済+スレッド有</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>1. /chat を開く</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>3ペインが描画され、モックの主要領域(スレッド検索/新規スレッド/工程グルーピング/工程文脈バー/社員ヘッダー/コンポーザ/右タブ)が全て存在</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>SE01-002</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>チャット画面</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>視覚忠実度</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>配色/角丸/タイポが design token 準拠</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面を目視</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>--color-*/--rounded-* トークン準拠・社員カラーはモック avatar-* 準拠</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>SE01-003</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>チャット画面</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>データ取得</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>スレッド一覧が実 API ( /chat/threads?project_id) から描画</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>1. 開いて一覧を確認</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>実スレッドが工程グルーピング(現在→完了→横断)で表示・message_count/相対時刻付き</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>SE01-004</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>チャット画面</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>空データ</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>スレッド0件時の空状態</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>スレッド0件</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1. 空プロジェクトで開く</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>「スレッドがありません…」の empty state ( にならない)</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>SE01-005</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>チャット画面</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>送信失敗時のエラーバナー(単一・dismiss可)</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>LLM 未設定 or API 5xx</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1. メッセージ送信</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>コンポーザ直上に エラー表示 バナー1箇所のみ・✕で閉じる・スレッド切替でリセット</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>SE01-006</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>チャット画面</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>スレッド検索フィルタ（ボタンが正しく動作するか）</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>スレッド複数</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. 検索欄に「競合」入力</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>タイトル/社員名/最終メッセージで絞り込まれる</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>SE01-007</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>チャット画面</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>スレッド切替・新規スレッド作成（ボタンが正しく動作するか）</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>1. 別スレッドをクリック 2. 新規スレッドで作成</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>メッセージが切替わる/ /chat/threads (phase_id 任意) で作成され選択される</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>SE01-008</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>チャット画面</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>ペイン開閉トグル（ボタンが正しく動作するか）</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>1. 左右トグルを各クリック</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>左ペイン/右ペインが開閉し grid が追従・aria-pressed 反映</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>SE01-009</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>チャット画面</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>メッセージ送信 (Enter=送信 / Shift+Enter=改行 / IME 変換中は送信しない)</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>スレッド選択済</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>1. 入力して Enter</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>user バブル即時表示→SSE 応答 (LLM 無環境では誠実なエラー表示)・IME 変換確定 Enter で誤送信しない</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>SE01-010</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>チャット画面</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>@メンション ピッカー（ボタンが正しく動作するか）</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>AI 社員複数</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>1. @メンション をクリック 2. 社員を選択</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>実 AI 社員一覧(対話相手は除外)が出て、カーソル位置に「@名前 」が挿入される</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>SE01-011</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>チャット画面</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>ナレッジ参照ピッカー（ボタンが正しく動作するか）</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>1. ナレッジ参照をクリック</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>実ナレッジ一覧から選択で「[ナレッジ: title] 」挿入。0件時は「まだありません+自動RAGは常時有効」の誠実表示</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>SE01-012</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>チャット画面</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>死に要素ゼロ</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>コンポーザに非機能ボタンが存在しない</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>1. コンポーザの全ボタンを列挙</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>添付・/コマンドのボタンは**描画されない**(gap tracker 起票済)。表示される全ボタンが機能する</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>SE01-013</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>チャット画面</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>表示</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>tool ロールメッセージのツールカード描画</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>tool メッセージ有</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>1. 該当スレッドを開く</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>monospace ツール名ヘッダ+本文カード (モック .tool-card 準拠)</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>SE01-014</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>チャット画面</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>表示</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>工程文脈バー (現在の工程・Stage n/9・工程画面リンク)</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>1. ヘッダーを確認 2. リンクをクリック</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>実 current_phase を表示し /workflow?project= へ遷移</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>SE01-015</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>チャット画面</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>表示</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>右ペイン: 主力決定/コンテキスト/参照タブ</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>decisions 有</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>1. 各タブをクリック</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>実 /decisions の確定カード(反映先付)・F-CTX01 実測値(SSE context)・実 /knowledge 一覧</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>SE01-016</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>チャット画面</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>履歴</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>リロードで会話が消えない (既存メッセージロード)</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>メッセージ有</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>1. F5</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>過去メッセージが created_at 付きで再表示</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>SE01-017</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>チャット画面</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>スマホ・タブレットでも崩れない</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>390/768/1440 で崩れない・モバイルは一覧⇄チャット切替</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>1. 各幅で開く 2. モバイルで戻るボタン</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>横スクロール無し・モバイルで戻る→一覧表示・右ペインは重ね表示トグル</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>SE01-018</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>チャット画面</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>読み上げ対応</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>axe 0 critical/serious・log role/aria-live/label 契約</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>1. axe 実行</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>違反0・role=log aria-live=polite・「メッセージを入力」label</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>SE01-020</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>チャット画面</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>状態永続</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>?thread= URL で直接スレッドを開ける</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>1. /chat?thread=&lt;id&gt; を開く</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>該当スレッドが選択状態で開く</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1380,7 +2283,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1968,7 +2871,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2943,7 +3846,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3617,7 +4520,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4420,7 +5323,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5309,7 +6212,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5795,7 +6698,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6426,7 +7329,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6879,680 +7782,6 @@
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="7" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>画面</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>テスト観点</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>テスト項目</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>前提条件</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>操作手順</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>期待結果</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>結果</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>SK02-001</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>昇格レビュー画面</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>画面表示</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>画面が正常表示（全 UI 要素・モック準拠）</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>1. 昇格レビュー を開く</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I2" s="4" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>SK02-002</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>昇格レビュー画面</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>視覚忠実度</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>配色/角丸/タイポが design token 準拠</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>1. 画面を目視</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>SK02-003</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>昇格レビュー画面</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>データ取得</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>loading skeleton 表示（昇格候補）</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>取得未完</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>1. 昇格レビュー を開き取得完了前を観察</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>SK02-004</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>昇格レビュー画面</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>空データ</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>0 件時の空状態（昇格候補）</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>/knowledge/promotions が空配列</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>1. データ0件で開く</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>空状態メッセージを表示（/undefined 参照にならない）</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>SK02-005</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>昇格レビュー画面</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>エラー</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>取得失敗の inline error + toast（昇格候補）</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>/knowledge/promotions が 5xx</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>1. API を でモックし開く</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>エラー表示 の inline error 表示 かつ toast 発火</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>SK02-007</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>昇格レビュー画面</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>インタラクション</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>「承認」を操作すると動作する（ボタンが正しく動作するか）</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>1. 「承認」をクリック</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>昇格処理→楽観除外（onClick/href/API が実在し、押すと副作用が起きる）</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>SK02-008</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>昇格レビュー画面</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>インタラクション</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>「却下」を操作すると動作する（ボタンが正しく動作するか）</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>1. 「却下」をクリック</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>却下 API 無し→クライアント側 dismiss（onClick/href/API が実在し、押すと副作用が起きる）</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>SK02-009</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>昇格レビュー画面</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>楽観更新</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>承認: 成功で即時反映</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>対象が存在</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>1. 承認 を実行</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>昇格承認 呼び出し前にUIへ楽観反映→成功で確定（別GET再取得で反映）</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>SK02-010</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>昇格レビュー画面</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>楽観更新</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>承認: 失敗でロールバック</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>サーバ 4xx/5xx</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>1. 承認 を実行しAPIが失敗</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>楽観反映が元に戻り、inline error + toast を表示</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>SK02-011</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>昇格レビュー画面</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>エラー</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>承認: API 失敗時 inline error + toast</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>接続失敗/レート</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>1. 承認 を失敗させる</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>エラー表示 + toast、状態は不整合にならない</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>SK02-012</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>昇格レビュー画面</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>受容差分</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>却下はクライアント dismiss</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>1. 却下</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>reject API 無しのため一覧から即時除去(honest)</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>SK02-013</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>昇格レビュー画面</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>読み上げ対応</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>axe scan で 0 critical/serious</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>1. axe を実行</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>critical/serious 違反 0（semantic role/aria）</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I13" s="4" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>SK02-015</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>昇格レビュー画面</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>状態永続</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>F5 リロードでログアウトに飛ばない</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>ログイン済</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>1. 画面で F5</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>保護ガードで維持・状態復元（URL クエリ等）</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I14" s="4" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>SK02-016</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>昇格レビュー画面</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>到達性</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I15" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8282,6 +8511,680 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>画面</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>テスト観点</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>テスト項目</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>前提条件</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>操作手順</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>期待結果</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>SK02-001</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>昇格レビュー画面</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>画面表示</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>画面が正常表示（全 UI 要素・モック準拠）</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>1. 昇格レビュー を開く</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>SK02-002</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>昇格レビュー画面</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>視覚忠実度</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>配色/角丸/タイポが design token 準拠</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面を目視</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>SK02-003</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>昇格レビュー画面</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>データ取得</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>loading skeleton 表示（昇格候補）</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>取得未完</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>1. 昇格レビュー を開き取得完了前を観察</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>SK02-004</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>昇格レビュー画面</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>空データ</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>0 件時の空状態（昇格候補）</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>/knowledge/promotions が空配列</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1. データ0件で開く</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>空状態メッセージを表示（/undefined 参照にならない）</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>SK02-005</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>昇格レビュー画面</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>取得失敗の inline error + toast（昇格候補）</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>/knowledge/promotions が 5xx</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1. API を でモックし開く</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>エラー表示 の inline error 表示 かつ toast 発火</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>SK02-007</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>昇格レビュー画面</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>「承認」を操作すると動作する（ボタンが正しく動作するか）</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. 「承認」をクリック</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>昇格処理→楽観除外（onClick/href/API が実在し、押すと副作用が起きる）</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>SK02-008</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>昇格レビュー画面</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>「却下」を操作すると動作する（ボタンが正しく動作するか）</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>1. 「却下」をクリック</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>却下 API 無し→クライアント側 dismiss（onClick/href/API が実在し、押すと副作用が起きる）</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>SK02-009</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>昇格レビュー画面</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>楽観更新</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>承認: 成功で即時反映</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>対象が存在</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>1. 承認 を実行</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>昇格承認 呼び出し前にUIへ楽観反映→成功で確定（別GET再取得で反映）</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>SK02-010</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>昇格レビュー画面</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>楽観更新</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>承認: 失敗でロールバック</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>サーバ 4xx/5xx</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>1. 承認 を実行しAPIが失敗</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>楽観反映が元に戻り、inline error + toast を表示</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>SK02-011</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>昇格レビュー画面</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>承認: API 失敗時 inline error + toast</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>接続失敗/レート</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>1. 承認 を失敗させる</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>エラー表示 + toast、状態は不整合にならない</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>SK02-012</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>昇格レビュー画面</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>受容差分</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>却下はクライアント dismiss</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>1. 却下</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>reject API 無しのため一覧から即時除去(honest)</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>SK02-013</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>昇格レビュー画面</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>読み上げ対応</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>axe scan で 0 critical/serious</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>1. axe を実行</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>critical/serious 違反 0（semantic role/aria）</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>SK02-015</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>昇格レビュー画面</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>状態永続</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>F5 リロードでログアウトに飛ばない</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>ログイン済</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面で F5</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>保護ガードで維持・状態復元（URL クエリ等）</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>SK02-016</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>昇格レビュー画面</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>到達性</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -9036,7 +9939,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9667,7 +10570,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10163,609 +11066,6 @@
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="7" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>画面</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>テスト観点</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>テスト項目</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>前提条件</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>操作手順</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>期待結果</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>結果</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>SM01-001</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>議事録アップロード画面</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>画面表示</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>画面が正常表示（全 UI 要素・モック準拠）</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>1. 議事録アップロード を開く</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I2" s="4" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>SM01-002</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>議事録アップロード画面</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>視覚忠実度</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>配色/角丸/タイポが design token 準拠</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>1. 画面を目視</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>SM01-003</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>議事録アップロード画面</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>データ取得</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>loading skeleton 表示（状態ポーリング）</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>取得未完</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>1. 議事録アップロード を開き取得完了前を観察</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>SM01-004</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>議事録アップロード画面</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>空データ</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>0 件時の空状態（状態ポーリング）</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>/meetings/{id} が空配列</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>1. データ0件で開く</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>空状態メッセージを表示（/undefined 参照にならない）</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>SM01-005</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>議事録アップロード画面</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>エラー</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>取得失敗の inline error + toast（状態ポーリング）</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>/meetings/{id} が 5xx</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>1. API を でモックし開く</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>エラー表示 の inline error 表示 かつ toast 発火</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr"/>
-      <c r="I6" s="3" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>SM01-007</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>議事録アップロード画面</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>インタラクション</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>「ファイル選択」を操作すると動作する（ボタンが正しく動作するか）</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>1. 「ファイル選択」を選択</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>署名URL発行→実PUT→登録→transcribe キュー→polling→本文表示（onClick/href/API が実在し、押すと副作用が起きる）</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>SM01-008</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>議事録アップロード画面</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>アップロード→transcription: 送信→反映</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>必須入力済</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>1. アップロード→transcription を実行</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>upload-url→→ /meetings→transcribe→poll→transcript-url 呼び出し→成功表示→別GET/DBに反映</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>SM01-009</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>議事録アップロード画面</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>エラー</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>アップロード→transcription: API 失敗時 inline error + toast</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>接続失敗/レート</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>1. アップロード→transcription を失敗させる</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>エラー表示 + toast、状態は不整合にならない</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>SM01-010</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>議事録アップロード画面</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>G3実副作用</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>実 storage/Whisper 副作用(BLOCKED)</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>実DB/実storage</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>1. 実ファイルをアップロード</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>storage にオブジェクト作成・parse_result_path 生成を実API照会で確認</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr"/>
-      <c r="I10" s="3" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>SM01-011</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>議事録アップロード画面</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>マルチターン</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>queued→parsing→done の状態継続</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>アップロード後</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>1. 完了までポーリングを観察</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>parsed_at/parse_error まで状態が継続遷移し本文取得</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr"/>
-      <c r="I11" s="3" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>SM01-012</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>議事録アップロード画面</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>読み上げ対応</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>axe scan で 0 critical/serious</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>1. axe を実行</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>critical/serious 違反 0（semantic role/aria）</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>SM01-014</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>議事録アップロード画面</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>状態永続</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>F5 リロードでログアウトに飛ばない</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>ログイン済</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>1. 画面で F5</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>保護ガードで維持・状態復元（URL クエリ等）</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I13" s="4" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>SM01-015</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>議事録アップロード画面</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>到達性</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I14" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10842,12 +11142,12 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>SO01-001</t>
+          <t>SM01-001</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>自動スケジュール(cron)画面</t>
+          <t>議事録アップロード画面</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -10867,7 +11167,7 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>1. 自動スケジュール(cron) を開く</t>
+          <t>1. 議事録アップロード を開く</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
@@ -10885,12 +11185,12 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>SO01-002</t>
+          <t>SM01-002</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>自動スケジュール(cron)画面</t>
+          <t>議事録アップロード画面</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -10926,143 +11226,131 @@
       <c r="I3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>SO01-003</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>自動スケジュール(cron)画面</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>SM01-003</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>議事録アップロード画面</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>データ取得</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>loading skeleton 表示（スケジュール一覧）</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>loading skeleton 表示（状態ポーリング）</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>取得未完</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>1. 自動スケジュール(cron) を開き取得完了前を観察</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>1. 議事録アップロード を開き取得完了前を観察</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr"/>
+      <c r="I4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>SO01-004</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>自動スケジュール(cron)画面</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>SM01-004</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>議事録アップロード画面</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>空データ</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>0 件時の空状態（スケジュール一覧）</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>/cron-schedules?project_id が空配列</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>0 件時の空状態（状態ポーリング）</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>/meetings/{id} が空配列</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>1. データ0件で開く</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>空状態メッセージを表示（/undefined 参照にならない）</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>SO01-005</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>自動スケジュール(cron)画面</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>SM01-005</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>議事録アップロード画面</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>エラー</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>取得失敗の inline error + toast（スケジュール一覧）</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>/cron-schedules?project_id が 5xx</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>取得失敗の inline error + toast（状態ポーリング）</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>/meetings/{id} が 5xx</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>1. API を でモックし開く</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>エラー表示 の inline error 表示 かつ toast 発火</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr"/>
+      <c r="I6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>SO01-007</t>
+          <t>SM01-007</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>自動スケジュール(cron)画面</t>
+          <t>議事録アップロード画面</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -11072,7 +11360,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>「有効/無効トグル」を操作すると動作する（ボタンが正しく動作するか）</t>
+          <t>「ファイル選択」を操作すると動作する（ボタンが正しく動作するか）</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -11082,12 +11370,12 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>1. 「有効/無効トグル」をクリック</t>
+          <t>1. 「ファイル選択」を選択</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>enabled(楽観トグル)（onClick/href/API が実在し、押すと副作用が起きる）</t>
+          <t>署名URL発行→実PUT→登録→transcribe キュー→polling→本文表示（onClick/href/API が実在し、押すと副作用が起きる）</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -11098,186 +11386,170 @@
       <c r="I7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>SO01-008</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>自動スケジュール(cron)画面</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>楽観更新</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>有効トグル: 成功で即時反映</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>対象が存在</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>1. 有効トグル を実行</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>/cron-schedules/{id} 呼び出し前にUIへ楽観反映→成功で確定（別GET再取得で反映）</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="inlineStr"/>
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>SM01-008</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>議事録アップロード画面</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>アップロード→transcription: 送信→反映</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>必須入力済</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>1. アップロード→transcription を実行</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>upload-url→→ /meetings→transcribe→poll→transcript-url 呼び出し→成功表示→別GET/DBに反映</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr"/>
+      <c r="I8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>SO01-009</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>自動スケジュール(cron)画面</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>楽観更新</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>有効トグル: 失敗でロールバック</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>サーバ 4xx/5xx</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>1. 有効トグル を実行しAPIが失敗</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>楽観反映が元に戻り、inline error + toast を表示</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr"/>
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>SM01-009</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>議事録アップロード画面</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>アップロード→transcription: API 失敗時 inline error + toast</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>接続失敗/レート</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>1. アップロード→transcription を失敗させる</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>エラー表示 + toast、状態は不整合にならない</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>SO01-010</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>自動スケジュール(cron)画面</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>エラー</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>有効トグル: API 失敗時 inline error + toast</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>接続失敗/レート</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>1. 有効トグル を失敗させる</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>エラー表示 + toast、状態は不整合にならない</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr"/>
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>SM01-010</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>議事録アップロード画面</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>G3実副作用</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>実 storage/Whisper 副作用(BLOCKED)</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>実DB/実storage</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>1. 実ファイルをアップロード</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>storage にオブジェクト作成・parse_result_path 生成を実API照会で確認</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr"/>
+      <c r="I10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>SO01-011</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>自動スケジュール(cron)画面</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>受容差分</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>即時実行ボタンは非表示</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>1. 一覧確認</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>run-now API 無しのため列非表示(honest)</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr"/>
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>SM01-011</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>議事録アップロード画面</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>マルチターン</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>queued→parsing→done の状態継続</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>アップロード後</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>1. 完了までポーリングを観察</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>parsed_at/parse_error まで状態が継続遷移し本文取得</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr"/>
+      <c r="I11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>SO01-012</t>
+          <t>SM01-012</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>自動スケジュール(cron)画面</t>
+          <t>議事録アップロード画面</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -11315,12 +11587,12 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>SO01-014</t>
+          <t>SM01-014</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>自動スケジュール(cron)画面</t>
+          <t>議事録アップロード画面</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -11358,12 +11630,12 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>SO01-015</t>
+          <t>SM01-015</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>自動スケジュール(cron)画面</t>
+          <t>議事録アップロード画面</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -11404,6 +11676,637 @@
 </file>
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>画面</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>テスト観点</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>テスト項目</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>前提条件</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>操作手順</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>期待結果</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>SO01-001</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)画面</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>画面表示</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>画面が正常表示（全 UI 要素・モック準拠）</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>1. 自動スケジュール(cron) を開く</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>SO01-002</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)画面</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>視覚忠実度</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>配色/角丸/タイポが design token 準拠</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面を目視</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>SO01-003</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)画面</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>データ取得</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>loading skeleton 表示（スケジュール一覧）</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>取得未完</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>1. 自動スケジュール(cron) を開き取得完了前を観察</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>SO01-004</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)画面</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>空データ</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>0 件時の空状態（スケジュール一覧）</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>/cron-schedules?project_id が空配列</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1. データ0件で開く</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>空状態メッセージを表示（/undefined 参照にならない）</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>SO01-005</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)画面</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>取得失敗の inline error + toast（スケジュール一覧）</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>/cron-schedules?project_id が 5xx</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1. API を でモックし開く</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>エラー表示 の inline error 表示 かつ toast 発火</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>SO01-007</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)画面</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>「有効/無効トグル」を操作すると動作する（ボタンが正しく動作するか）</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. 「有効/無効トグル」をクリック</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>enabled(楽観トグル)（onClick/href/API が実在し、押すと副作用が起きる）</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>SO01-008</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)画面</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>楽観更新</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>有効トグル: 成功で即時反映</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>対象が存在</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>1. 有効トグル を実行</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>/cron-schedules/{id} 呼び出し前にUIへ楽観反映→成功で確定（別GET再取得で反映）</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>SO01-009</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)画面</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>楽観更新</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>有効トグル: 失敗でロールバック</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>サーバ 4xx/5xx</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>1. 有効トグル を実行しAPIが失敗</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>楽観反映が元に戻り、inline error + toast を表示</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>SO01-010</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)画面</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>有効トグル: API 失敗時 inline error + toast</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>接続失敗/レート</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>1. 有効トグル を失敗させる</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>エラー表示 + toast、状態は不整合にならない</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>SO01-011</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)画面</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>受容差分</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>即時実行ボタンは非表示</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>1. 一覧確認</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>run-now API 無しのため列非表示(honest)</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>SO01-012</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)画面</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>読み上げ対応</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>axe scan で 0 critical/serious</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>1. axe を実行</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>critical/serious 違反 0（semantic role/aria）</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>SO01-014</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)画面</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>状態永続</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>F5 リロードでログアウトに飛ばない</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>ログイン済</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面で F5</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>保護ガードで維持・状態復元（URL クエリ等）</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>SO01-015</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)画面</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>到達性</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11991,7 +12894,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12788,465 +13691,6 @@
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="7" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>画面</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>テスト観点</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>テスト項目</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>前提条件</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>操作手順</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>期待結果</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>結果</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-001</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替画面</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>画面表示</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>画面が正常表示（全 UI 要素・モック準拠）</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>1. ワークスペース切替 を開く</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I2" s="4" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-002</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替画面</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>視覚忠実度</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>配色/角丸/タイポが design token 準拠</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>1. 画面を目視</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-003</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替画面</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>データ取得</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>loading skeleton 表示（所属 WS 一覧）</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>取得未完</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>1. ワークスペース切替 を開き取得完了前を観察</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-004</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替画面</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>空データ</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>0 件時の空状態（所属 WS 一覧）</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>/workspaces が空配列</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>1. データ0件で開く</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>空状態メッセージを表示（/undefined 参照にならない）</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-005</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替画面</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>エラー</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>取得失敗の inline error + toast（所属 WS 一覧）</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>/workspaces が 5xx</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>1. API を でモックし開く</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>エラー表示 の inline error 表示 かつ toast 発火</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-007</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替画面</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>インタラクション</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>「WS picker」を操作すると動作する（ボタンが正しく動作するか）</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>1. 「WS picker」を選択</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>localStorage(atelier_current_workspace) 永続化（onClick/href/API が実在し、押すと副作用が起きる）</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-008</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替画面</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>読み上げ対応</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>axe scan で 0 critical/serious</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>1. axe を実行</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>critical/serious 違反 0（semantic role/aria）</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-010</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替画面</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>状態永続</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>F5 リロードでログアウトに飛ばない</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>ログイン済</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>1. 画面で F5</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>保護ガードで維持・状態復元（URL クエリ等）</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-011</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替画面</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>到達性</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13323,12 +13767,12 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>TUC39-001</t>
+          <t>TUC38-001</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替画面</t>
+          <t>ワークスペース切替画面</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -13348,7 +13792,7 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>1. プロジェクト切替 を開く</t>
+          <t>1. ワークスペース切替 を開く</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
@@ -13366,12 +13810,12 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>TUC39-002</t>
+          <t>TUC38-002</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替画面</t>
+          <t>ワークスペース切替画面</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -13409,12 +13853,12 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>TUC39-003</t>
+          <t>TUC38-003</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替画面</t>
+          <t>ワークスペース切替画面</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -13424,7 +13868,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>loading skeleton 表示（現在WS内プロジェクト）</t>
+          <t>loading skeleton 表示（所属 WS 一覧）</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -13434,7 +13878,7 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>1. プロジェクト切替 を開き取得完了前を観察</t>
+          <t>1. ワークスペース切替 を開き取得完了前を観察</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
@@ -13452,12 +13896,12 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>TUC39-004</t>
+          <t>TUC38-004</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替画面</t>
+          <t>ワークスペース切替画面</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -13467,12 +13911,12 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>0 件時の空状態（現在WS内プロジェクト）</t>
+          <t>0 件時の空状態（所属 WS 一覧）</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>/projects?workspace_id が空配列</t>
+          <t>/workspaces が空配列</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -13495,12 +13939,12 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>TUC39-005</t>
+          <t>TUC38-005</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替画面</t>
+          <t>ワークスペース切替画面</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -13510,12 +13954,12 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>取得失敗の inline error + toast（現在WS内プロジェクト）</t>
+          <t>取得失敗の inline error + toast（所属 WS 一覧）</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>/projects?workspace_id が 5xx</t>
+          <t>/workspaces が 5xx</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -13538,12 +13982,12 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>TUC39-007</t>
+          <t>TUC38-007</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替画面</t>
+          <t>ワークスペース切替画面</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -13553,7 +13997,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>「Project picker」を操作すると動作する（ボタンが正しく動作するか）</t>
+          <t>「WS picker」を操作すると動作する（ボタンが正しく動作するか）</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -13563,12 +14007,12 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>1. 「Project picker」を選択</t>
+          <t>1. 「WS picker」を選択</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>localStorage(atelier_current_project) 永続化（onClick/href/API が実在し、押すと副作用が起きる）</t>
+          <t>localStorage(atelier_current_workspace) 永続化（onClick/href/API が実在し、押すと副作用が起きる）</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -13581,12 +14025,12 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>TUC39-008</t>
+          <t>TUC38-008</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替画面</t>
+          <t>ワークスペース切替画面</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -13624,12 +14068,12 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>TUC39-010</t>
+          <t>TUC38-010</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替画面</t>
+          <t>ワークスペース切替画面</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -13667,12 +14111,12 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>TUC39-011</t>
+          <t>TUC38-011</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替画面</t>
+          <t>ワークスペース切替画面</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -13718,7 +14162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -13782,12 +14226,12 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>TUC40-001</t>
+          <t>TUC39-001</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>グローバル検索画面</t>
+          <t>プロジェクト切替画面</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -13807,7 +14251,7 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>1. グローバル検索 を開く</t>
+          <t>1. プロジェクト切替 を開く</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
@@ -13825,12 +14269,12 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>TUC40-002</t>
+          <t>TUC39-002</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>グローバル検索画面</t>
+          <t>プロジェクト切替画面</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -13868,12 +14312,12 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>TUC40-003</t>
+          <t>TUC39-003</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>グローバル検索画面</t>
+          <t>プロジェクト切替画面</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -13883,7 +14327,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>loading skeleton 表示（横断検索）</t>
+          <t>loading skeleton 表示（現在WS内プロジェクト）</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -13893,7 +14337,7 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>1. グローバル検索 を開き取得完了前を観察</t>
+          <t>1. プロジェクト切替 を開き取得完了前を観察</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
@@ -13911,12 +14355,12 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>TUC40-004</t>
+          <t>TUC39-004</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>グローバル検索画面</t>
+          <t>プロジェクト切替画面</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -13926,12 +14370,12 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>0 件時の空状態（横断検索）</t>
+          <t>0 件時の空状態（現在WS内プロジェクト）</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>/search?q=&amp;kind= が空配列</t>
+          <t>/projects?workspace_id が空配列</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -13954,12 +14398,12 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>TUC40-005</t>
+          <t>TUC39-005</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>グローバル検索画面</t>
+          <t>プロジェクト切替画面</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -13969,12 +14413,12 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>取得失敗の inline error + toast（横断検索）</t>
+          <t>取得失敗の inline error + toast（現在WS内プロジェクト）</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>/search?q=&amp;kind= が 5xx</t>
+          <t>/projects?workspace_id が 5xx</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -13997,22 +14441,22 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>TUC40-007</t>
+          <t>TUC39-007</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>グローバル検索画面</t>
+          <t>プロジェクト切替画面</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>入力フォーム</t>
+          <t>インタラクション</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>初期値/placeholder（キーワード）</t>
+          <t>「Project picker」を操作すると動作する（ボタンが正しく動作するか）</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -14022,12 +14466,12 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>1. フォームを開く</t>
+          <t>1. 「Project picker」を選択</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>キーワード の初期値/placeholder が正しい</t>
+          <t>localStorage(atelier_current_project) 永続化（onClick/href/API が実在し、押すと副作用が起きる）</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -14040,22 +14484,22 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>TUC40-008</t>
+          <t>TUC39-008</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>グローバル検索画面</t>
+          <t>プロジェクト切替画面</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>バリデーション</t>
+          <t>読み上げ対応</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>キーワード: 必須(空で未検索)</t>
+          <t>axe scan で 0 critical/serious</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -14065,12 +14509,12 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>1. キーワード に不正値/未入力を入れる</t>
+          <t>1. axe を実行</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>エラー表示 かつ 送信ボタン無効</t>
+          <t>critical/serious 違反 0（semantic role/aria）</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -14083,37 +14527,37 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>TUC40-009</t>
+          <t>TUC39-010</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>グローバル検索画面</t>
+          <t>プロジェクト切替画面</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>インタラクション</t>
+          <t>状態永続</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>「種別フィルタ(all/project/task/knowledge/employee)」を操作すると動作する（ボタンが正しく動作するか）</t>
+          <t>F5 リロードでログアウトに飛ばない</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>ログイン済</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>1. 「種別フィルタ(all/project/task/knowledge/employee)」を各クリック</t>
+          <t>1. 画面で F5</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>kind を切替して再検索（onClick/href/API が実在し、押すと副作用が起きる）</t>
+          <t>保護ガードで維持・状態復元（URL クエリ等）</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -14126,22 +14570,22 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>TUC40-010</t>
+          <t>TUC39-011</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>グローバル検索画面</t>
+          <t>プロジェクト切替画面</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>インタラクション</t>
+          <t>到達性</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>「検索入力」を操作すると動作する（ボタンが正しく動作するか）</t>
+          <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -14151,12 +14595,12 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>1. 「検索入力」を入力(debounce)</t>
+          <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>/search を叩き結果を種別ラベル付きで表示（onClick/href/API が実在し、押すと副作用が起きる）</t>
+          <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -14165,178 +14609,6 @@
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>TUC40-011</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>グローバル検索画面</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>R-T08</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>他人のデータが見えない権限 で可視性担保</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>1. 検索実行</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>他人のデータが見えない権限 内のみヒット(越境自動除外)</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>TUC40-012</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>グローバル検索画面</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>読み上げ対応</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>axe scan で 0 critical/serious</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>1. axe を実行</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>critical/serious 違反 0（semantic role/aria）</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>TUC40-014</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>グローバル検索画面</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>状態永続</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>F5 リロードでログアウトに飛ばない</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>ログイン済</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>1. 画面で F5</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>保護ガードで維持・状態復元（URL クエリ等）</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I13" s="4" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>TUC40-015</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>グローバル検索画面</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>到達性</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I14" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15103,6 +15375,637 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>画面</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>テスト観点</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>テスト項目</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>前提条件</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>操作手順</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>期待結果</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>TUC40-001</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>グローバル検索画面</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>画面表示</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>画面が正常表示（全 UI 要素・モック準拠）</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>1. グローバル検索 を開く</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>TUC40-002</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>グローバル検索画面</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>視覚忠実度</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>配色/角丸/タイポが design token 準拠</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面を目視</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>TUC40-003</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>グローバル検索画面</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>データ取得</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>loading skeleton 表示（横断検索）</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>取得未完</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>1. グローバル検索 を開き取得完了前を観察</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>TUC40-004</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>グローバル検索画面</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>空データ</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>0 件時の空状態（横断検索）</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>/search?q=&amp;kind= が空配列</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1. データ0件で開く</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>空状態メッセージを表示（/undefined 参照にならない）</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>TUC40-005</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>グローバル検索画面</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>取得失敗の inline error + toast（横断検索）</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>/search?q=&amp;kind= が 5xx</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1. API を でモックし開く</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>エラー表示 の inline error 表示 かつ toast 発火</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>TUC40-007</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>グローバル検索画面</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>入力フォーム</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>初期値/placeholder（キーワード）</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. フォームを開く</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>キーワード の初期値/placeholder が正しい</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>TUC40-008</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>グローバル検索画面</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>バリデーション</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>キーワード: 必須(空で未検索)</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>1. キーワード に不正値/未入力を入れる</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>エラー表示 かつ 送信ボタン無効</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>TUC40-009</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>グローバル検索画面</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>「種別フィルタ(all/project/task/knowledge/employee)」を操作すると動作する（ボタンが正しく動作するか）</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>1. 「種別フィルタ(all/project/task/knowledge/employee)」を各クリック</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>kind を切替して再検索（onClick/href/API が実在し、押すと副作用が起きる）</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>TUC40-010</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>グローバル検索画面</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>「検索入力」を操作すると動作する（ボタンが正しく動作するか）</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>1. 「検索入力」を入力(debounce)</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>/search を叩き結果を種別ラベル付きで表示（onClick/href/API が実在し、押すと副作用が起きる）</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>TUC40-011</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>グローバル検索画面</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>R-T08</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>他人のデータが見えない権限 で可視性担保</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>1. 検索実行</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>他人のデータが見えない権限 内のみヒット(越境自動除外)</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>TUC40-012</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>グローバル検索画面</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>読み上げ対応</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>axe scan で 0 critical/serious</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>1. axe を実行</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>critical/serious 違反 0（semantic role/aria）</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>TUC40-014</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>グローバル検索画面</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>状態永続</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>F5 リロードでログアウトに飛ばない</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>ログイン済</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面で F5</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>保護ガードで維持・状態復元（URL クエリ等）</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>TUC40-015</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>グローバル検索画面</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>到達性</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -17346,6 +18249,895 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>画面</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>テスト観点</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>テスト項目</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>前提条件</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>操作手順</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>期待結果</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>SB04-001</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト・シークレット画面</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>画面表示</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>主要領域 (注意書き/新規追加/一覧) がモック準拠で表示</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>project 選択済</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>1. サイドバー「シークレット」から開く</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>secure-note (amber)・フォーム・一覧テーブルが揃う</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>SB04-002</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト・シークレット画面</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>登録・編集</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>フォームから作成 → 一覧反映</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>1. 名称/種別/値を入力 2. 暗号化して保存</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>→ 一覧に新行 (別 再取得)</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>SB04-003</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト・シークレット画面</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>整合性</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>DB は暗号化保存・平文を含まない</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>作成直後</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>1. psql で encrypted_value を確認</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Fernet 暗号文のみ・平文部分文字列なし・last4 記録</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>SB04-004</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト・シークレット画面</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>画面表示</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>一覧の値はマスク (••••••••last4)</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1. 一覧を目視</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>平文は出ない</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>SB04-005</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト・シークレット画面</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>画面表示</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>作成者列に実ユーザー名</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1. 一覧を目視</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>created_by → users.display_name (契約拡張 v2)</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>SB04-006</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト・シークレット画面</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>画面表示</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>作成日が YYYY-MM-DD (生 ISO 露出なし)</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. 一覧を目視</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>人間可読の日付 (鉄則5)</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>SB04-007</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト・シークレット画面</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>「表示」→ 復号平文が一時表示</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>1. 表示をクリック</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>reveal API → 平文 + コピー/隠す</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>SB04-008</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト・シークレット画面</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>整合性</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>reveal が監査ログに記録される</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>1. 表示 2. psql audit_logs</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>action=credential.reveal が +1</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>SB04-009</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト・シークレット画面</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>「隠す」でマスクへ復帰 (平文を保持しない)</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>表示中</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>1. 隠すをクリック</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>マスク表示へ戻る</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>SB04-010</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト・シークレット画面</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>reveal 失敗時に明示エラー (握り潰さない)</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>API 5xx/</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>1. 失敗させる</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>エラー表示「復号に失敗しました…」</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>SB04-012</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト・シークレット画面</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>削除は 2 段階確認</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>1. ゴミ箱 → 削除する</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>1 クリック目は確認のみ。確定で</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>SB04-013</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト・シークレット画面</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>整合性</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>削除確定 → 一覧から消え DB soft-delete</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>1. 削除確定 2. psql</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>deleted_at セット・一覧再取得で消滅</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>SB04-014</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト・シークレット画面</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>バリデーション</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>名称/値の必須チェック</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>1. 空のまま保存</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>「名前と値は必須です。」・ 不発</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>SB04-015</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト・シークレット画面</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>入力フォーム</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>既定種別=トークン (モック準拠)・成功後は全欄クリア</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>1. 送信成功後を目視</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>値を画面に残さない (機密)</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>SB04-016</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト・シークレット画面</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>保存失敗時に エラー表示</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>4xx/5xx</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>1. 失敗させる</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>エラーメッセージ表示・入力は保持</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>SB04-017</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト・シークレット画面</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>空データ</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>0 件時の空状態</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>0 件</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>1. 空の project で開く</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>「まだ何も保管されていません。」</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>SB04-018</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト・シークレット画面</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>スマホ・タブレットでも崩れない</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>390/768/1440 で崩れず操作可能</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>1. 各幅で開き入力</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>body 横スクロール無し (表は自前スクロール)・フォーム操作可</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>SB04-019</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト・シークレット画面</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>project 未指定は明示メッセージ</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>?project= なし</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>1. /projects/vault 直接</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>「プロジェクトが指定されていません。」</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>SB04-020</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト・シークレット画面</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>状態永続</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>で signin へ誘導</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>未ログイン</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>1. cookie なしで開く</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>/signin?redirect=... へ</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -17842,7 +19634,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -18557,893 +20349,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="7" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>画面</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>テスト観点</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>テスト項目</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>前提条件</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>操作手順</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>期待結果</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>結果</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>SE01-001</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>チャット画面</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>画面表示</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>3ペイン構成が正常表示（モック S-E01-thread.html 準拠: 左260px スレッド/中央チャット/右340px コンテキスト）</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>ログイン済+スレッド有</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>1. /chat を開く</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>3ペインが描画され、モックの主要領域(スレッド検索/新規スレッド/工程グルーピング/工程文脈バー/社員ヘッダー/コンポーザ/右タブ)が全て存在</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I2" s="4" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>SE01-002</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>チャット画面</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>視覚忠実度</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>配色/角丸/タイポが design token 準拠</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>1. 画面を目視</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>--color-*/--rounded-* トークン準拠・社員カラーはモック avatar-* 準拠</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>SE01-003</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>チャット画面</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>データ取得</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>スレッド一覧が実 API ( /chat/threads?project_id) から描画</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>1. 開いて一覧を確認</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>実スレッドが工程グルーピング(現在→完了→横断)で表示・message_count/相対時刻付き</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>SE01-004</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>チャット画面</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>空データ</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>スレッド0件時の空状態</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>スレッド0件</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>1. 空プロジェクトで開く</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>「スレッドがありません…」の empty state ( にならない)</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>SE01-005</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>チャット画面</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>エラー</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>送信失敗時のエラーバナー(単一・dismiss可)</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>LLM 未設定 or API 5xx</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>1. メッセージ送信</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>コンポーザ直上に エラー表示 バナー1箇所のみ・✕で閉じる・スレッド切替でリセット</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>SE01-006</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>チャット画面</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>インタラクション</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>スレッド検索フィルタ（ボタンが正しく動作するか）</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>スレッド複数</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>1. 検索欄に「競合」入力</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>タイトル/社員名/最終メッセージで絞り込まれる</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>SE01-007</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>チャット画面</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>インタラクション</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>スレッド切替・新規スレッド作成（ボタンが正しく動作するか）</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>1. 別スレッドをクリック 2. 新規スレッドで作成</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>メッセージが切替わる/ /chat/threads (phase_id 任意) で作成され選択される</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>SE01-008</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>チャット画面</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>インタラクション</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>ペイン開閉トグル（ボタンが正しく動作するか）</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>1. 左右トグルを各クリック</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>左ペイン/右ペインが開閉し grid が追従・aria-pressed 反映</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>SE01-009</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>チャット画面</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>インタラクション</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>メッセージ送信 (Enter=送信 / Shift+Enter=改行 / IME 変換中は送信しない)</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>スレッド選択済</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>1. 入力して Enter</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>user バブル即時表示→SSE 応答 (LLM 無環境では誠実なエラー表示)・IME 変換確定 Enter で誤送信しない</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>SE01-010</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>チャット画面</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>インタラクション</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>@メンション ピッカー（ボタンが正しく動作するか）</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>AI 社員複数</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>1. @メンション をクリック 2. 社員を選択</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>実 AI 社員一覧(対話相手は除外)が出て、カーソル位置に「@名前 」が挿入される</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>SE01-011</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>チャット画面</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>インタラクション</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>ナレッジ参照ピッカー（ボタンが正しく動作するか）</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>1. ナレッジ参照をクリック</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>実ナレッジ一覧から選択で「[ナレッジ: title] 」挿入。0件時は「まだありません+自動RAGは常時有効」の誠実表示</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>SE01-012</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>チャット画面</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>死に要素ゼロ</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>コンポーザに非機能ボタンが存在しない</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>1. コンポーザの全ボタンを列挙</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>添付・/コマンドのボタンは**描画されない**(gap tracker 起票済)。表示される全ボタンが機能する</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I13" s="4" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>SE01-013</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>チャット画面</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>表示</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>tool ロールメッセージのツールカード描画</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>tool メッセージ有</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>1. 該当スレッドを開く</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>monospace ツール名ヘッダ+本文カード (モック .tool-card 準拠)</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I14" s="4" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>SE01-014</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>チャット画面</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>表示</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>工程文脈バー (現在の工程・Stage n/9・工程画面リンク)</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>1. ヘッダーを確認 2. リンクをクリック</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>実 current_phase を表示し /workflow?project= へ遷移</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I15" s="4" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>SE01-015</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>チャット画面</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>表示</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>右ペイン: 主力決定/コンテキスト/参照タブ</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>decisions 有</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>1. 各タブをクリック</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>実 /decisions の確定カード(反映先付)・F-CTX01 実測値(SSE context)・実 /knowledge 一覧</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I16" s="4" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>SE01-016</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>チャット画面</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>履歴</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>リロードで会話が消えない (既存メッセージロード)</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>メッセージ有</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>1. F5</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>過去メッセージが created_at 付きで再表示</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I17" s="4" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>SE01-017</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>チャット画面</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>スマホ・タブレットでも崩れない</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>390/768/1440 で崩れない・モバイルは一覧⇄チャット切替</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>1. 各幅で開く 2. モバイルで戻るボタン</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>横スクロール無し・モバイルで戻る→一覧表示・右ペインは重ね表示トグル</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I18" s="4" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>SE01-018</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>チャット画面</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>読み上げ対応</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>axe 0 critical/serious・log role/aria-live/label 契約</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>1. axe 実行</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t>違反0・role=log aria-live=polite・「メッセージを入力」label</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I19" s="4" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>SE01-020</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>チャット画面</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>状態永続</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>?thread= URL で直接スレッドを開ける</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>1. /chat?thread=&lt;id&gt; を開く</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>該当スレッドが選択状態で開く</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I20" s="4" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/apps/web/.qa/テスト仕様書_クライアント版.xlsx
+++ b/apps/web/.qa/テスト仕様書_クライアント版.xlsx
@@ -31,12 +31,13 @@
     <sheet name="クライアントサインイン" sheetId="22" state="visible" r:id="rId22"/>
     <sheet name="クライアントプロジェクトビュー" sheetId="23" state="visible" r:id="rId23"/>
     <sheet name="議事録アップロード" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="自動スケジュール(cron)" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="通知センター" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="プロフィール" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="ワークスペース切替" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="プロジェクト切替" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="グローバル検索" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="商談ドラフト" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="自動スケジュール(cron)" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="通知センター" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="プロフィール" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="ワークスペース切替" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="プロジェクト切替" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="グローバル検索" sheetId="31" state="visible" r:id="rId31"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -491,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -841,59 +842,59 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>自動スケジュール(cron)画面</t>
+          <t>商談ドラフト画面</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>通知センター画面</t>
+          <t>自動スケジュール(cron)画面</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>プロフィール画面</t>
+          <t>通知センター画面</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>ワークスペース切替画面</t>
+          <t>プロフィール画面</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>プロジェクト切替画面</t>
+          <t>ワークスペース切替画面</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
@@ -906,29 +907,42 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
+          <t>プロジェクト切替画面</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
           <t>グローバル検索画面</t>
         </is>
       </c>
-      <c r="B33" s="3" t="n">
+      <c r="B34" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="C33" s="3" t="n">
+      <c r="C34" s="3" t="n">
         <v>13</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="3" t="n"/>
-      <c r="B34" s="3" t="n"/>
-      <c r="C34" s="3" t="n"/>
-    </row>
     <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>完全性: 全469件 ＝ クライアント可視404件 ＋ 技術専用65件（画面で見えない裏取り=エンジニア版）</t>
-        </is>
-      </c>
+      <c r="A35" s="3" t="n"/>
       <c r="B35" s="3" t="n"/>
       <c r="C35" s="3" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>完全性: 全485件 ＝ クライアント可視420件 ＋ 技術専用65件（画面で見えない裏取り=エンジニア版）</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n"/>
+      <c r="C36" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11681,6 +11695,766 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>画面</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>テスト観点</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>テスト項目</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>前提条件</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>操作手順</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>期待結果</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>SN01-001</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>商談ドラフト画面</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>到達性</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>ナビ「営業ドラフト」から UI 到達できる</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>project 選択済</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>1. ダッシュボード → サイドバー営業ドラフト</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>/sales?project= に遷移し描画</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>SN01-002</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>商談ドラフト画面</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>種別タブ (提案書/見積書) が実タブとして切替わる</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>1. 見積書タブをクリック</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>aria-selected 遷移・一覧/フォーム見出しが追従</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>SN01-003</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>商談ドラフト画面</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>画面表示</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>タブ件数バッジが実データ</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>保存済みあり</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>1. タブを目視</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>/sales-docs の実件数</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>SN01-004</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>商談ドラフト画面</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>登録・編集</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>フォームから作成 → /sales-docs → プレビュー表示</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1. 顧客名/案件/概要 → ドラフト生成</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>doc_type=タブ追従で保存・article に本文</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>SN01-005</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>商談ドラフト画面</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>整合性</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>作成が DB (workflow_outputs stage=proposal/estimate) に永続</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1. psql 突合</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>stage/version が記録される</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>SN01-006</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>商談ドラフト画面</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>画面表示</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>保存済みドキュメント一覧 (版数 vN + 日付)</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>保存済みあり</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. サイドバーを目視</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>v1 等の版数と YYYY-MM-DD 表示</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>SN01-007</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>商談ドラフト画面</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>状態永続</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>リロード後も一覧から開き直せる</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>保存済みあり</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>1. F5 → 一覧クリック</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>本文がプレビューに出る</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>SN01-008</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>商談ドラフト画面</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>登録・編集</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>編集 → /sales-docs/{id} → DB 反映</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>ドキュメント選択中</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>1. 編集 → 本文変更 → 保存</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>summary が DB 更新・表示反映</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>SN01-009</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>商談ドラフト画面</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>削除は 2 段階確認 → DB 論理削除</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>1. ゴミ箱 → 削除する</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>1 クリック目は確認のみ。確定で deleted_at</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>SN01-010</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>商談ドラフト画面</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>到達性</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>「修正依頼」がチャットへの実リンク</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>1. href を検証</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>/chat?project={id}</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>SN01-011</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>商談ドラフト画面</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>受容差分</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>PDF/送信/送信履歴/参照ナレッジは未描画 (honest)</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面を目視</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>API 不在機能の偽装 UI が無い</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>SN01-012</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>商談ドラフト画面</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>バリデーション</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>必須 (顧客名/案件) + 概要 10 文字未満を拒否</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>1. 空/短文で生成</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>エラー表示・ 不発</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>SN01-013</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>商談ドラフト画面</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>一覧取得失敗時に エラー表示</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>5xx</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>1. 失敗させる</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>「一覧の取得に失敗しました。」</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>SN01-014</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>商談ドラフト画面</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>空データ</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>0 件時「まだドキュメントがありません。」</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>0 件</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>1. 空タブを目視</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>空状態表示 ( にならない)</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>SN01-015</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>商談ドラフト画面</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>スマホ・タブレットでも崩れない</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>390/768/1440 で崩れず操作可能</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>1. 各幅で開きタブ操作</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>横スクロール無し・タブ/フォーム操作可</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>SN01-016</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>商談ドラフト画面</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>受容差分</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>project 未選択時は案内メッセージ</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>?project= なし</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>1. /sales 直接</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>「プロジェクトを選択すると…」</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -12306,7 +13080,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12894,7 +13668,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13691,465 +14465,6 @@
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="7" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>画面</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>テスト観点</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>テスト項目</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>前提条件</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>操作手順</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>期待結果</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>結果</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-001</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替画面</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>画面表示</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>画面が正常表示（全 UI 要素・モック準拠）</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>1. ワークスペース切替 を開く</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I2" s="4" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-002</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替画面</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>視覚忠実度</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>配色/角丸/タイポが design token 準拠</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>1. 画面を目視</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-003</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替画面</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>データ取得</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>loading skeleton 表示（所属 WS 一覧）</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>取得未完</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>1. ワークスペース切替 を開き取得完了前を観察</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-004</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替画面</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>空データ</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>0 件時の空状態（所属 WS 一覧）</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>/workspaces が空配列</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>1. データ0件で開く</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>空状態メッセージを表示（/undefined 参照にならない）</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-005</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替画面</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>エラー</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>取得失敗の inline error + toast（所属 WS 一覧）</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>/workspaces が 5xx</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>1. API を でモックし開く</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>エラー表示 の inline error 表示 かつ toast 発火</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-007</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替画面</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>インタラクション</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>「WS picker」を操作すると動作する（ボタンが正しく動作するか）</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>1. 「WS picker」を選択</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>localStorage(atelier_current_workspace) 永続化（onClick/href/API が実在し、押すと副作用が起きる）</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-008</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替画面</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>読み上げ対応</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>axe scan で 0 critical/serious</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>1. axe を実行</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>critical/serious 違反 0（semantic role/aria）</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-010</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替画面</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>状態永続</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>F5 リロードでログアウトに飛ばない</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>ログイン済</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>1. 画面で F5</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>保護ガードで維持・状態復元（URL クエリ等）</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-011</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替画面</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>到達性</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -14226,12 +14541,12 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>TUC39-001</t>
+          <t>TUC38-001</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替画面</t>
+          <t>ワークスペース切替画面</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -14251,7 +14566,7 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>1. プロジェクト切替 を開く</t>
+          <t>1. ワークスペース切替 を開く</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
@@ -14269,12 +14584,12 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>TUC39-002</t>
+          <t>TUC38-002</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替画面</t>
+          <t>ワークスペース切替画面</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -14312,12 +14627,12 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>TUC39-003</t>
+          <t>TUC38-003</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替画面</t>
+          <t>ワークスペース切替画面</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -14327,7 +14642,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>loading skeleton 表示（現在WS内プロジェクト）</t>
+          <t>loading skeleton 表示（所属 WS 一覧）</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -14337,7 +14652,7 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>1. プロジェクト切替 を開き取得完了前を観察</t>
+          <t>1. ワークスペース切替 を開き取得完了前を観察</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
@@ -14355,12 +14670,12 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>TUC39-004</t>
+          <t>TUC38-004</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替画面</t>
+          <t>ワークスペース切替画面</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -14370,12 +14685,12 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>0 件時の空状態（現在WS内プロジェクト）</t>
+          <t>0 件時の空状態（所属 WS 一覧）</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>/projects?workspace_id が空配列</t>
+          <t>/workspaces が空配列</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -14398,12 +14713,12 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>TUC39-005</t>
+          <t>TUC38-005</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替画面</t>
+          <t>ワークスペース切替画面</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -14413,12 +14728,12 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>取得失敗の inline error + toast（現在WS内プロジェクト）</t>
+          <t>取得失敗の inline error + toast（所属 WS 一覧）</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>/projects?workspace_id が 5xx</t>
+          <t>/workspaces が 5xx</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -14441,12 +14756,12 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>TUC39-007</t>
+          <t>TUC38-007</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替画面</t>
+          <t>ワークスペース切替画面</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -14456,7 +14771,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>「Project picker」を操作すると動作する（ボタンが正しく動作するか）</t>
+          <t>「WS picker」を操作すると動作する（ボタンが正しく動作するか）</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -14466,12 +14781,12 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>1. 「Project picker」を選択</t>
+          <t>1. 「WS picker」を選択</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>localStorage(atelier_current_project) 永続化（onClick/href/API が実在し、押すと副作用が起きる）</t>
+          <t>localStorage(atelier_current_workspace) 永続化（onClick/href/API が実在し、押すと副作用が起きる）</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -14484,12 +14799,12 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>TUC39-008</t>
+          <t>TUC38-008</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替画面</t>
+          <t>ワークスペース切替画面</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -14527,12 +14842,12 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>TUC39-010</t>
+          <t>TUC38-010</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替画面</t>
+          <t>ワークスペース切替画面</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -14570,12 +14885,12 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>TUC39-011</t>
+          <t>TUC38-011</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替画面</t>
+          <t>ワークスペース切替画面</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -15381,6 +15696,465 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>画面</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>テスト観点</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>テスト項目</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>前提条件</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>操作手順</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>期待結果</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-001</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替画面</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>画面表示</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>画面が正常表示（全 UI 要素・モック準拠）</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>1. プロジェクト切替 を開く</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-002</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替画面</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>視覚忠実度</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>配色/角丸/タイポが design token 準拠</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面を目視</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-003</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替画面</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>データ取得</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>loading skeleton 表示（現在WS内プロジェクト）</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>取得未完</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>1. プロジェクト切替 を開き取得完了前を観察</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-004</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替画面</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>空データ</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>0 件時の空状態（現在WS内プロジェクト）</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>/projects?workspace_id が空配列</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1. データ0件で開く</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>空状態メッセージを表示（/undefined 参照にならない）</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-005</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替画面</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>取得失敗の inline error + toast（現在WS内プロジェクト）</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>/projects?workspace_id が 5xx</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1. API を でモックし開く</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>エラー表示 の inline error 表示 かつ toast 発火</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-007</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替画面</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>「Project picker」を操作すると動作する（ボタンが正しく動作するか）</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. 「Project picker」を選択</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>localStorage(atelier_current_project) 永続化（onClick/href/API が実在し、押すと副作用が起きる）</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-008</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替画面</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>読み上げ対応</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>axe scan で 0 critical/serious</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>1. axe を実行</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>critical/serious 違反 0（semantic role/aria）</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-010</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替画面</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>状態永続</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>F5 リロードでログアウトに飛ばない</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>ログイン済</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面で F5</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>保護ガードで維持・状態復元（URL クエリ等）</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-011</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替画面</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>到達性</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/apps/web/.qa/テスト仕様書_クライアント版.xlsx
+++ b/apps/web/.qa/テスト仕様書_クライアント版.xlsx
@@ -33,11 +33,15 @@
     <sheet name="議事録アップロード" sheetId="24" state="visible" r:id="rId24"/>
     <sheet name="商談ドラフト" sheetId="25" state="visible" r:id="rId25"/>
     <sheet name="自動スケジュール(cron)" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="通知センター" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="プロフィール" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="ワークスペース切替" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="プロジェクト切替" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet name="グローバル検索" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet name="利用規約" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="プライバシーポリシー" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="特商法表記" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="個人データ削除要求" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="通知センター" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet name="プロフィール" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet name="ワークスペース切替" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet name="プロジェクト切替" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet name="グローバル検索" sheetId="35" state="visible" r:id="rId35"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -492,7 +496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -868,81 +872,133 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>通知センター画面</t>
+          <t>利用規約画面</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>プロフィール画面</t>
+          <t>プライバシーポリシー画面</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>ワークスペース切替画面</t>
+          <t>特商法表記画面</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>プロジェクト切替画面</t>
+          <t>個人データ削除要求画面</t>
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>グローバル検索画面</t>
+          <t>通知センター画面</t>
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n"/>
-      <c r="B35" s="3" t="n"/>
-      <c r="C35" s="3" t="n"/>
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>プロフィール画面</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>完全性: 全485件 ＝ クライアント可視420件 ＋ 技術専用65件（画面で見えない裏取り=エンジニア版）</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="n"/>
-      <c r="C36" s="3" t="n"/>
+          <t>ワークスペース切替画面</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>プロジェクト切替画面</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>グローバル検索画面</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="n"/>
+      <c r="B39" s="3" t="n"/>
+      <c r="C39" s="3" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>完全性: 全513件 ＝ クライアント可視447件 ＋ 技術専用66件（画面で見えない裏取り=エンジニア版）</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n"/>
+      <c r="C40" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13086,7 +13142,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -13150,12 +13206,12 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>TUC36-001</t>
+          <t>SPUB01-001</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>通知センター画面</t>
+          <t>利用規約画面</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -13165,22 +13221,22 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>画面が正常表示（全 UI 要素・モック準拠）</t>
+          <t>未認証で /terms が開ける (公開)</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>未ログイン</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>1. 通知センター を開く</t>
+          <t>1. cookie なしで /terms</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
+          <t>・本文描画</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
@@ -13193,22 +13249,22 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>TUC36-002</t>
+          <t>SPUB01-002</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>通知センター画面</t>
+          <t>利用規約画面</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>視覚忠実度</t>
+          <t>整合性</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>配色/角丸/タイポが design token 準拠</t>
+          <t>本文が正本 ( /public/legal-documents) と一致</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -13218,12 +13274,12 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>1. 画面を目視</t>
+          <t>1. API の body_md の一文が画面に出るか</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
+          <t>DB 正本の文言が描画される</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
@@ -13236,37 +13292,37 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>TUC36-003</t>
+          <t>SPUB01-003</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>通知センター画面</t>
+          <t>利用規約画面</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>データ取得</t>
+          <t>画面表示</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>loading skeleton 表示（承認待ち集約）</t>
+          <t>版数・最終更新が実データ</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>取得未完</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>1. 通知センター を開き取得完了前を観察</t>
+          <t>1. メタ行を目視</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
+          <t>version / effective_date を表示</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
@@ -13279,37 +13335,37 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>TUC36-004</t>
+          <t>SPUB01-004</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>通知センター画面</t>
+          <t>利用規約画面</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>空データ</t>
+          <t>画面表示</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>0 件時の空状態（承認待ち集約）</t>
+          <t>タイトルの二重見出しが無い</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>/approval-inbox が空配列</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>1. データ0件で開く</t>
+          <t>1. h1/h2 を数える</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>空状態メッセージを表示（/undefined 参照にならない）</t>
+          <t>見出し 1 個のみ</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
@@ -13322,37 +13378,37 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>TUC36-005</t>
+          <t>SPUB01-005</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>通知センター画面</t>
+          <t>利用規約画面</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>エラー</t>
+          <t>到達性</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>取得失敗の inline error + toast（承認待ち集約）</t>
+          <t>公開ヘッダーのナビ (規約/プライバシー/特商法) が遷移</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>/approval-inbox が 5xx</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>1. API を でモックし開く</t>
+          <t>1. 各リンクをクリック</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>エラー表示 の inline error 表示 かつ toast 発火</t>
+          <t>相互に遷移できる</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
@@ -13365,37 +13421,37 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>TUC36-007</t>
+          <t>SPUB01-006</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>通知センター画面</t>
+          <t>利用規約画面</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>インタラクション</t>
+          <t>エラー</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>「既読」を操作すると動作する（ボタンが正しく動作するか）</t>
+          <t>API 失敗時に明示エラー</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5xx</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>1. 「既読」をクリック</t>
+          <t>1. 失敗させる</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>localStorage に記録→未読数減・未読フィルタ連動（onClick/href/API が実在し、押すと副作用が起きる）</t>
+          <t>エラー表示「文書の取得に失敗しました…」</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -13408,22 +13464,22 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>TUC36-008</t>
+          <t>SPUB01-007</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>通知センター画面</t>
+          <t>利用規約画面</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>インタラクション</t>
+          <t>スマホ・タブレットでも崩れない</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>「すべて/未読のみ タブ」を操作すると動作する（ボタンが正しく動作するか）</t>
+          <t>390px で横スクロールなし</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -13433,12 +13489,12 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>1. 「すべて/未読のみ タブ」を各クリック</t>
+          <t>1. 390 で開く</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>フィルタ切替（onClick/href/API が実在し、押すと副作用が起きる）</t>
+          <t>崩れなし</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -13447,221 +13503,6 @@
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>TUC36-009</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>通知センター画面</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>楽観更新</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>既読(localStorage): 成功で即時反映</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>対象が存在</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>1. 既読(localStorage) を実行</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>localStorage 更新 呼び出し前にUIへ楽観反映→成功で確定（別GET再取得で反映）</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>TUC36-012</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>通知センター画面</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>受容差分</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>永続既読/承認以外の種別は別migration</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>1. 既読挙動</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>専用テーブル(R-T08致命級)が無く localStorage 管理(MVP)</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>TUC36-013</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>通知センター画面</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>読み上げ対応</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>axe scan で 0 critical/serious</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>1. axe を実行</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>critical/serious 違反 0（semantic role/aria）</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>TUC36-015</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>通知センター画面</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>状態永続</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>F5 リロードでログアウトに飛ばない</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>ログイン済</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>1. 画面で F5</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>保護ガードで維持・状態復元（URL クエリ等）</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>TUC36-016</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>通知センター画面</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>到達性</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I13" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13674,7 +13515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -13738,12 +13579,12 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>TUC37-001</t>
+          <t>SPUB02-001</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>プロフィール画面</t>
+          <t>プライバシーポリシー画面</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -13753,22 +13594,22 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>画面が正常表示（全 UI 要素・モック準拠）</t>
+          <t>未認証で /privacy が開ける</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>未ログイン</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>1. プロフィール を開く</t>
+          <t>1. cookie なしで開く</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
+          <t>・本文描画</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
@@ -13781,22 +13622,22 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>TUC37-002</t>
+          <t>SPUB02-002</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>プロフィール画面</t>
+          <t>プライバシーポリシー画面</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>視覚忠実度</t>
+          <t>整合性</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>配色/角丸/タイポが design token 準拠</t>
+          <t>本文が正本 (privacy_policy) と一致</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -13806,12 +13647,12 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>1. 画面を目視</t>
+          <t>1. API body_md の一文を照合</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
+          <t>DB 正本を描画</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
@@ -13824,37 +13665,37 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>TUC37-003</t>
+          <t>SPUB02-003</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>プロフィール画面</t>
+          <t>プライバシーポリシー画面</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>データ取得</t>
+          <t>画面表示</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>loading skeleton 表示（自己プロフィール）</t>
+          <t>版数・最終更新・見出し非重複</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>取得未完</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>1. プロフィール を開き取得完了前を観察</t>
+          <t>1. メタ/見出し目視</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
+          <t>version 表示・見出し 1 個</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
@@ -13867,37 +13708,37 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>TUC37-004</t>
+          <t>SPUB02-004</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>プロフィール画面</t>
+          <t>プライバシーポリシー画面</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>空データ</t>
+          <t>到達性</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>0 件時の空状態（自己プロフィール）</t>
+          <t>公開ヘッダーナビで相互遷移</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>/me が空配列</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>1. データ0件で開く</t>
+          <t>1. リンク巡回</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>空状態メッセージを表示（/undefined 参照にならない）</t>
+          <t>/terms ↔ /privacy ↔ /tokushoho</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
@@ -13910,37 +13751,37 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>TUC37-005</t>
+          <t>SPUB02-005</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>プロフィール画面</t>
+          <t>プライバシーポリシー画面</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>エラー</t>
+          <t>スマホ・タブレットでも崩れない</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>取得失敗の inline error + toast（自己プロフィール）</t>
+          <t>390px 横スクロールなし</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>/me が 5xx</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>1. API を でモックし開く</t>
+          <t>1. 390 で開く</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>エラー表示 の inline error 表示 かつ toast 発火</t>
+          <t>崩れなし</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
@@ -13949,522 +13790,6 @@
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>TUC37-007</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>プロフィール画面</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>入力フォーム</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>初期値/placeholder（display_name）</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>1. フォームを開く</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>display_name の初期値/placeholder が正しい</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>TUC37-008</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>プロフィール画面</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>バリデーション</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>display_name: 必須/最大100</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>1. display_name に不正値/未入力を入れる</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>エラー表示 かつ 送信ボタン無効</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>TUC37-009</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>プロフィール画面</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>入力フォーム</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>初期値/placeholder（email）</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>1. フォームを開く</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>email の初期値/placeholder が正しい</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>TUC37-010</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>プロフィール画面</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>バリデーション</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>email: readonly</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>1. email に不正値/未入力を入れる</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>エラー表示 かつ 送信ボタン無効</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>TUC37-011</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>プロフィール画面</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>インタラクション</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>「保存」を操作すると動作する（ボタンが正しく動作するか）</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>1. 「保存」をクリック</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>/me(楽観)→保存表示（onClick/href/API が実在し、押すと副作用が起きる）</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>TUC37-012</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>プロフィール画面</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>楽観更新</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>表示名保存(): 成功で即時反映</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>対象が存在</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>1. 表示名保存() を実行</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>/me 呼び出し前にUIへ楽観反映→成功で確定（別GET再取得で反映）</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>TUC37-013</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>プロフィール画面</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>楽観更新</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>表示名保存(): 失敗でロールバック</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>サーバ 4xx/5xx</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>1. 表示名保存() を実行しAPIが失敗</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>楽観反映が元に戻り、inline error + toast を表示</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I13" s="4" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>TUC37-014</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>プロフィール画面</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>エラー</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>表示名保存(): API 失敗時 inline error + toast</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>接続失敗/レート</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>1. 表示名保存() を失敗させる</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>エラー表示 + toast、状態は不整合にならない</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I14" s="4" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>TUC37-015</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>プロフィール画面</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>受容差分</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>email は readonly</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>1. email 欄を確認</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>Auth 紐付けのため変更不可(readonly)</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I15" s="4" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>TUC37-016</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>プロフィール画面</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>読み上げ対応</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>axe scan で 0 critical/serious</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>1. axe を実行</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>critical/serious 違反 0（semantic role/aria）</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I16" s="4" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>TUC37-018</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>プロフィール画面</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>状態永続</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>F5 リロードでログアウトに飛ばない</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>ログイン済</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>1. 画面で F5</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>保護ガードで維持・状態復元（URL クエリ等）</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I17" s="4" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>TUC37-019</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>プロフィール画面</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>到達性</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I18" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -14477,7 +13802,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -14541,12 +13866,12 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>TUC38-001</t>
+          <t>SPUB03-001</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>ワークスペース切替画面</t>
+          <t>特商法表記画面</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -14556,22 +13881,22 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>画面が正常表示（全 UI 要素・モック準拠）</t>
+          <t>未認証で /tokushoho が開ける</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>未ログイン</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>1. ワークスペース切替 を開く</t>
+          <t>1. cookie なしで開く</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
+          <t>・本文描画</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
@@ -14584,22 +13909,22 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>TUC38-002</t>
+          <t>SPUB03-002</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>ワークスペース切替画面</t>
+          <t>特商法表記画面</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>視覚忠実度</t>
+          <t>整合性</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>配色/角丸/タイポが design token 準拠</t>
+          <t>本文が正本 (tokushoho) と一致</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -14609,12 +13934,12 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>1. 画面を目視</t>
+          <t>1. API body_md の項目値を照合</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
+          <t>DB 正本 (販売事業者/連絡先等) を描画</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
@@ -14627,37 +13952,37 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>TUC38-003</t>
+          <t>SPUB03-003</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>ワークスペース切替画面</t>
+          <t>特商法表記画面</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>データ取得</t>
+          <t>画面表示</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>loading skeleton 表示（所属 WS 一覧）</t>
+          <t>版数・最終更新・見出し非重複</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>取得未完</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>1. ワークスペース切替 を開き取得完了前を観察</t>
+          <t>1. メタ/見出し目視</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
+          <t>version 表示・見出し 1 個</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
@@ -14670,37 +13995,37 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>TUC38-004</t>
+          <t>SPUB03-004</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>ワークスペース切替画面</t>
+          <t>特商法表記画面</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>空データ</t>
+          <t>到達性</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>0 件時の空状態（所属 WS 一覧）</t>
+          <t>公開ヘッダーナビで相互遷移</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>/workspaces が空配列</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>1. データ0件で開く</t>
+          <t>1. リンク巡回</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>空状態メッセージを表示（/undefined 参照にならない）</t>
+          <t>相互遷移</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
@@ -14713,37 +14038,37 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>TUC38-005</t>
+          <t>SPUB03-005</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>ワークスペース切替画面</t>
+          <t>特商法表記画面</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>エラー</t>
+          <t>スマホ・タブレットでも崩れない</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>取得失敗の inline error + toast（所属 WS 一覧）</t>
+          <t>390px 横スクロールなし</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>/workspaces が 5xx</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>1. API を でモックし開く</t>
+          <t>1. 390 で開く</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>エラー表示 の inline error 表示 かつ toast 発火</t>
+          <t>崩れなし</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
@@ -14752,178 +14077,6 @@
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-007</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替画面</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>インタラクション</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>「WS picker」を操作すると動作する（ボタンが正しく動作するか）</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>1. 「WS picker」を選択</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>localStorage(atelier_current_workspace) 永続化（onClick/href/API が実在し、押すと副作用が起きる）</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-008</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替画面</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>読み上げ対応</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>axe scan で 0 critical/serious</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>1. axe を実行</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>critical/serious 違反 0（semantic role/aria）</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-010</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替画面</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>状態永続</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>F5 リロードでログアウトに飛ばない</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>ログイン済</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>1. 画面で F5</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>保護ガードで維持・状態復元（URL クエリ等）</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-011</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替画面</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>到達性</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15696,6 +14849,1899 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>画面</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>テスト観点</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>テスト項目</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>前提条件</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>操作手順</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>期待結果</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>SPUB04-002</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>個人データ削除要求画面</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>画面表示</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>削除内容チェックリスト + 残存データ説明 (モック準拠)</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>1. danger カード目視</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>6 項目 + 匿名化説明</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>SPUB04-003</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>個人データ削除要求画面</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>画面表示</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>削除スケジュールカード</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>1. 目視</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>当日/30日後/キャンセル可の 3 行</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>SPUB04-004</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>個人データ削除要求画面</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>入力フォーム</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>ログイン中メールが表示専用 (disabled)</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>ログイン済</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>1. email 欄を確認</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>実メールを表示・編集不可</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>SPUB04-005</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>個人データ削除要求画面</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>バリデーション</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>「削除する」タイプ確認が必須</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1. 未入力/誤入力で申請</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>「「削除する」と入力してください」・ 不発</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>SPUB04-006</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>個人データ削除要求画面</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>バリデーション</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>同意チェック必須・理由は任意</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1. 同意なしで申請</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>エラー・ 不発</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>SPUB04-007</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>個人データ削除要求画面</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>登録・編集</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>実申請 → /public/data-deletion-requests → 受付番号表示</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>ログイン済</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. 正しく入力し申請</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>→ 受付番号 + 30 日案内</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>SPUB04-008</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>個人データ削除要求画面</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>整合性</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>申請が audit_logs に記録される</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>申請直後</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>1. psql 突合</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>action=data_deletion.request が actor 本人で +1</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>SPUB04-009</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>個人データ削除要求画面</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>到達性</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>キャンセル/戻りリンクが /privacy へ</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>1. リンク確認</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>href=/privacy</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>SPUB04-010</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>個人データ削除要求画面</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>送信失敗時に明示エラー</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>5xx</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>1. 失敗させる</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>エラー表示「送信に失敗しました…」</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>SPUB04-011</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>個人データ削除要求画面</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>スマホ・タブレットでも崩れない</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>390px 横スクロールなし</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>1. 390 で開く</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>崩れなし</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>画面</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>テスト観点</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>テスト項目</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>前提条件</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>操作手順</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>期待結果</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>TUC36-001</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>通知センター画面</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>画面表示</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>画面が正常表示（全 UI 要素・モック準拠）</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>1. 通知センター を開く</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>TUC36-002</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>通知センター画面</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>視覚忠実度</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>配色/角丸/タイポが design token 準拠</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面を目視</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>TUC36-003</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>通知センター画面</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>データ取得</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>loading skeleton 表示（承認待ち集約）</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>取得未完</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>1. 通知センター を開き取得完了前を観察</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>TUC36-004</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>通知センター画面</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>空データ</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>0 件時の空状態（承認待ち集約）</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>/approval-inbox が空配列</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1. データ0件で開く</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>空状態メッセージを表示（/undefined 参照にならない）</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>TUC36-005</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>通知センター画面</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>取得失敗の inline error + toast（承認待ち集約）</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>/approval-inbox が 5xx</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1. API を でモックし開く</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>エラー表示 の inline error 表示 かつ toast 発火</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>TUC36-007</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>通知センター画面</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>「既読」を操作すると動作する（ボタンが正しく動作するか）</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. 「既読」をクリック</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>localStorage に記録→未読数減・未読フィルタ連動（onClick/href/API が実在し、押すと副作用が起きる）</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>TUC36-008</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>通知センター画面</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>「すべて/未読のみ タブ」を操作すると動作する（ボタンが正しく動作するか）</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>1. 「すべて/未読のみ タブ」を各クリック</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>フィルタ切替（onClick/href/API が実在し、押すと副作用が起きる）</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>TUC36-009</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>通知センター画面</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>楽観更新</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>既読(localStorage): 成功で即時反映</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>対象が存在</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>1. 既読(localStorage) を実行</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>localStorage 更新 呼び出し前にUIへ楽観反映→成功で確定（別GET再取得で反映）</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>TUC36-012</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>通知センター画面</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>受容差分</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>永続既読/承認以外の種別は別migration</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>1. 既読挙動</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>専用テーブル(R-T08致命級)が無く localStorage 管理(MVP)</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>TUC36-013</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>通知センター画面</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>読み上げ対応</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>axe scan で 0 critical/serious</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>1. axe を実行</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>critical/serious 違反 0（semantic role/aria）</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>TUC36-015</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>通知センター画面</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>状態永続</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>F5 リロードでログアウトに飛ばない</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>ログイン済</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面で F5</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>保護ガードで維持・状態復元（URL クエリ等）</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>TUC36-016</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>通知センター画面</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>到達性</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>画面</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>テスト観点</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>テスト項目</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>前提条件</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>操作手順</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>期待結果</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>TUC37-001</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>プロフィール画面</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>画面表示</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>画面が正常表示（全 UI 要素・モック準拠）</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>1. プロフィール を開く</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>TUC37-002</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>プロフィール画面</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>視覚忠実度</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>配色/角丸/タイポが design token 準拠</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面を目視</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>TUC37-003</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>プロフィール画面</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>データ取得</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>loading skeleton 表示（自己プロフィール）</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>取得未完</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>1. プロフィール を開き取得完了前を観察</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>TUC37-004</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>プロフィール画面</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>空データ</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>0 件時の空状態（自己プロフィール）</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>/me が空配列</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1. データ0件で開く</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>空状態メッセージを表示（/undefined 参照にならない）</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>TUC37-005</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>プロフィール画面</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>取得失敗の inline error + toast（自己プロフィール）</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>/me が 5xx</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1. API を でモックし開く</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>エラー表示 の inline error 表示 かつ toast 発火</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>TUC37-007</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>プロフィール画面</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>入力フォーム</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>初期値/placeholder（display_name）</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. フォームを開く</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>display_name の初期値/placeholder が正しい</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>TUC37-008</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>プロフィール画面</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>バリデーション</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>display_name: 必須/最大100</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>1. display_name に不正値/未入力を入れる</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>エラー表示 かつ 送信ボタン無効</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>TUC37-009</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>プロフィール画面</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>入力フォーム</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>初期値/placeholder（email）</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>1. フォームを開く</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>email の初期値/placeholder が正しい</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>TUC37-010</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>プロフィール画面</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>バリデーション</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>email: readonly</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>1. email に不正値/未入力を入れる</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>エラー表示 かつ 送信ボタン無効</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>TUC37-011</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>プロフィール画面</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>「保存」を操作すると動作する（ボタンが正しく動作するか）</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>1. 「保存」をクリック</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>/me(楽観)→保存表示（onClick/href/API が実在し、押すと副作用が起きる）</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>TUC37-012</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>プロフィール画面</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>楽観更新</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>表示名保存(): 成功で即時反映</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>対象が存在</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>1. 表示名保存() を実行</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>/me 呼び出し前にUIへ楽観反映→成功で確定（別GET再取得で反映）</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>TUC37-013</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>プロフィール画面</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>楽観更新</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>表示名保存(): 失敗でロールバック</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>サーバ 4xx/5xx</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>1. 表示名保存() を実行しAPIが失敗</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>楽観反映が元に戻り、inline error + toast を表示</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>TUC37-014</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>プロフィール画面</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>表示名保存(): API 失敗時 inline error + toast</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>接続失敗/レート</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>1. 表示名保存() を失敗させる</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>エラー表示 + toast、状態は不整合にならない</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>TUC37-015</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>プロフィール画面</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>受容差分</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>email は readonly</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>1. email 欄を確認</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>Auth 紐付けのため変更不可(readonly)</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>TUC37-016</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>プロフィール画面</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>読み上げ対応</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>axe scan で 0 critical/serious</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>1. axe を実行</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>critical/serious 違反 0（semantic role/aria）</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>TUC37-018</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>プロフィール画面</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>状態永続</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>F5 リロードでログアウトに飛ばない</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>ログイン済</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面で F5</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>保護ガードで維持・状態復元（URL クエリ等）</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>TUC37-019</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>プロフィール画面</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>到達性</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -15760,12 +16806,12 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>TUC39-001</t>
+          <t>TUC38-001</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替画面</t>
+          <t>ワークスペース切替画面</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -15785,7 +16831,7 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>1. プロジェクト切替 を開く</t>
+          <t>1. ワークスペース切替 を開く</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
@@ -15803,12 +16849,12 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>TUC39-002</t>
+          <t>TUC38-002</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替画面</t>
+          <t>ワークスペース切替画面</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -15846,12 +16892,12 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>TUC39-003</t>
+          <t>TUC38-003</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替画面</t>
+          <t>ワークスペース切替画面</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -15861,7 +16907,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>loading skeleton 表示（現在WS内プロジェクト）</t>
+          <t>loading skeleton 表示（所属 WS 一覧）</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -15871,7 +16917,7 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>1. プロジェクト切替 を開き取得完了前を観察</t>
+          <t>1. ワークスペース切替 を開き取得完了前を観察</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
@@ -15889,12 +16935,12 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>TUC39-004</t>
+          <t>TUC38-004</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替画面</t>
+          <t>ワークスペース切替画面</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -15904,12 +16950,12 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>0 件時の空状態（現在WS内プロジェクト）</t>
+          <t>0 件時の空状態（所属 WS 一覧）</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>/projects?workspace_id が空配列</t>
+          <t>/workspaces が空配列</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -15932,12 +16978,12 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>TUC39-005</t>
+          <t>TUC38-005</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替画面</t>
+          <t>ワークスペース切替画面</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -15947,12 +16993,12 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>取得失敗の inline error + toast（現在WS内プロジェクト）</t>
+          <t>取得失敗の inline error + toast（所属 WS 一覧）</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>/projects?workspace_id が 5xx</t>
+          <t>/workspaces が 5xx</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -15975,12 +17021,12 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>TUC39-007</t>
+          <t>TUC38-007</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替画面</t>
+          <t>ワークスペース切替画面</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -15990,7 +17036,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>「Project picker」を操作すると動作する（ボタンが正しく動作するか）</t>
+          <t>「WS picker」を操作すると動作する（ボタンが正しく動作するか）</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -16000,12 +17046,12 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>1. 「Project picker」を選択</t>
+          <t>1. 「WS picker」を選択</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>localStorage(atelier_current_project) 永続化（onClick/href/API が実在し、押すと副作用が起きる）</t>
+          <t>localStorage(atelier_current_workspace) 永続化（onClick/href/API が実在し、押すと副作用が起きる）</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -16018,12 +17064,12 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>TUC39-008</t>
+          <t>TUC38-008</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替画面</t>
+          <t>ワークスペース切替画面</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -16061,12 +17107,12 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>TUC39-010</t>
+          <t>TUC38-010</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替画面</t>
+          <t>ワークスペース切替画面</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -16104,12 +17150,12 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>TUC39-011</t>
+          <t>TUC38-011</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替画面</t>
+          <t>ワークスペース切替画面</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -16149,7 +17195,466 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>画面</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>テスト観点</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>テスト項目</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>前提条件</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>操作手順</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>期待結果</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-001</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替画面</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>画面表示</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>画面が正常表示（全 UI 要素・モック準拠）</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>1. プロジェクト切替 を開く</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-002</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替画面</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>視覚忠実度</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>配色/角丸/タイポが design token 準拠</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面を目視</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-003</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替画面</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>データ取得</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>loading skeleton 表示（現在WS内プロジェクト）</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>取得未完</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>1. プロジェクト切替 を開き取得完了前を観察</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-004</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替画面</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>空データ</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>0 件時の空状態（現在WS内プロジェクト）</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>/projects?workspace_id が空配列</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1. データ0件で開く</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>空状態メッセージを表示（/undefined 参照にならない）</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-005</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替画面</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>取得失敗の inline error + toast（現在WS内プロジェクト）</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>/projects?workspace_id が 5xx</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1. API を でモックし開く</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>エラー表示 の inline error 表示 かつ toast 発火</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-007</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替画面</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>「Project picker」を操作すると動作する（ボタンが正しく動作するか）</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. 「Project picker」を選択</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>localStorage(atelier_current_project) 永続化（onClick/href/API が実在し、押すと副作用が起きる）</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-008</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替画面</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>読み上げ対応</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>axe scan で 0 critical/serious</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>1. axe を実行</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>critical/serious 違反 0（semantic role/aria）</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-010</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替画面</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>状態永続</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>F5 リロードでログアウトに飛ばない</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>ログイン済</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面で F5</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>保護ガードで維持・状態復元（URL クエリ等）</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-011</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替画面</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>到達性</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/apps/web/.qa/テスト仕様書_クライアント版.xlsx
+++ b/apps/web/.qa/テスト仕様書_クライアント版.xlsx
@@ -37,11 +37,17 @@
     <sheet name="プライバシーポリシー" sheetId="28" state="visible" r:id="rId28"/>
     <sheet name="特商法表記" sheetId="29" state="visible" r:id="rId29"/>
     <sheet name="個人データ削除要求" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet name="通知センター" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet name="プロフィール" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet name="ワークスペース切替" sheetId="33" state="visible" r:id="rId33"/>
-    <sheet name="プロジェクト切替" sheetId="34" state="visible" r:id="rId34"/>
-    <sheet name="グローバル検索" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet name="運営ダッシュボード" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet name="スキル管理" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet name="AI 社員テンプレート" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet name="ユーザー管理" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet name="監査ログ" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet name="運営デフォルト・ナレッジ" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet name="通知センター" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet name="プロフィール" sheetId="38" state="visible" r:id="rId38"/>
+    <sheet name="ワークスペース切替" sheetId="39" state="visible" r:id="rId39"/>
+    <sheet name="プロジェクト切替" sheetId="40" state="visible" r:id="rId40"/>
+    <sheet name="グローバル検索" sheetId="41" state="visible" r:id="rId41"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -496,7 +502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C40"/>
+  <dimension ref="A1:C46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -924,81 +930,159 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>通知センター画面</t>
+          <t>運営ダッシュボード画面</t>
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>プロフィール画面</t>
+          <t>スキル管理画面</t>
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>ワークスペース切替画面</t>
+          <t>AI 社員テンプレート画面</t>
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>プロジェクト切替画面</t>
+          <t>ユーザー管理画面</t>
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>グローバル検索画面</t>
+          <t>監査ログ画面</t>
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n"/>
-      <c r="B39" s="3" t="n"/>
-      <c r="C39" s="3" t="n"/>
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>運営デフォルト・ナレッジ画面</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>完全性: 全513件 ＝ クライアント可視447件 ＋ 技術専用66件（画面で見えない裏取り=エンジニア版）</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="n"/>
-      <c r="C40" s="3" t="n"/>
+          <t>通知センター画面</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>プロフィール画面</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>ワークスペース切替画面</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>プロジェクト切替画面</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>グローバル検索画面</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="n"/>
+      <c r="B45" s="3" t="n"/>
+      <c r="C45" s="3" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>完全性: 全547件 ＝ クライアント可視475件 ＋ 技術専用72件（画面で見えない裏取り=エンジニア版）</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n"/>
+      <c r="C46" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15351,6 +15435,1642 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>画面</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>テスト観点</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>テスト項目</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>前提条件</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>操作手順</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>期待結果</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>ST01-002</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>運営ダッシュボード画面</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>画面表示</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>管理シェル (ダークサイドバー) がモック準拠</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>1. /admin を開く</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>ADMIN CONSOLE・運営タグ・6 項目ナビ</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>ST01-003</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>運営ダッシュボード画面</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>整合性</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>KPI が API=DB (admin 所属 WS 範囲) と一致</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>1. KPI と psql を突合</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>契約 (T-A-41) 通り所属 WS 範囲の実数</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>ST01-004</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>運営ダッシュボード画面</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>画面表示</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>KPI 4 種 (WS/プロジェクト/AI社員/監査イベント24h)</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>1. bento を目視</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>4 タイル表示</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>ST01-005</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>運営ダッシュボード画面</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>画面表示</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>アクティビティ actor がメール表示</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1. 一覧を目視</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>生 UUID を出さない (/admin/users で解決、未解決時は短縮 ID)</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>ST01-006</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>運営ダッシュボード画面</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>到達性</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>ナビから他 5 画面へ遷移</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1. 各ナビをクリック</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>全画面到達・active 表示</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>ST01-007</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>運営ダッシュボード画面</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>スマホ・タブレットでも崩れない</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>390px 横スクロールなし・モバイルナビ操作可</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. 390 で操作</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>KPI 2×2・チップナビで遷移</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>ST01-008</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>運営ダッシュボード画面</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>受容差分</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>ミッションヒーロー/トレンド/健全性/コスト等は未描画</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>1. 目視</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>ダミー業務数値 (100社獲得/¥906 等) の虚偽表示をしない</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>画面</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>テスト観点</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>テスト項目</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>前提条件</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>操作手順</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>期待結果</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>ST02-001</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>スキル管理画面</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>画面表示</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>一覧が実データ (登録スキル数・active バッジ)</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>1. /admin/skills</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>skills テーブルの実数</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>ST02-002</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>スキル管理画面</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>登録・編集</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>新規登録 → 一覧反映 + DB</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>1. 新規アップロード 2. name/version/本文 3. 登録</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>/admin/skills → 一覧 + DB 行</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>ST02-003</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>スキル管理画面</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>**重複登録 (name+version) が 409 明示エラー**</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>同名同版が存在</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>1. 同じ内容で登録</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>「同じ名前・バージョンのスキルが既に存在します」</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>ST02-004</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>スキル管理画面</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>登録・編集</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>削除 → 一覧から消え DB 反映</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1. 削除</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>→ 行消滅</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>ST02-005</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>スキル管理画面</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>検索・編集・装着 (attach) が実 API</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1. 各操作</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>/ attach 実配線</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>ST02-006</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>スキル管理画面</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>スマホ・タブレットでも崩れない</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>390px 横スクロールなし</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. 390</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>崩れなし</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>画面</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>テスト観点</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>テスト項目</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>前提条件</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>操作手順</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>期待結果</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>ST03-001</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>AI 社員テンプレート画面</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>画面表示</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>一覧が実データ (DB 件数一致)</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>1. /admin/templates</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>ai_employee_templates 全 14 件</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>ST03-003</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>AI 社員テンプレート画面</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>到達性</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>シェルナビから到達</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>1. ナビ</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>遷移 + active</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>ST03-004</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>AI 社員テンプレート画面</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>受容差分</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>編集 UI なし (契約が read-only)</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>1. 目視</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>偽の編集ボタンを出さない</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>ST03-005</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>AI 社員テンプレート画面</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>スマホ・タブレットでも崩れない</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>390px 横スクロールなし</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1. 390</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>崩れなし</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>画面</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>テスト観点</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>テスト項目</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>前提条件</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>操作手順</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>期待結果</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>ST04-001</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>ユーザー管理画面</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>画面表示</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>一覧に実ユーザー (所属 WS 横断)</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>1. /admin/users</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>design-audit@example.com 等の実行行</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>ST04-002</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>ユーザー管理画面</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>検索で絞り込み</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>1. 検索欄に入力</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>一致行のみ表示</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>ST04-004</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>ユーザー管理画面</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>スマホ・タブレットでも崩れない</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>390px 横スクロールなし</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>1. 390</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>崩れなし</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>画面</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>テスト観点</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>テスト項目</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>前提条件</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>操作手順</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>期待結果</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>ST05-001</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>監査ログ画面</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>画面表示</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>集計カード + ログ表が実データ</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>1. /admin/audit</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>audit_logs の実行行 (時刻/アクター/アクション/対象/IP)</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>ST05-002</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>監査ログ画面</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>検索で絞り込み (credential 等)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>1. 検索欄に入力</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>一致行のみ・他アクション消滅</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>ST05-003</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>監査ログ画面</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>アクター/アクション/日付フィルタが実動</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>1. select/date 操作</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>クライアント側絞り込み + クリア</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>ST05-005</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>監査ログ画面</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>スマホ・タブレットでも崩れない</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>**390px 横スクロールなし (v2 実バグ修正)**</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1. 390</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>集計 2×2・フィルタ折返し・ログ表は自前スクロール</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>画面</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>テスト観点</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>テスト項目</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>前提条件</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>操作手順</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>期待結果</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>ST06-001</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>運営デフォルト・ナレッジ画面</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>登録・編集</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>新規追加 → 一覧 + DB</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>1. 新規追加 2. タイトル/カテゴリ/本文 3. 追加</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>/admin/knowledge → knowledge_nodes 行</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>ST06-002</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>運営デフォルト・ナレッジ画面</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>ツリー表示トグル → DB 反転</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>行あり</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>1. switch をクリック</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>visible_in_tree が実反転</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>ST06-003</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>運営デフォルト・ナレッジ画面</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>登録・編集</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>**削除 (2 段階確認) → DB 反映**</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>行あり</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>1. 削除 → 削除する</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>/admin/knowledge/{id} → 論理削除</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>ST06-005</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>運営デフォルト・ナレッジ画面</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>スマホ・タブレットでも崩れない</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>390px 横スクロールなし</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1. 390</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>崩れなし</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -15933,7 +17653,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -16736,7 +18456,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -17189,1096 +18909,6 @@
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="7" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>画面</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>テスト観点</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>テスト項目</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>前提条件</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>操作手順</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>期待結果</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>結果</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>TUC39-001</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>プロジェクト切替画面</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>画面表示</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>画面が正常表示（全 UI 要素・モック準拠）</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>1. プロジェクト切替 を開く</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I2" s="4" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>TUC39-002</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>プロジェクト切替画面</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>視覚忠実度</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>配色/角丸/タイポが design token 準拠</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>1. 画面を目視</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>TUC39-003</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>プロジェクト切替画面</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>データ取得</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>loading skeleton 表示（現在WS内プロジェクト）</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>取得未完</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>1. プロジェクト切替 を開き取得完了前を観察</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>TUC39-004</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>プロジェクト切替画面</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>空データ</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>0 件時の空状態（現在WS内プロジェクト）</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>/projects?workspace_id が空配列</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>1. データ0件で開く</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>空状態メッセージを表示（/undefined 参照にならない）</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>TUC39-005</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>プロジェクト切替画面</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>エラー</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>取得失敗の inline error + toast（現在WS内プロジェクト）</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>/projects?workspace_id が 5xx</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>1. API を でモックし開く</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>エラー表示 の inline error 表示 かつ toast 発火</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>TUC39-007</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>プロジェクト切替画面</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>インタラクション</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>「Project picker」を操作すると動作する（ボタンが正しく動作するか）</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>1. 「Project picker」を選択</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>localStorage(atelier_current_project) 永続化（onClick/href/API が実在し、押すと副作用が起きる）</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>TUC39-008</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>プロジェクト切替画面</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>読み上げ対応</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>axe scan で 0 critical/serious</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>1. axe を実行</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>critical/serious 違反 0（semantic role/aria）</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>TUC39-010</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>プロジェクト切替画面</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>状態永続</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>F5 リロードでログアウトに飛ばない</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>ログイン済</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>1. 画面で F5</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>保護ガードで維持・状態復元（URL クエリ等）</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>TUC39-011</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>プロジェクト切替画面</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>到達性</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="7" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>画面</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>テスト観点</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>テスト項目</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>前提条件</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>操作手順</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>期待結果</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>結果</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>TUC40-001</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>グローバル検索画面</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>画面表示</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>画面が正常表示（全 UI 要素・モック準拠）</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>1. グローバル検索 を開く</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I2" s="4" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>TUC40-002</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>グローバル検索画面</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>視覚忠実度</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>配色/角丸/タイポが design token 準拠</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>1. 画面を目視</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>TUC40-003</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>グローバル検索画面</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>データ取得</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>loading skeleton 表示（横断検索）</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>取得未完</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>1. グローバル検索 を開き取得完了前を観察</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>TUC40-004</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>グローバル検索画面</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>空データ</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>0 件時の空状態（横断検索）</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>/search?q=&amp;kind= が空配列</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>1. データ0件で開く</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>空状態メッセージを表示（/undefined 参照にならない）</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>TUC40-005</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>グローバル検索画面</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>エラー</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>取得失敗の inline error + toast（横断検索）</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>/search?q=&amp;kind= が 5xx</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>1. API を でモックし開く</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>エラー表示 の inline error 表示 かつ toast 発火</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>TUC40-007</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>グローバル検索画面</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>入力フォーム</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>初期値/placeholder（キーワード）</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>1. フォームを開く</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>キーワード の初期値/placeholder が正しい</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>TUC40-008</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>グローバル検索画面</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>バリデーション</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>キーワード: 必須(空で未検索)</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>1. キーワード に不正値/未入力を入れる</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>エラー表示 かつ 送信ボタン無効</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>TUC40-009</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>グローバル検索画面</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>インタラクション</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>「種別フィルタ(all/project/task/knowledge/employee)」を操作すると動作する（ボタンが正しく動作するか）</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>1. 「種別フィルタ(all/project/task/knowledge/employee)」を各クリック</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>kind を切替して再検索（onClick/href/API が実在し、押すと副作用が起きる）</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>TUC40-010</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>グローバル検索画面</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>インタラクション</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>「検索入力」を操作すると動作する（ボタンが正しく動作するか）</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>1. 「検索入力」を入力(debounce)</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>/search を叩き結果を種別ラベル付きで表示（onClick/href/API が実在し、押すと副作用が起きる）</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>TUC40-011</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>グローバル検索画面</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>R-T08</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>他人のデータが見えない権限 で可視性担保</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>1. 検索実行</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>他人のデータが見えない権限 内のみヒット(越境自動除外)</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>TUC40-012</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>グローバル検索画面</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>読み上げ対応</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>axe scan で 0 critical/serious</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>1. axe を実行</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>critical/serious 違反 0（semantic role/aria）</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>TUC40-014</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>グローバル検索画面</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>状態永続</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>F5 リロードでログアウトに飛ばない</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>ログイン済</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>1. 画面で F5</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>保護ガードで維持・状態復元（URL クエリ等）</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I13" s="4" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>TUC40-015</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>グローバル検索画面</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>到達性</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I14" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -19002,6 +19632,1096 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>画面</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>テスト観点</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>テスト項目</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>前提条件</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>操作手順</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>期待結果</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-001</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替画面</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>画面表示</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>画面が正常表示（全 UI 要素・モック準拠）</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>1. プロジェクト切替 を開く</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-002</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替画面</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>視覚忠実度</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>配色/角丸/タイポが design token 準拠</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面を目視</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-003</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替画面</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>データ取得</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>loading skeleton 表示（現在WS内プロジェクト）</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>取得未完</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>1. プロジェクト切替 を開き取得完了前を観察</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-004</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替画面</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>空データ</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>0 件時の空状態（現在WS内プロジェクト）</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>/projects?workspace_id が空配列</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1. データ0件で開く</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>空状態メッセージを表示（/undefined 参照にならない）</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-005</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替画面</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>取得失敗の inline error + toast（現在WS内プロジェクト）</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>/projects?workspace_id が 5xx</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1. API を でモックし開く</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>エラー表示 の inline error 表示 かつ toast 発火</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-007</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替画面</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>「Project picker」を操作すると動作する（ボタンが正しく動作するか）</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. 「Project picker」を選択</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>localStorage(atelier_current_project) 永続化（onClick/href/API が実在し、押すと副作用が起きる）</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-008</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替画面</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>読み上げ対応</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>axe scan で 0 critical/serious</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>1. axe を実行</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>critical/serious 違反 0（semantic role/aria）</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-010</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替画面</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>状態永続</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>F5 リロードでログアウトに飛ばない</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>ログイン済</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面で F5</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>保護ガードで維持・状態復元（URL クエリ等）</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-011</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替画面</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>到達性</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>画面</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>テスト観点</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>テスト項目</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>前提条件</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>操作手順</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>期待結果</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>TUC40-001</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>グローバル検索画面</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>画面表示</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>画面が正常表示（全 UI 要素・モック準拠）</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>1. グローバル検索 を開く</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>TUC40-002</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>グローバル検索画面</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>視覚忠実度</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>配色/角丸/タイポが design token 準拠</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面を目視</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>TUC40-003</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>グローバル検索画面</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>データ取得</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>loading skeleton 表示（横断検索）</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>取得未完</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>1. グローバル検索 を開き取得完了前を観察</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>TUC40-004</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>グローバル検索画面</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>空データ</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>0 件時の空状態（横断検索）</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>/search?q=&amp;kind= が空配列</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1. データ0件で開く</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>空状態メッセージを表示（/undefined 参照にならない）</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>TUC40-005</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>グローバル検索画面</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>取得失敗の inline error + toast（横断検索）</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>/search?q=&amp;kind= が 5xx</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1. API を でモックし開く</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>エラー表示 の inline error 表示 かつ toast 発火</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>TUC40-007</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>グローバル検索画面</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>入力フォーム</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>初期値/placeholder（キーワード）</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. フォームを開く</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>キーワード の初期値/placeholder が正しい</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>TUC40-008</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>グローバル検索画面</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>バリデーション</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>キーワード: 必須(空で未検索)</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>1. キーワード に不正値/未入力を入れる</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>エラー表示 かつ 送信ボタン無効</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>TUC40-009</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>グローバル検索画面</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>「種別フィルタ(all/project/task/knowledge/employee)」を操作すると動作する（ボタンが正しく動作するか）</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>1. 「種別フィルタ(all/project/task/knowledge/employee)」を各クリック</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>kind を切替して再検索（onClick/href/API が実在し、押すと副作用が起きる）</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>TUC40-010</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>グローバル検索画面</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>「検索入力」を操作すると動作する（ボタンが正しく動作するか）</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>1. 「検索入力」を入力(debounce)</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>/search を叩き結果を種別ラベル付きで表示（onClick/href/API が実在し、押すと副作用が起きる）</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>TUC40-011</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>グローバル検索画面</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>R-T08</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>他人のデータが見えない権限 で可視性担保</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>1. 検索実行</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>他人のデータが見えない権限 内のみヒット(越境自動除外)</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>TUC40-012</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>グローバル検索画面</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>読み上げ対応</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>axe scan で 0 critical/serious</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>1. axe を実行</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>critical/serious 違反 0（semantic role/aria）</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>TUC40-014</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>グローバル検索画面</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>状態永続</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>F5 リロードでログアウトに飛ばない</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>ログイン済</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面で F5</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>保護ガードで維持・状態復元（URL クエリ等）</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>TUC40-015</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>グローバル検索画面</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>到達性</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/apps/web/.qa/テスト仕様書_クライアント版.xlsx
+++ b/apps/web/.qa/テスト仕様書_クライアント版.xlsx
@@ -589,10 +589,10 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8">
@@ -615,10 +615,10 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10">
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="C16" s="3" t="n">
         <v>25</v>
-      </c>
-      <c r="C16" s="3" t="n">
-        <v>21</v>
       </c>
     </row>
     <row r="17">
@@ -732,10 +732,10 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
@@ -745,10 +745,10 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20">
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21">
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C22" s="3" t="n">
         <v>19</v>
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C24" s="3" t="n">
         <v>13</v>
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C25" s="3" t="n">
         <v>9</v>
@@ -836,7 +836,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C26" s="3" t="n">
         <v>14</v>
@@ -849,10 +849,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28">
@@ -862,10 +862,10 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29">
@@ -875,10 +875,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="30">
@@ -891,7 +891,7 @@
         <v>13</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31">
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="33">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="38">
@@ -1151,7 +1151,7 @@
         <v>22</v>
       </c>
       <c r="C50" s="3" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="51">
@@ -1162,7 +1162,7 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>完全性: 全719件 ＝ クライアント可視628件 ＋ 技術専用91件（画面で見えない裏取り=エンジニア版）</t>
+          <t>完全性: 全758件 ＝ クライアント可視663件 ＋ 技術専用95件（画面で見えない裏取り=エンジニア版）</t>
         </is>
       </c>
       <c r="B52" s="3" t="n"/>
@@ -3287,7 +3287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4166,246 +4166,301 @@
       <c r="I20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>SE01-616</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>チャット画面</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>秘密の保持</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>拒んだ添付のファイル名を応答に返さない</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>別スレッドの添付を指定して送信</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>1. 応答本文を見る</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>日本語で「この会話に属さない添付は送信できません」とだけ出る。送ったファイル名が本文に含まれない</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>SE01-610</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>チャット画面</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>表示</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>混雑時に順番待ちが見える</t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>上限まで実行中</t>
         </is>
       </c>
-      <c r="F21" s="3" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>1. 送信する</t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>断られず「順番待ち N 番目」が出続ける（汎用エラーに潰れない）</t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr"/>
-      <c r="I21" s="3" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>SE01-611</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>チャット画面</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>表示</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>根拠の無い待ち時間を出さない</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="E23" s="3" t="inlineStr">
         <is>
           <t>実測データ無し</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr">
+      <c r="F23" s="3" t="inlineStr">
         <is>
           <t>1. 順番待ちを見る</t>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr">
+      <c r="G23" s="3" t="inlineStr">
         <is>
           <t>目安の秒数を出さない（実測が貯まるまで数字を言わない）</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr"/>
-      <c r="I22" s="3" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="H23" s="3" t="inlineStr"/>
+      <c r="I23" s="3" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>SE01-612</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>チャット画面</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>エラー</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>打った文章が消えない</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="E24" s="4" t="inlineStr">
         <is>
           <t>送信を失敗させる</t>
         </is>
       </c>
-      <c r="F23" s="4" t="inlineStr">
+      <c r="F24" s="4" t="inlineStr">
         <is>
           <t>1. 送信して失敗させる</t>
         </is>
       </c>
-      <c r="G23" s="4" t="inlineStr">
+      <c r="G24" s="4" t="inlineStr">
         <is>
           <t>入力欄に文章が戻り、押し直すだけで再送できる</t>
         </is>
       </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I23" s="4" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>SE01-613</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>チャット画面</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>整合性</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t>待っている間に閉じたら席が返る</t>
         </is>
       </c>
-      <c r="E24" s="3" t="inlineStr">
+      <c r="E25" s="4" t="inlineStr">
         <is>
           <t>順番待ち中</t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr">
+      <c r="F25" s="4" t="inlineStr">
         <is>
           <t>1. 画面を閉じる 2. 空き状況を見る</t>
         </is>
       </c>
-      <c r="G24" s="3" t="inlineStr">
+      <c r="G25" s="4" t="inlineStr">
         <is>
           <t>席が戻る（列に残り続けない・GAP-203 で見つけた実バグの回帰）</t>
         </is>
       </c>
-      <c r="H24" s="3" t="inlineStr"/>
-      <c r="I24" s="3" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>SE01-614</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>チャット画面</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>実行経路</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>どの経路で動いたかが分かる</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>1. 実行後に経路表示を見る</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>利用者自身の契約で動いたことが画面か記録で確定できる（意図しない課金経路で動いていないか・GAP-175/178）</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr"/>
-      <c r="I25" s="3" t="inlineStr"/>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
+          <t>SE01-614</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>チャット画面</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>実行経路</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>どの経路で動いたかが分かる</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>1. 実行後に経路表示を見る</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>利用者自身の契約で動いたことが画面か記録で確定できる（意図しない課金経路で動いていないか・GAP-175/178）</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
           <t>SE01-615</t>
         </is>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>チャット画面</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>エラー</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="D27" s="4" t="inlineStr">
         <is>
           <t>未接続と未設定を混同しない</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="E27" s="4" t="inlineStr">
         <is>
           <t>Bridge 未接続 / 経路未設定</t>
         </is>
       </c>
-      <c r="F26" s="4" t="inlineStr">
+      <c r="F27" s="4" t="inlineStr">
         <is>
           <t>1. それぞれで送信</t>
         </is>
       </c>
-      <c r="G26" s="4" t="inlineStr">
+      <c r="G27" s="4" t="inlineStr">
         <is>
           <t>出る案内が別物になる（全部「パソコンを繋いでください」に潰れない・GAP-206）</t>
         </is>
       </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I26" s="4" t="inlineStr"/>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4877,7 +4932,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5454,6 +5509,92 @@
       </c>
       <c r="I13" s="4" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>SF02-315</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>フェーズ管理画面</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>表示</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>提案の重複・二重処理が日本語で伝わる</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>保留中のフェーズ提案がある状態</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>1. もう一度提案する 2. 処理済みの提案を承認する</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>日本語で理由と次の行動が出る。`a pending phase proposal already exists for this project` のような英語が出ない</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>SF02-316</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>フェーズ管理画面</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>整合性</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>確定は明示の承認が要り、確定後の成果物は変わらない</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>active フェーズにモックがある</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>1. 確認なしで確定する 2. 承認つきで確定する 3. 凍結後にモックを変更・削除する</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>確認なしは で理由が出る。承認つきなら frozen になり次フェーズが active になる。凍結後の変更・削除は 409 で、DB の内容は 1 文字も変わらない</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5465,7 +5606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6429,6 +6570,217 @@
       </c>
       <c r="I22" s="4" t="inlineStr"/>
     </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>SG01-217</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>成果物ビューア画面</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>表示</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>同時編集の衝突が日本語で伝わる</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>2 つのタブで同じ成果物を改訂</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>1. 片方を保存 2. もう片方も保存する</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>「ほかの編集と同時に保存されたため反映できませんでした。最新の内容を読み直してください」と日本語で出る。内部の版番号や英語が出ない</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>SG01-221</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>成果物ビューア画面</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>拒否 (409/) の理由は API の文言をそのまま画面に出す</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>確定済みフェーズの成果物、または唯一の版</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>1. 破棄 / 削除 / 保存を試す</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>画面の文言が API の detail (「確定済みのフェーズの成果物は変更できません…」等) と一致する。画面側の固定文で理由を書き換えない</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>SG01-218</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>成果物ビューア画面</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>表示</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>修正案の二重操作が日本語で伝わる</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>すでに処理済みの修正案</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>1. もう一度承認/却下する</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>日本語で「すでに処理済み」と出る。`proposal already resolved` のような英語が出ない</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr"/>
+      <c r="I25" s="3" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>SG01-219</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>成果物ビューア画面</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>表示</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>書き込みが「誰のものか」名前で分かる</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>社内メンバー 1 人 + クライアント窓口 1 人が同じ対象にコメント</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>1. 両方からコメントする 2. 社内の画面で一覧を見る</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>**それぞれの表示名**が出る。「クライアント（招待）」「メンバー 8f3bbf48」のような **種別だけ・UUID の断片**にならない。クライアント発か社内発かも見分けられる</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>SG01-220</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>成果物ビューア画面</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>整合性</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>名前が引けない書き込みでも一覧から消えない</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>表示名が未設定の利用者のコメント</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>1. その人がコメントする 2. 一覧を見る</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>名前は空欄 (既定の呼び方) になるが、**発言そのものは一覧に出る**。誰か分からないより、発言が消えるほうが悪い</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6440,7 +6792,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7106,7 +7458,7 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>SH01-215</t>
+          <t>SH01-212</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
@@ -7116,35 +7468,164 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
+          <t>表示</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>確定フェーズの変更を止める文言が日本語</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>確定済みフェーズのモック</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>1. 編集して保存する</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>「確定済みのフェーズの成果物は変更できません。追加や修正は次のフェーズで行ってください。」と、次にどうすればよいかまで日本語で出る</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>SH01-213</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>モックビューア画面</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>表示</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>書き込みが「誰のものか」名前で分かる</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>社内メンバー 1 人 + クライアント窓口 1 人が同じ対象にコメント</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>1. 両方からコメントする 2. 社内の画面で一覧を見る</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>**それぞれの表示名**が出る。「クライアント（招待）」「メンバー 8f3bbf48」のような **種別だけ・UUID の断片**にならない。クライアント発か社内発かも見分けられる</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>SH01-214</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>モックビューア画面</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>バリデーション</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>既にある画面と同じ名前では作れず、理由が分かる</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>同名の画面モックが既にある</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>1. 同じ名前でもう一度作る</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>409 で「既にあります。別の名前にするか、既存の画面へ新しい版として追加してください」と日本語で出る。**「サーバー側で問題…」にならない** (利用者の入力起因を運営の障害と偽らない)</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>SH01-216</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>モックビューア画面</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
           <t>エラー</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>URL の ID が UUID の形式でないときの案内</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>サインイン済</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>1. アドレス欄を `/mocks/undefined` 等、ID を壊した URL に書き換えて開く</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>「対象が見つかりません。」(404) が返る。「サーバー側で問題が発生しました。時間をおいて…」等の**一時障害の案内が出ない**（ID の形式不正は時間をおいても直らないため。一時障害の文言は再試行で直るものにだけ使う）</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I16" s="4" t="inlineStr"/>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7960,7 +8441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -8837,6 +9318,45 @@
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>SI02-307</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>タスク詳細(6タブ)画面</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>表示</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>書き込みが「誰のものか」名前で分かる</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>社内メンバー 1 人 + クライアント窓口 1 人が同じ対象にコメント</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>1. 両方からコメントする 2. 社内の画面で一覧を見る</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>**それぞれの表示名**が出る。「クライアント（招待）」「メンバー 8f3bbf48」のような **種別だけ・UUID の断片**にならない。クライアント発か社内発かも見分けられる</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr"/>
+      <c r="I21" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9794,7 +10314,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -10414,6 +10934,84 @@
       </c>
       <c r="I14" s="4" t="inlineStr"/>
     </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>SJ01-112</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>承認インボックス画面</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>整合性</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>インボックスの承認がタスク本体まで効く</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>awaiting のタスクと pending の通知がある</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>1. 一覧で承認する 2. **タスク側の状態を突合する**</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>一覧から消えるだけでなく、タスクの lifecycle が done になる。一覧から消えても本体が awaiting のままなら幽霊承認</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr"/>
+      <c r="I15" s="3" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>SJ01-113</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>承認インボックス画面</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>整合性</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>却下は差戻としてタスク本体に伝わり、承認と区別できる</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>1. 一覧で却下する (理由を入れる) 2. タスク側を突合する</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>inbox=rejected / タスク=blocked + 理由が残る。タスク画面からの差戻と同じ結果になる (入口で結果が変わらない)</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr"/>
+      <c r="I16" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10425,7 +11023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -10873,12 +11471,1692 @@
       </c>
       <c r="I10" s="4" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>SK01-404</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>ナレッジエクスプローラ画面</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>表示</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>存在しない語の検索は 0 件になる</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>ナレッジが数件ある</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>1. 本文のどこにも無いデタラメな語で検索する</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>0 件。**無関係なナレッジが「一番近いから」という理由で出ない** (意味検索の足切り)。該当がある語では従来どおり出る</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr"/>
+      <c r="I11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>SK01-405</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>ナレッジエクスプローラ画面</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>整合性</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>検索の足切りは RAG にも効く</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>1. 検索と RAG が同じ検索関数を使っていることを確認する</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>デタラメな文脈で無関係なナレッジがプロンプトへ注入されない</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr"/>
+      <c r="I12" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>画面</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>テスト観点</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>テスト項目</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>前提条件</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>操作手順</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>期待結果</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>SK02-001</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>昇格レビュー画面</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>画面表示</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>画面が正常表示（全 UI 要素・モック準拠）</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>1. 昇格レビュー を開く</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>SK02-002</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>昇格レビュー画面</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>視覚忠実度</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>配色/角丸/タイポが design token 準拠</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面を目視</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>SK02-003</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>昇格レビュー画面</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>データ取得</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>loading skeleton 表示（昇格候補）</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>取得未完</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>1. 昇格レビュー を開き取得完了前を観察</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>SK02-004</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>昇格レビュー画面</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>空データ</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>0 件時の空状態（昇格候補）</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>/knowledge/promotions が空配列</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1. データ0件で開く</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>空状態メッセージを表示（/undefined 参照にならない）</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>SK02-005</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>昇格レビュー画面</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>取得失敗の inline error + toast（昇格候補）</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>/knowledge/promotions が 5xx</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1. API を でモックし開く</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>エラー表示 の inline error 表示 かつ toast 発火</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>SK02-007</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>昇格レビュー画面</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>「承認」を操作すると動作する（ボタンが正しく動作するか）</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. 「承認」をクリック</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>昇格処理→楽観除外（onClick/href/API が実在し、押すと副作用が起きる）</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>SK02-008</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>昇格レビュー画面</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>「却下」を操作すると動作する（ボタンが正しく動作するか）</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>1. 「却下」をクリック</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>却下 API 無し→クライアント側 dismiss（onClick/href/API が実在し、押すと副作用が起きる）</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>SK02-009</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>昇格レビュー画面</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>楽観更新</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>承認: 成功で即時反映</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>対象が存在</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>1. 承認 を実行</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>昇格承認 呼び出し前にUIへ楽観反映→成功で確定（別GET再取得で反映）</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>SK02-010</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>昇格レビュー画面</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>楽観更新</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>承認: 失敗でロールバック</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>サーバ 4xx/5xx</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>1. 承認 を実行しAPIが失敗</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>楽観反映が元に戻り、inline error + toast を表示</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>SK02-011</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>昇格レビュー画面</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>承認: API 失敗時 inline error + toast</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>接続失敗/レート</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>1. 承認 を失敗させる</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>エラー表示 + toast、状態は不整合にならない</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>SK02-012</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>昇格レビュー画面</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>受容差分</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>却下はクライアント dismiss</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>1. 却下</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>reject API 無しのため一覧から即時除去(honest)</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>SK02-013</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>昇格レビュー画面</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>読み上げ対応</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>axe scan で 0 critical/serious</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>1. axe を実行</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>critical/serious 違反 0（semantic role/aria）</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>SK02-015</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>昇格レビュー画面</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>状態永続</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>F5 リロードでログアウトに飛ばない</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>ログイン済</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面で F5</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>保護ガードで維持・状態復元（URL クエリ等）</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>SK02-016</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>昇格レビュー画面</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>到達性</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>SK02-017</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>昇格レビュー画面</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>正常系</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>採用した候補だけが正式なナレッジになる</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>pending の候補が 2 件</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>1. 1 件を採用、1 件を却下</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>採用 → approved + knowledge_nodes に 1 件でき、候補から辿れる。却下 → rejected でナレッジはできない。両者が一覧で区別できる</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr"/>
+      <c r="I16" s="3" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>画面</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>テスト観点</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>テスト項目</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>前提条件</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>操作手順</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>期待結果</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>SL01-001</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>クライアント招待管理画面</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>画面表示</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>画面が正常表示（全 UI 要素・モック準拠）</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>1. クライアント招待管理 を開く</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>SL01-002</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>クライアント招待管理画面</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>視覚忠実度</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>配色/角丸/タイポが design token 準拠</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面を目視</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>SL01-003</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>クライアント招待管理画面</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>データ取得</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>loading skeleton 表示（招待一覧）</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>取得未完</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>1. クライアント招待管理 を開き取得完了前を観察</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>SL01-004</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>クライアント招待管理画面</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>空データ</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>0 件時の空状態（招待一覧）</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>/client-invitations?project_id が空配列</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1. データ0件で開く</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>空状態メッセージを表示（/undefined 参照にならない）</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>SL01-005</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>クライアント招待管理画面</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>取得失敗の inline error + toast（招待一覧）</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>/client-invitations?project_id が 5xx</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1. API を でモックし開く</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>エラー表示 の inline error 表示 かつ toast 発火</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>SL01-007</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>クライアント招待管理画面</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>「招待を発行」を操作すると動作する（ボタンが正しく動作するか）</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. 「招待を発行」をクリック</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>→raw token を1度だけバナー表示(R-T08 再取得不可)（onClick/href/API が実在し、押すと副作用が起きる）</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>SL01-008</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>クライアント招待管理画面</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>「失効」を操作すると動作する（ボタンが正しく動作するか）</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>1. 「失効」をクリック</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>revoke(楽観)（onClick/href/API が実在し、押すと副作用が起きる）</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>SL01-009</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>クライアント招待管理画面</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>発行(): 送信→反映</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>必須入力済</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>1. 発行() を実行</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>/client-invitations 呼び出し→成功表示→別GET/DBに反映</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>SL01-010</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>クライアント招待管理画面</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>発行(): API 失敗時 inline error + toast</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>接続失敗/レート</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>1. 発行() を失敗させる</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>エラー表示 + toast、状態は不整合にならない</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>SL01-011</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>クライアント招待管理画面</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>楽観更新</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>失効(revoke): 成功で即時反映</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>対象が存在</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>1. 失効(revoke) を実行</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>/client-invitations/{id}/revoke 呼び出し前にUIへ楽観反映→成功で確定（別GET再取得で反映）</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>SL01-012</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>クライアント招待管理画面</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>楽観更新</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>失効(revoke): 失敗でロールバック</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>サーバ 4xx/5xx</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>1. 失効(revoke) を実行しAPIが失敗</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>楽観反映が元に戻り、inline error + toast を表示</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>SL01-013</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>クライアント招待管理画面</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>失効(revoke): API 失敗時 inline error + toast</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>接続失敗/レート</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>1. 失効(revoke) を失敗させる</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>エラー表示 + toast、状態は不整合にならない</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>SL01-014</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>クライアント招待管理画面</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>受容差分</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>再送ボタンは非表示</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>1. 一覧確認</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>resend API 無しのため非表示(honest)</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>SL01-015</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>クライアント招待管理画面</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>読み上げ対応</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>axe scan で 0 critical/serious</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>1. axe を実行</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>critical/serious 違反 0（semantic role/aria）</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>SL01-017</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>クライアント招待管理画面</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>状態永続</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>F5 リロードでログアウトに飛ばない</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>ログイン済</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面で F5</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>保護ガードで維持・状態復元（URL クエリ等）</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>SL01-018</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>クライアント招待管理画面</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>到達性</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>SL01-304</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>クライアント招待管理画面</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>整合性</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>「失効」が次のアクセスから効く</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>相手がすでにサインインしている招待</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>1. 一覧から失効させる 2. 相手側で操作してもらう</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>相手はその場で入れなくなる。「失効させたのにしばらく見られる」状態にならない</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>SL01-052</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>クライアント招待管理画面</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>整合性</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>使わせる意図のある表が 他人のデータが見えない権限 で丸ごと塞がれていない</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>1. 実 DB のポリシーを走査する</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>permissive な policy を持つ表に、`restrictive for all using(false)` の蓋が同居していない。**同居すると AND で全部 false になり、何を許可しても読み書きできない**</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>SL01-053</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>クライアント招待管理画面</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>初期構築</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>構築手順を最後まで流しても蓋が復活しない</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>ローカル構築を最初から実行</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>1. `scripts/dev-bootstrap.sh` 相当を流す 2. ポリシーを確認</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>仮の default-deny が復活していない（revoke 再適用パスに巻き込まれない）</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10948,12 +13226,12 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>SK02-001</t>
+          <t>SL02-001</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>昇格レビュー画面</t>
+          <t>クライアントサインイン画面</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -10973,7 +13251,7 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>1. 昇格レビュー を開く</t>
+          <t>1. クライアントサインイン を開く</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
@@ -10991,12 +13269,12 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>SK02-002</t>
+          <t>SL02-002</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>昇格レビュー画面</t>
+          <t>クライアントサインイン画面</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -11034,37 +13312,37 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>SK02-003</t>
+          <t>SL02-003</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>昇格レビュー画面</t>
+          <t>クライアントサインイン画面</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>データ取得</t>
+          <t>入力フォーム</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>loading skeleton 表示（昇格候補）</t>
+          <t>初期値/placeholder（招待トークン）</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>取得未完</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>1. 昇格レビュー を開き取得完了前を観察</t>
+          <t>1. フォームを開く</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
+          <t>招待トークン の初期値/placeholder が正しい</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
@@ -11077,37 +13355,37 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>SK02-004</t>
+          <t>SL02-004</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>昇格レビュー画面</t>
+          <t>クライアントサインイン画面</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>空データ</t>
+          <t>バリデーション</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>0 件時の空状態（昇格候補）</t>
+          <t>招待トークン: 必須/最小10</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>/knowledge/promotions が空配列</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>1. データ0件で開く</t>
+          <t>1. 招待トークン に不正値/未入力を入れる</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>空状態メッセージを表示（/undefined 参照にならない）</t>
+          <t>エラー表示 かつ 送信ボタン無効</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
@@ -11120,37 +13398,37 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>SK02-005</t>
+          <t>SL02-005</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>昇格レビュー画面</t>
+          <t>クライアントサインイン画面</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>エラー</t>
+          <t>入力フォーム</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>取得失敗の inline error + toast（昇格候補）</t>
+          <t>初期値/placeholder（表示名）</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>/knowledge/promotions が 5xx</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>1. API を でモックし開く</t>
+          <t>1. フォームを開く</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>エラー表示 の inline error 表示 かつ toast 発火</t>
+          <t>表示名 の初期値/placeholder が正しい</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
@@ -11163,22 +13441,22 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>SK02-007</t>
+          <t>SL02-006</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>昇格レビュー画面</t>
+          <t>クライアントサインイン画面</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>インタラクション</t>
+          <t>バリデーション</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>「承認」を操作すると動作する（ボタンが正しく動作するか）</t>
+          <t>表示名: 任意</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -11188,12 +13466,12 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>1. 「承認」をクリック</t>
+          <t>1. 表示名 に不正値/未入力を入れる</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>昇格処理→楽観除外（onClick/href/API が実在し、押すと副作用が起きる）</t>
+          <t>エラー表示 かつ 送信ボタン無効</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -11206,12 +13484,12 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>SK02-008</t>
+          <t>SL02-007</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>昇格レビュー画面</t>
+          <t>クライアントサインイン画面</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -11221,7 +13499,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>「却下」を操作すると動作する（ボタンが正しく動作するか）</t>
+          <t>「プロジェクトを開く」を操作すると動作する（ボタンが正しく動作するか）</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -11231,12 +13509,12 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>1. 「却下」をクリック</t>
+          <t>1. 「プロジェクトを開く」をクリック</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>却下 API 無し→クライアント側 dismiss（onClick/href/API が実在し、押すと副作用が起きる）</t>
+          <t>signin→client_portal cookie→/client/s_l03 遷移（onClick/href/API が実在し、押すと副作用が起きる）</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -11249,37 +13527,37 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>SK02-009</t>
+          <t>SL02-008</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>昇格レビュー画面</t>
+          <t>クライアントサインイン画面</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>楽観更新</t>
+          <t>更新</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>承認: 成功で即時反映</t>
+          <t>サインイン: 送信→反映</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>対象が存在</t>
+          <t>必須入力済</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>1. 承認 を実行</t>
+          <t>1. サインイン を実行</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>昇格承認 呼び出し前にUIへ楽観反映→成功で確定（別GET再取得で反映）</t>
+          <t>/client/auth/signin 呼び出し→成功表示→別GET/DBに反映</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -11292,37 +13570,37 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>SK02-010</t>
+          <t>SL02-009</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>昇格レビュー画面</t>
+          <t>クライアントサインイン画面</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>楽観更新</t>
+          <t>エラー</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>承認: 失敗でロールバック</t>
+          <t>サインイン: API 失敗時 inline error + toast</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>サーバ 4xx/5xx</t>
+          <t>接続失敗/レート</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>1. 承認 を実行しAPIが失敗</t>
+          <t>1. サインイン を失敗させる</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>楽観反映が元に戻り、inline error + toast を表示</t>
+          <t>エラー表示 + toast、状態は不整合にならない</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -11335,37 +13613,37 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>SK02-011</t>
+          <t>SL02-010</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>昇格レビュー画面</t>
+          <t>クライアントサインイン画面</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>エラー</t>
+          <t>認証</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>承認: API 失敗時 inline error + toast</t>
+          <t>invalid/410 expired 文言化</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>接続失敗/レート</t>
+          <t>無効/期限切れトークン</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>1. 承認 を失敗させる</t>
+          <t>1. 無効トークンで送信</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>エラー表示 + toast、状態は不整合にならない</t>
+          <t>→『招待トークンが無効』/410→『有効期限切れ』</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -11378,22 +13656,22 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>SK02-012</t>
+          <t>SL02-011</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>昇格レビュー画面</t>
+          <t>クライアントサインイン画面</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>受容差分</t>
+          <t>読み上げ対応</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>却下はクライアント dismiss</t>
+          <t>axe scan で 0 critical/serious</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -11403,12 +13681,12 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>1. 却下</t>
+          <t>1. axe を実行</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>reject API 無しのため一覧から即時除去(honest)</t>
+          <t>critical/serious 違反 0（semantic role/aria）</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -11421,37 +13699,37 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>SK02-013</t>
+          <t>SL02-013</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>昇格レビュー画面</t>
+          <t>クライアントサインイン画面</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>読み上げ対応</t>
+          <t>状態永続</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>axe scan で 0 critical/serious</t>
+          <t>F5 リロードでログアウトに飛ばない</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>ログイン済</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>1. axe を実行</t>
+          <t>1. 画面で F5</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>critical/serious 違反 0（semantic role/aria）</t>
+          <t>保護ガードで維持・状態復元（URL クエリ等）</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -11464,37 +13742,37 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>SK02-015</t>
+          <t>SL02-014</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>昇格レビュー画面</t>
+          <t>クライアントサインイン画面</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>状態永続</t>
+          <t>到達性</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>F5 リロードでログアウトに飛ばない</t>
+          <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>ログイン済</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>1. 画面で F5</t>
+          <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>保護ガードで維持・状態復元（URL クエリ等）</t>
+          <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
@@ -11507,37 +13785,37 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>SK02-016</t>
+          <t>SL02-207</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>昇格レビュー画面</t>
+          <t>クライアントサインイン画面</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>到達性</t>
+          <t>表示</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
+          <t>期限切れ・失効の理由が日本語で分かる</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>期限切れの招待リンク / 失効させた招待リンク</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
+          <t>1. それぞれのリンクを開く</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
+          <t>どちらも入れず、理由が日本語で出る。内部の識別子 (invitation_id / token / expired 等) が画面に出ない</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
@@ -11552,13 +13830,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -11622,12 +13900,12 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>SL01-001</t>
+          <t>SL03-001</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>クライアント招待管理画面</t>
+          <t>クライアントプロジェクトビュー画面</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -11647,7 +13925,7 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>1. クライアント招待管理 を開く</t>
+          <t>1. クライアントプロジェクトビュー を開く</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
@@ -11665,12 +13943,12 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>SL01-002</t>
+          <t>SL03-002</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>クライアント招待管理画面</t>
+          <t>クライアントプロジェクトビュー画面</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -11708,12 +13986,12 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>SL01-003</t>
+          <t>SL03-003</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>クライアント招待管理画面</t>
+          <t>クライアントプロジェクトビュー画面</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -11723,7 +14001,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>loading skeleton 表示（招待一覧）</t>
+          <t>loading skeleton 表示（限定ビュー(client JWT)）</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -11733,7 +14011,7 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>1. クライアント招待管理 を開き取得完了前を観察</t>
+          <t>1. クライアントプロジェクトビュー を開き取得完了前を観察</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
@@ -11751,12 +14029,12 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>SL01-004</t>
+          <t>SL03-004</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>クライアント招待管理画面</t>
+          <t>クライアントプロジェクトビュー画面</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -11766,12 +14044,12 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>0 件時の空状態（招待一覧）</t>
+          <t>0 件時の空状態（限定ビュー(client JWT)）</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>/client-invitations?project_id が空配列</t>
+          <t>/client/projects/{id} が空配列</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -11794,12 +14072,12 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>SL01-005</t>
+          <t>SL03-005</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>クライアント招待管理画面</t>
+          <t>クライアントプロジェクトビュー画面</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -11809,12 +14087,12 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>取得失敗の inline error + toast（招待一覧）</t>
+          <t>取得失敗の inline error + toast（限定ビュー(client JWT)）</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>/client-invitations?project_id が 5xx</t>
+          <t>/client/projects/{id} が 5xx</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -11837,37 +14115,37 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>SL01-007</t>
+          <t>SL03-007</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>クライアント招待管理画面</t>
+          <t>クライアントプロジェクトビュー画面</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>インタラクション</t>
+          <t>R-T08越境</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>「招待を発行」を操作すると動作する（ボタンが正しく動作するか）</t>
+          <t>他プロジェクトは 拒否</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>他プロジェクトの id</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>1. 「招待を発行」をクリック</t>
+          <t>1. 越境 id でアクセス</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>→raw token を1度だけバナー表示(R-T08 再取得不可)（onClick/href/API が実在し、押すと副作用が起きる）</t>
+          <t>API が cross_project→拒否表示(越境不可)</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -11880,37 +14158,37 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>SL01-008</t>
+          <t>SL03-008</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>クライアント招待管理画面</t>
+          <t>クライアントプロジェクトビュー画面</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>インタラクション</t>
+          <t>認証</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>「失効」を操作すると動作する（ボタンが正しく動作するか）</t>
+          <t>token 未保有→サインイン誘導</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>cookie 無し</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>1. 「失効」をクリック</t>
+          <t>1. token 無しで開く</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>revoke(楽観)（onClick/href/API が実在し、押すと副作用が起きる）</t>
+          <t>『サインインが必要』表示</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -11923,37 +14201,37 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>SL01-009</t>
+          <t>SL03-009</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>クライアント招待管理画面</t>
+          <t>クライアントプロジェクトビュー画面</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>更新</t>
+          <t>読み上げ対応</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>発行(): 送信→反映</t>
+          <t>axe scan で 0 critical/serious</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>必須入力済</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>1. 発行() を実行</t>
+          <t>1. axe を実行</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>/client-invitations 呼び出し→成功表示→別GET/DBに反映</t>
+          <t>critical/serious 違反 0（semantic role/aria）</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -11966,37 +14244,37 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>SL01-010</t>
+          <t>SL03-011</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>クライアント招待管理画面</t>
+          <t>クライアントプロジェクトビュー画面</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>エラー</t>
+          <t>状態永続</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>発行(): API 失敗時 inline error + toast</t>
+          <t>F5 リロードでログアウトに飛ばない</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>接続失敗/レート</t>
+          <t>ログイン済</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>1. 発行() を失敗させる</t>
+          <t>1. 画面で F5</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>エラー表示 + toast、状態は不整合にならない</t>
+          <t>保護ガードで維持・状態復元（URL クエリ等）</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -12009,37 +14287,37 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>SL01-011</t>
+          <t>SL03-012</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>クライアント招待管理画面</t>
+          <t>クライアントプロジェクトビュー画面</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>楽観更新</t>
+          <t>到達性</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>失効(revoke): 成功で即時反映</t>
+          <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>対象が存在</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>1. 失効(revoke) を実行</t>
+          <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>/client-invitations/{id}/revoke 呼び出し前にUIへ楽観反映→成功で確定（別GET再取得で反映）</t>
+          <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -12052,37 +14330,37 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>SL01-012</t>
+          <t>SL03-208</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>クライアント招待管理画面</t>
+          <t>クライアントプロジェクトビュー画面</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>楽観更新</t>
+          <t>秘密の保持</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>失効(revoke): 失敗でロールバック</t>
+          <t>他人の案件へは参照も投稿も通らない</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>サーバ 4xx/5xx</t>
+          <t>クライアント A の券 / 他社の案件 B とその成果物</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>1. 失効(revoke) を実行しAPIが失敗</t>
+          <t>1. 自分の成果物へコメントして通ることを確かめる 2. 案件 B の参照・コメント・成果物一覧・モック一覧・概要を試す</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>楽観反映が元に戻り、inline error + toast を表示</t>
+          <t>自分のものは通り、他人のものは /404。**通る操作があることを先に確かめてから拒否を見る**（全部拒否なら認可の証明にならない）。拒否の本文に他人の案件名が 1 文字も出ない</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -12095,37 +14373,37 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>SL01-013</t>
+          <t>SL03-209</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>クライアント招待管理画面</t>
+          <t>クライアントプロジェクトビュー画面</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>エラー</t>
+          <t>表示</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>失効(revoke): API 失敗時 inline error + toast</t>
+          <t>クライアントの書き込みが社内へ「誰のものか」分かる形で届く</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>接続失敗/レート</t>
+          <t>クライアントがコメントした直後</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>1. 失効(revoke) を失敗させる</t>
+          <t>1. 社内の画面で同じ対象を見る</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>エラー表示 + toast、状態は不整合にならない</t>
+          <t>クライアントの表示名つきで出る。社内の書き込みと見分けられる</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -12138,37 +14416,37 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>SL01-014</t>
+          <t>SL03-210</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>クライアント招待管理画面</t>
+          <t>クライアントプロジェクトビュー画面</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>受容差分</t>
+          <t>秘密の保持</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>再送ボタンは非表示</t>
+          <t>招待を失効させたら、配布済みの券もその場で止まる</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>クライアントがサインイン済み (券を持っている)</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>1. 一覧確認</t>
+          <t>1. 失効前に読めることを確かめる 2. 招待を失効させる 3. **同じ券で**同じ画面・API を叩く</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>resend API 無しのため非表示(honest)</t>
+          <t>失効の直後から拒否される。券の有効期限 (24 時間) を待たない。文言は「この招待は取り消されています…」</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
@@ -12181,37 +14459,37 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>SL01-015</t>
+          <t>SL03-211</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>クライアント招待管理画面</t>
+          <t>クライアントプロジェクトビュー画面</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>読み上げ対応</t>
+          <t>秘密の保持</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>axe scan で 0 critical/serious</t>
+          <t>案件が消えたら、その案件の券も通らない</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>券を持っているクライアント / 案件を削除</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>1. axe を実行</t>
+          <t>1. 削除後に同じ券で開く</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>critical/serious 違反 0（semantic role/aria）</t>
+          <t>拒否される。消えた案件の券が生き続けない</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
@@ -12220,1311 +14498,6 @@
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>SL01-017</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>クライアント招待管理画面</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>状態永続</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>F5 リロードでログアウトに飛ばない</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>ログイン済</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>1. 画面で F5</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>保護ガードで維持・状態復元（URL クエリ等）</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I16" s="4" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>SL01-018</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>クライアント招待管理画面</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>到達性</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I17" s="4" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>SL01-052</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>クライアント招待管理画面</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>整合性</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>使わせる意図のある表が 他人のデータが見えない権限 で丸ごと塞がれていない</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>1. 実 DB のポリシーを走査する</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>permissive な policy を持つ表に、`restrictive for all using(false)` の蓋が同居していない。**同居すると AND で全部 false になり、何を許可しても読み書きできない**</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I18" s="4" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>SL01-053</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>クライアント招待管理画面</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>初期構築</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>構築手順を最後まで流しても蓋が復活しない</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>ローカル構築を最初から実行</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>1. `scripts/dev-bootstrap.sh` 相当を流す 2. ポリシーを確認</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t>仮の default-deny が復活していない（revoke 再適用パスに巻き込まれない）</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I19" s="4" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="7" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>画面</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>テスト観点</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>テスト項目</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>前提条件</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>操作手順</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>期待結果</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>結果</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>SL02-001</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>クライアントサインイン画面</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>画面表示</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>画面が正常表示（全 UI 要素・モック準拠）</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>1. クライアントサインイン を開く</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I2" s="4" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>SL02-002</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>クライアントサインイン画面</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>視覚忠実度</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>配色/角丸/タイポが design token 準拠</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>1. 画面を目視</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>SL02-003</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>クライアントサインイン画面</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>入力フォーム</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>初期値/placeholder（招待トークン）</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>1. フォームを開く</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>招待トークン の初期値/placeholder が正しい</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>SL02-004</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>クライアントサインイン画面</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>バリデーション</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>招待トークン: 必須/最小10</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>1. 招待トークン に不正値/未入力を入れる</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>エラー表示 かつ 送信ボタン無効</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>SL02-005</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>クライアントサインイン画面</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>入力フォーム</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>初期値/placeholder（表示名）</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>1. フォームを開く</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>表示名 の初期値/placeholder が正しい</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>SL02-006</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>クライアントサインイン画面</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>バリデーション</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>表示名: 任意</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>1. 表示名 に不正値/未入力を入れる</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>エラー表示 かつ 送信ボタン無効</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>SL02-007</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>クライアントサインイン画面</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>インタラクション</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>「プロジェクトを開く」を操作すると動作する（ボタンが正しく動作するか）</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>1. 「プロジェクトを開く」をクリック</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>signin→client_portal cookie→/client/s_l03 遷移（onClick/href/API が実在し、押すと副作用が起きる）</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>SL02-008</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>クライアントサインイン画面</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>サインイン: 送信→反映</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>必須入力済</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>1. サインイン を実行</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>/client/auth/signin 呼び出し→成功表示→別GET/DBに反映</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>SL02-009</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>クライアントサインイン画面</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>エラー</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>サインイン: API 失敗時 inline error + toast</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>接続失敗/レート</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>1. サインイン を失敗させる</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>エラー表示 + toast、状態は不整合にならない</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>SL02-010</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>クライアントサインイン画面</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>認証</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>invalid/410 expired 文言化</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>無効/期限切れトークン</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>1. 無効トークンで送信</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>→『招待トークンが無効』/410→『有効期限切れ』</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>SL02-011</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>クライアントサインイン画面</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>読み上げ対応</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>axe scan で 0 critical/serious</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>1. axe を実行</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>critical/serious 違反 0（semantic role/aria）</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>SL02-013</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>クライアントサインイン画面</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>状態永続</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>F5 リロードでログアウトに飛ばない</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>ログイン済</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>1. 画面で F5</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>保護ガードで維持・状態復元（URL クエリ等）</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I13" s="4" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>SL02-014</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>クライアントサインイン画面</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>到達性</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I14" s="4" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="7" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>画面</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>テスト観点</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>テスト項目</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>前提条件</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>操作手順</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>期待結果</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>結果</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>SL03-001</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>クライアントプロジェクトビュー画面</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>画面表示</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>画面が正常表示（全 UI 要素・モック準拠）</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>1. クライアントプロジェクトビュー を開く</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I2" s="4" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>SL03-002</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>クライアントプロジェクトビュー画面</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>視覚忠実度</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>配色/角丸/タイポが design token 準拠</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>1. 画面を目視</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>SL03-003</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>クライアントプロジェクトビュー画面</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>データ取得</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>loading skeleton 表示（限定ビュー(client JWT)）</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>取得未完</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>1. クライアントプロジェクトビュー を開き取得完了前を観察</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>SL03-004</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>クライアントプロジェクトビュー画面</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>空データ</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>0 件時の空状態（限定ビュー(client JWT)）</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>/client/projects/{id} が空配列</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>1. データ0件で開く</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>空状態メッセージを表示（/undefined 参照にならない）</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>SL03-005</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>クライアントプロジェクトビュー画面</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>エラー</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>取得失敗の inline error + toast（限定ビュー(client JWT)）</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>/client/projects/{id} が 5xx</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>1. API を でモックし開く</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>エラー表示 の inline error 表示 かつ toast 発火</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>SL03-007</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>クライアントプロジェクトビュー画面</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>R-T08越境</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>他プロジェクトは 拒否</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>他プロジェクトの id</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>1. 越境 id でアクセス</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>API が cross_project→拒否表示(越境不可)</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>SL03-008</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>クライアントプロジェクトビュー画面</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>認証</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>token 未保有→サインイン誘導</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>cookie 無し</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>1. token 無しで開く</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>『サインインが必要』表示</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>SL03-009</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>クライアントプロジェクトビュー画面</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>読み上げ対応</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>axe scan で 0 critical/serious</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>1. axe を実行</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>critical/serious 違反 0（semantic role/aria）</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>SL03-011</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>クライアントプロジェクトビュー画面</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>状態永続</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>F5 リロードでログアウトに飛ばない</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>ログイン済</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>1. 画面で F5</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>保護ガードで維持・状態復元（URL クエリ等）</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>SL03-012</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>クライアントプロジェクトビュー画面</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>到達性</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13845,43 +14818,47 @@
       <c r="I7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>SM01-008</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>議事録アップロード画面</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>更新</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>アップロード→transcription: 送信→反映</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>必須入力済</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>1. アップロード→transcription を実行</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>upload-url→→ /meetings→transcribe→poll→transcript-url 呼び出し→成功表示→別GET/DBに反映</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -14900,7 +15877,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -15519,6 +16496,217 @@
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>SO01-405</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)画面</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>バリデーション</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>式の誤りは「どこが悪いか」まで日本語で出る</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>不正な cron 式（空の項目 / 範囲の逆転 / 数字以外）</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>1. それぞれ保存する 2. 文言を見る</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>日本語で、式のどの項目が悪いかが分かる。一般的な「入力が不正です」で終わらない</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>SO01-406</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)画面</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>実行</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>「今すぐ実行」が action を最後まで動かし、履歴に残る (G-15)</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>予定が 1 件ある</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>1. 今すぐ実行 2. 実行履歴を見る</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>結果が done / deferred (PC 未接続) のどちらかで返り、「実行に失敗しました: … transaction is aborted」のような内部エラーが出ない。実行履歴に 1 行 (状態・時刻) が増える</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>SO01-407</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)画面</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>有効/無効の切替が保存され、次回時刻が追随する</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>無効の予定が 1 件</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>1. 有効に切り替える 2. 無効に戻す</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>どちらも 。有効化で次回時刻が入り、無効化で空になる。 にならない</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>SO01-408</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)画面</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>実行</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>定刻に本当に発火する (G-11: 外部の見張り役が実在する)</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>enabled=true・毎分の予定</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>1. 数分待つ 2. 実行履歴と次回時刻を見る</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>次回時刻が進み、履歴に自動実行の行が増える (Inngest の user-schedules が動いている)</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>SO01-409</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)画面</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>実行</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>PC が落ちていても 15 分以内にサーバー側の滑り止めが拾う (G-11: Inngest の user-schedules が本番に実在する)</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>enabled=true の予定・Bridge 未接続</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>1. 15 分以上待つ 2. 履歴と次回時刻を見る</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>15 分以内に 1 回発火し履歴が増える</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr"/>
+      <c r="I19" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -18041,7 +19229,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -18406,7 +19594,7 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>ST01-220</t>
+          <t>ST01-235</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -18416,27 +19604,27 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>初期構築</t>
+          <t>秘密の保持</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>新しい環境で最初の運営を作る手順が存在し、そのとおりにやれば運営画面に入れる</t>
+          <t>外部サービスの応答をそのまま利用者に見せない</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>誰も運営でない DB</t>
+          <t>決済 (Stripe) が失敗する状態</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>1. 手順書を読む 2. 書かれたとおりに実行する 3. 運営画面を開く</t>
+          <t>1. 解約手続きの画面を開く 2. 応答本文を見る</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>手順書に沿って運営になれる。「登録もサインインもできるが運営画面には永久に入れない」状態にならない</t>
+          <t>「決済サービスとのやり取りに失敗しました」とだけ出る。事業者の応答本文や HTTP の状態コードが本文に載らない</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -18449,7 +19637,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>ST01-221</t>
+          <t>ST01-220</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -18464,22 +19652,22 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>昇格しても外部サインインの情報を壊さない</t>
+          <t>新しい環境で最初の運営を作る手順が存在し、そのとおりにやれば運営画面に入れる</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>外部サインイン済みの利用者</t>
+          <t>誰も運営でない DB</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>1. 昇格させる 2. `raw_app_meta_data` を見る</t>
+          <t>1. 手順書を読む 2. 書かれたとおりに実行する 3. 運営画面を開く</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>`role` が足されるだけで `provider` 等の既存の値が残る（jsonb を丸ごと置き換えていない）</t>
+          <t>手順書に沿って運営になれる。「登録もサインインもできるが運営画面には永久に入れない」状態にならない</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -18492,7 +19680,7 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>ST01-222</t>
+          <t>ST01-221</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -18507,22 +19695,22 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>昇格後に入り直す必要があることが手順に書いてある</t>
+          <t>昇格しても外部サインインの情報を壊さない</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>昇格直後</t>
+          <t>外部サインイン済みの利用者</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>1. 入り直さずに運営画面を開く 2. 手順書を読む</t>
+          <t>1. 昇格させる 2. `raw_app_meta_data` を見る</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>入り直す前は のまま。手順書にその理由（トークンはサインイン時の role を焼き込む）と対処が書かれている</t>
+          <t>`role` が足されるだけで `provider` 等の既存の値が残る（jsonb を丸ごと置き換えていない）</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -18535,7 +19723,7 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>ST01-223</t>
+          <t>ST01-222</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -18545,27 +19733,27 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>エラー</t>
+          <t>初期構築</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>居ない相手を昇格させようとしたら理由が出て止まる</t>
+          <t>昇格後に入り直す必要があることが手順に書いてある</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>未登録のメールアドレス</t>
+          <t>昇格直後</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>1. その相手を昇格させようとする</t>
+          <t>1. 入り直さずに運営画面を開く 2. 手順書を読む</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>「アカウントがありません」と出て終了する。黙って 0 件更新して成功に見せない</t>
+          <t>入り直す前は のまま。手順書にその理由（トークンはサインイン時の role を焼き込む）と対処が書かれている</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -18578,7 +19766,7 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>ST01-224</t>
+          <t>ST01-223</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -18588,27 +19776,27 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>表示</t>
+          <t>エラー</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>運営専用 API を非 admin が叩いたときの文言が日本語</t>
+          <t>居ない相手を昇格させようとしたら理由が出て止まる</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>一般利用者でサインイン</t>
+          <t>未登録のメールアドレス</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>1. 運営画面を開く 2. 応答本文を見る</t>
+          <t>1. その相手を昇格させようとする</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>`admin privilege required` 等の英語ではなく日本語で返る（例:「この操作は運営のみが行えます。」）</t>
+          <t>「アカウントがありません」と出て終了する。黙って 0 件更新して成功に見せない</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -18621,7 +19809,7 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>ST01-225</t>
+          <t>ST01-224</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
@@ -18631,27 +19819,27 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>整合性</t>
+          <t>表示</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>利用者に届く文言に英語・内部名が残っていない</t>
+          <t>運営専用 API を非 admin が叩いたときの文言が日本語</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>一般利用者でサインイン</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>1. route 全体を機械で走査する</t>
+          <t>1. 運営画面を開く 2. 応答本文を見る</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>`HTTPException` の文言がすべて日本語で、snake_case の内部名（byok_key / cron_schedule 等）や社内の管理番号を含まない。**新しく英語で書いたらテストが落ちる**</t>
+          <t>`admin privilege required` 等の英語ではなく日本語で返る（例:「この操作は運営のみが行えます。」）</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
@@ -18664,7 +19852,7 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>ST01-228</t>
+          <t>ST01-225</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -18674,27 +19862,27 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>秘密の保持</t>
+          <t>整合性</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>画面側の門を防御と取り違えない</t>
+          <t>利用者に届く文言に英語・内部名が残っていない</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>署名が正しくない JWT</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>1. 偽のトークンで `/admin` を開く 2. 運営専用 API を直接叩く</t>
+          <t>1. route 全体を機械で走査する</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>画面は通り抜けられても **API が を返す**。画面側の門は表示の整理であって防御ではないことが、実装のコメントにも明記されている</t>
+          <t>`HTTPException` の文言がすべて日本語で、snake_case の内部名（byok_key / cron_schedule 等）や社内の管理番号を含まない。**新しく英語で書いたらテストが落ちる**</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
@@ -18707,7 +19895,7 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>ST01-229</t>
+          <t>ST01-228</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
@@ -18717,27 +19905,27 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>初期構築</t>
+          <t>秘密の保持</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>新しい環境の DB を最後まで作れる</t>
+          <t>画面側の門を防御と取り違えない</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>空の PostgreSQL</t>
+          <t>署名が正しくない JWT</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>1. bootstrap → migration → seed を順に流す</t>
+          <t>1. 偽のトークンで `/admin` を開く 2. 運営専用 API を直接叩く</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>すべて成功で終わる。1 本も「適用できず」が残らず、seed も 0 エラー。途中で止まると **その先のゲートが本体を一度も実行できない**</t>
+          <t>画面は通り抜けられても **API が を返す**。画面側の門は表示の整理であって防御ではないことが、実装のコメントにも明記されている</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
@@ -18750,7 +19938,7 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>ST01-230</t>
+          <t>ST01-229</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -18765,22 +19953,22 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>適用できない migration を黙って飛ばさない</t>
+          <t>新しい環境の DB を最後まで作れる</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>依存が壊れた migration がある状態</t>
+          <t>空の PostgreSQL</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>1. migration を流す</t>
+          <t>1. bootstrap → migration → seed を順に流す</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>「skip した」で成功扱いにせず、残ったファイル名とエラーを出して失敗する（表の欠けた DB で緑にならない）</t>
+          <t>すべて成功で終わる。1 本も「適用できず」が残らず、seed も 0 エラー。途中で止まると **その先のゲートが本体を一度も実行できない**</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
@@ -18793,7 +19981,7 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>ST01-231</t>
+          <t>ST01-230</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -18803,27 +19991,27 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>整合性</t>
+          <t>初期構築</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>同じ表を seed と migration の両方が書いていない</t>
+          <t>適用できない migration を黙って飛ばさない</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>依存が壊れた migration がある状態</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>1. seed を走査する</t>
+          <t>1. migration を流す</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>migration が持ち主の表（法務文書など）を seed が書いていない。両方に書くと適用順で結果が変わる</t>
+          <t>「skip した」で成功扱いにせず、残ったファイル名とエラーを出して失敗する（表の欠けた DB で緑にならない）</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
@@ -18836,7 +20024,7 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>ST01-232</t>
+          <t>ST01-231</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -18846,27 +20034,27 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>秘密の保持</t>
+          <t>整合性</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>運営専用の表を、一般利用者が消せない</t>
+          <t>同じ表を seed と migration の両方が書いていない</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>一般利用者のロール</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>1. 運営のエラーログ等に対し `truncate` を試す</t>
+          <t>1. seed を走査する</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>権限エラーで拒否される。**TRUNCATE は 他人のデータが見えない権限 の対象外**なので、他人のデータが見えない権限 だけでなく権限側でも閉じていること</t>
+          <t>migration が持ち主の表（法務文書など）を seed が書いていない。両方に書くと適用順で結果が変わる</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
@@ -18879,7 +20067,7 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>ST01-233</t>
+          <t>ST01-232</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
@@ -18889,27 +20077,27 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>整合性</t>
+          <t>秘密の保持</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>ローカルと本番でアプリ用ロールの権限が同じ</t>
+          <t>運営専用の表を、一般利用者が消せない</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>一般利用者のロール</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>1. ローカル構築と CI の grant を突き合わせる</t>
+          <t>1. 運営のエラーログ等に対し `truncate` を試す</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>ローカルだけ広い権限（TRUNCATE 等）になっていない。**ローカルで通ったことが本番で通る保証**になる</t>
+          <t>権限エラーで拒否される。**TRUNCATE は 他人のデータが見えない権限 の対象外**なので、他人のデータが見えない権限 だけでなく権限側でも閉じていること</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
@@ -18922,45 +20110,88 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
+          <t>ST01-233</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>運営ダッシュボード画面</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>整合性</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>ローカルと本番でアプリ用ロールの権限が同じ</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>1. ローカル構築と CI の grant を突き合わせる</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>ローカルだけ広い権限（TRUNCATE 等）になっていない。**ローカルで通ったことが本番で通る保証**になる</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
           <t>ST01-234</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>運営ダッシュボード画面</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>整合性</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>門が「正しい設計」を違反と呼ばない</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>policy を意図的に置かない表がある状態</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>1. 他人のデータが見えない権限 監査を走らせる</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>理由つきで宣言された default deny は PASS。宣言が無い 0 本は FAIL。**赤が普通になった門は本物の穴を見逃す**</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I21" s="4" t="inlineStr"/>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -20236,7 +21467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -20945,7 +22176,7 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>SA01-040</t>
+          <t>SA01-036</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -20955,27 +22186,27 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>貫通</t>
+          <t>表示</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>退会済みアカウントの復元 (30 日以内)</t>
+          <t>券が使えないときの文言が日本語</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>退会手続き済のアカウントがある</t>
+          <t>期限切れ / 壊れた券 / 券なし / クライアント用の券</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>1. サインイン画面の「退会済みアカウントの復元」を開く 2. メールとパスワードで復元 3. サインインする</t>
+          <t>1. それぞれの状態で保護された画面を開く 2. 応答本文と画面の文言を見る</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>復元が成功して案内が出る。復元後は通常どおりサインインでき、削除の予約が解除されている</t>
+          <t>すべて日本語で「もう一度サインインしてください」と次の行動が分かる。`token expired` `malformed token` `missing bearer token` 等の英語が出ない</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
@@ -20988,7 +22219,7 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>SA01-020</t>
+          <t>SA01-037</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -20998,27 +22229,27 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>整合性</t>
+          <t>秘密の保持</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>**同意記録の版が、その時点の現行版と一致する**</t>
+          <t>断り方の違いを外から数えられない</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>現行の法務文書あり</t>
+          <t>期限切れ / 署名違い / sub 欠落</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>1. 新規登録する 2. consents を照会</t>
+          <t>1. それぞれで応答本文を比べる</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>記録された版が `legal_documents.is_current` の版と一致する（登録日など別の値になっていない）</t>
+          <t>3 つとも**同じ文言**。どの理由で断られたかが応答から読み取れない（理由はサーバーログにだけ残る）</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
@@ -21031,7 +22262,7 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>SA01-021</t>
+          <t>SA01-038</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -21041,27 +22272,27 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>エラー</t>
+          <t>整合性</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>版が取れないときは登録を止める</t>
+          <t>利用者に届く文言が「route の外」にも無いか</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>版の取得を失敗させる</t>
+          <t>券の検証 (dependencies) / 混雑の制限 (rate_limit) — route より手前で応答を返す層</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>1. 新規登録を試みる</t>
+          <t>1. HTTPException に渡す文言を src 全体で走査する</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>「何に同意したのか分からない記録」を作らず、理由を出して登録しない</t>
+          <t>route の中だけでなく **src 全体**が日本語。手前の層に英語が残っていない</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
@@ -21074,7 +22305,7 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>SA01-022</t>
+          <t>SA01-039</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
@@ -21084,27 +22315,27 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>表示</t>
+          <t>整合性</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>登録直後に再同意を求めない</t>
+          <t>文言を定数・f 文字列・関数の陰に隠しても検査から逃げられない</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>新規登録直後</t>
+          <t>文言を別ファイルの定数にした場合 / f 文字列にした場合</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>1. 着地した画面を見る</t>
+          <t>1. 検査を走らせる</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>「規約を更新しました。同意をお願いします」の帯が出ない（いま同意したばかりのため）</t>
+          <t>どちらも中身まで解決して検査される。解決できない書き方は理由つきの一覧に載せない限り落ちる</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
@@ -21117,7 +22348,7 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>SA01-023</t>
+          <t>SA01-040</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
@@ -21127,27 +22358,27 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>バリデーション</t>
+          <t>貫通</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>入力エラーが日本語で出る</t>
+          <t>退会済みアカウントの復元 (30 日以内)</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>パスワード確認が空</t>
+          <t>退会手続き済のアカウントがある</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>1. 送信する</t>
+          <t>1. サインイン画面の「退会済みアカウントの復元」を開く 2. メールとパスワードで復元 3. サインインする</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>英語の既定メッセージ（String must contain…）ではなく日本語で出る</t>
+          <t>復元が成功して案内が出る。復元後は通常どおりサインインでき、削除の予約が解除されている</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
@@ -21160,7 +22391,7 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>SA01-024</t>
+          <t>SA01-020</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
@@ -21170,27 +22401,27 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>秘密の保持</t>
+          <t>整合性</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>同意文に社内の管理番号を出さない</t>
+          <t>**同意記録の版が、その時点の現行版と一致する**</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>現行の法務文書あり</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>1. 同意文と配布物を検査</t>
+          <t>1. 新規登録する 2. consents を照会</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>GAP-xxx 等の社内番号が 1 つも出ていない</t>
+          <t>記録された版が `legal_documents.is_current` の版と一致する（登録日など別の値になっていない）</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
@@ -21203,7 +22434,7 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>SA01-025</t>
+          <t>SA01-021</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
@@ -21213,27 +22444,27 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>バリデーション</t>
+          <t>エラー</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>同意しなければ登録できない</t>
+          <t>版が取れないときは登録を止める</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>同意チェック無し</t>
+          <t>版の取得を失敗させる</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>1. 送信する</t>
+          <t>1. 新規登録を試みる</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>画面とサーバーの両方で拒否される（画面だけの防御にしない）</t>
+          <t>「何に同意したのか分からない記録」を作らず、理由を出して登録しない</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
@@ -21246,7 +22477,7 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>SA01-026</t>
+          <t>SA01-022</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
@@ -21256,27 +22487,27 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>整合性</t>
+          <t>表示</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>公開パス一覧のパスが、実在するルートと一致する</t>
+          <t>登録直後に再同意を求めない</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>新規登録直後</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>1. `middleware.ts` / `ConditionalAppShell.tsx` の公開パス一覧を取り出す 2. 各パスを未サインインで開く</t>
+          <t>1. 着地した画面を見る</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>一覧のどのパスも 404 にならない（実ルートの無いパスが一覧に残っていない）。逆に、一覧に無い公開画面がガードで弾かれない</t>
+          <t>「規約を更新しました。同意をお願いします」の帯が出ない（いま同意したばかりのため）</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
@@ -21289,7 +22520,7 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>SA01-027</t>
+          <t>SA01-023</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
@@ -21299,27 +22530,27 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>秘密の保持</t>
+          <t>バリデーション</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>サーバー側の想定外エラーで、内部の言葉を利用者に出さない</t>
+          <t>入力エラーが日本語で出る</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>API がサーバー側エラーを返す状態</t>
+          <t>パスワード確認が空</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>1. サインインを送信する 2. 画面の赤帯と応答本文を見る</t>
+          <t>1. 送信する</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>例外クラス名・内部パス・英語の "internal server error" が 1 つも出ない。日本語で「時間をおいて試す」旨が出て、記録できたときは参照 ID が添えられる</t>
+          <t>英語の既定メッセージ（String must contain…）ではなく日本語で出る</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
@@ -21332,7 +22563,7 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>SA01-028</t>
+          <t>SA01-024</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
@@ -21342,27 +22573,27 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>表示</t>
+          <t>秘密の保持</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>失敗したときの文言が日本語で、内部の識別子を含まない</t>
+          <t>同意文に社内の管理番号を出さない</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>存在しないアカウント / パスワード違い / 試行上限 / 退会済み</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>1. 各条件でサインインを送信する 2. 赤帯の文言と応答本文を見る</t>
+          <t>1. 同意文と配布物を検査</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>すべて日本語。`invalid email or password` 等の英語も、`terms_of_service` 等の内部名も出ない。存在するアカウントかどうかで文言が変わらない</t>
+          <t>GAP-xxx 等の社内番号が 1 つも出ていない</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
@@ -21375,7 +22606,7 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>SA01-029</t>
+          <t>SA01-025</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
@@ -21390,22 +22621,22 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>足りない同意が「どれか」分かる</t>
+          <t>同意しなければ登録できない</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>利用規約に同意せず送信</t>
+          <t>同意チェック無し</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>1. 同意欄の一方だけ外して送信する</t>
+          <t>1. 送信する</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>「利用規約への同意が必要です。」のように日本語の文書名で示される（内部名を出さず、「同意が必要です」だけで終わらない）</t>
+          <t>画面とサーバーの両方で拒否される（画面だけの防御にしない）</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
@@ -21418,7 +22649,7 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>SA01-030</t>
+          <t>SA01-026</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
@@ -21428,27 +22659,27 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>秘密の保持</t>
+          <t>整合性</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>送信した内容がエラー応答に返ってこない</t>
+          <t>公開パス一覧のパスが、実在するルートと一致する</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>必須項目を 1 つ落として送信</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>1. 開発者ツールで応答本文を見る</t>
+          <t>1. `middleware.ts` / `ConditionalAppShell.tsx` の公開パス一覧を取り出す 2. 各パスを未サインインで開く</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>入力したパスワードもメールアドレスも本文に含まれない（FastAPI 既定は本文をエコーバックする）</t>
+          <t>一覧のどのパスも 404 にならない（実ルートの無いパスが一覧に残っていない）。逆に、一覧に無い公開画面がガードで弾かれない</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
@@ -21461,7 +22692,7 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>SA01-031</t>
+          <t>SA01-027</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
@@ -21471,195 +22702,367 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
+          <t>秘密の保持</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>サーバー側の想定外エラーで、内部の言葉を利用者に出さない</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>API がサーバー側エラーを返す状態</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>1. サインインを送信する 2. 画面の赤帯と応答本文を見る</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>例外クラス名・内部パス・英語の "internal server error" が 1 つも出ない。日本語で「時間をおいて試す」旨が出て、記録できたときは参照 ID が添えられる</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>SA01-028</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>サインイン/サインアップ画面</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
           <t>表示</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>形式エラーの文言が日本語で、内部名を出さない</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>必須項目を落として送信 / 項目数が足りない状態で送信</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>1. 応答本文を見る</t>
-        </is>
-      </c>
-      <c r="G29" s="4" t="inlineStr">
-        <is>
-          <t>`Field required` / `List should have at least 2 items` 等の英語も `display_name` 等の内部名も出ず、日本語の項目名で示される</t>
-        </is>
-      </c>
-      <c r="H29" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I29" s="4" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>SA01-032</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>失敗したときの文言が日本語で、内部の識別子を含まない</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>存在しないアカウント / パスワード違い / 試行上限 / 退会済み</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>1. 各条件でサインインを送信する 2. 赤帯の文言と応答本文を見る</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>すべて日本語。`invalid email or password` 等の英語も、`terms_of_service` 等の内部名も出ない。存在するアカウントかどうかで文言が変わらない</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>SA01-029</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>サインイン/サインアップ画面</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>復旧</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>パスワードを忘れても自力で復旧できる</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>パスワードを忘れた利用者</t>
-        </is>
-      </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t>1. 再設定を要求 2. 届いたリンクを開く 3. 新しいパスワードを設定 4. サインイン</t>
-        </is>
-      </c>
-      <c r="G30" s="3" t="inlineStr">
-        <is>
-          <t>**再設定用のリンクが実際にメールで届く**。新しいパスワードで入れて、古いパスワードでは入れない</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr"/>
-      <c r="I30" s="3" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>SA01-033</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>バリデーション</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>足りない同意が「どれか」分かる</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>利用規約に同意せず送信</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>1. 同意欄の一方だけ外して送信する</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>「利用規約への同意が必要です。」のように日本語の文書名で示される（内部名を出さず、「同意が必要です」だけで終わらない）</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>SA01-030</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>サインイン/サインアップ画面</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>秘密の保持</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>再設定リンクは 1 回しか使えない</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>1 度使った再設定リンク</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>1. 同じリンクでもう一度設定を試す</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t>拒否される（使い回せない）</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr"/>
-      <c r="I31" s="3" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>SA01-034</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>サインイン/サインアップ画面</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>秘密の保持</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>再設定すると古いセッションが死ぬ</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>再設定前に発行された更新用トークン</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>1. 再設定後にそのトークンで再取得を試す</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t>通らない。パスワードを変えたのに古いセッションが生き続けない</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr"/>
-      <c r="I32" s="3" t="inlineStr"/>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>送信した内容がエラー応答に返ってこない</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>必須項目を 1 つ落として送信</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>1. 開発者ツールで応答本文を見る</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>入力したパスワードもメールアドレスも本文に含まれない（FastAPI 既定は本文をエコーバックする）</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
+          <t>SA01-031</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>サインイン/サインアップ画面</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>表示</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>形式エラーの文言が日本語で、内部名を出さない</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>必須項目を落として送信 / 項目数が足りない状態で送信</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>1. 応答本文を見る</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>`Field required` / `List should have at least 2 items` 等の英語も `display_name` 等の内部名も出ず、日本語の項目名で示される</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>SA01-032</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>サインイン/サインアップ画面</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>復旧</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>パスワードを忘れても自力で復旧できる</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>パスワードを忘れた利用者</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>1. 再設定を要求 2. 届いたリンクを開く 3. 新しいパスワードを設定 4. サインイン</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>**再設定用のリンクが実際にメールで届く**。新しいパスワードで入れて、古いパスワードでは入れない</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr"/>
+      <c r="I34" s="3" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>SA01-033</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>サインイン/サインアップ画面</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>秘密の保持</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>再設定リンクは 1 回しか使えない</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>1 度使った再設定リンク</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>1. 同じリンクでもう一度設定を試す</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>拒否される（使い回せない）</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr"/>
+      <c r="I35" s="3" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>SA01-034</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>サインイン/サインアップ画面</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>秘密の保持</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>再設定すると古いセッションが死ぬ</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>再設定前に発行された更新用トークン</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>1. 再設定後にそのトークンで再取得を試す</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>通らない。パスワードを変えたのに古いセッションが生き続けない</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr"/>
+      <c r="I36" s="3" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
           <t>SA01-035</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>サインイン/サインアップ画面</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
         <is>
           <t>整合性</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="D37" s="4" t="inlineStr">
         <is>
           <t>認証まわりのメールが送信経路に繋がっている</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
+      <c r="E37" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F33" s="4" t="inlineStr">
+      <c r="F37" s="4" t="inlineStr">
         <is>
           <t>1. 送信関数を検査する</t>
         </is>
       </c>
-      <c r="G33" s="4" t="inlineStr">
+      <c r="G37" s="4" t="inlineStr">
         <is>
           <t>実際の送信経路（Resend）を呼んでいる。`_ = email; return` のようなスタブになっていない</t>
         </is>
       </c>
-      <c r="H33" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I33" s="4" t="inlineStr"/>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -27011,43 +28414,47 @@
       <c r="I10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>TEMPLATES-010</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>出力デザインテンプレート画面</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>表示</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>実行中が分かる</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>1. 作成を実行</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>実行中であることと経過時間が出る（無反応に見せない・GAP-136）</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr"/>
-      <c r="I11" s="3" t="inlineStr"/>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -27394,43 +28801,47 @@
       <c r="I19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>TEMPLATES-020</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>出力デザインテンプレート画面</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>更新</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>部分改訂で全面書き換えにならない</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>版あり</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>1. 一部だけ変える指示を出す</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>指示した箇所以外の作り込みが保たれる（GAP-147 の全面書き換えバグの回帰）</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr"/>
-      <c r="I20" s="3" t="inlineStr"/>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -28117,7 +29528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -28869,7 +30280,7 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>SA03-020</t>
+          <t>SA03-027</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -28879,27 +30290,27 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>表示</t>
+          <t>正常系</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>契約者にやめる口が出る</t>
+          <t>メンバー招待が最後まで通る</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>Pro 契約中</t>
+          <t>登録済みの別アカウント</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>1. プランを開く</t>
+          <t>1. メンバータブ → メンバー招待 2. 登録済みメールを入れて招待する</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>「プランの管理・解約」が出ている</t>
+          <t>一覧に相手が出て、DB にも membership が 1 行できる。**「サーバーでエラー」にならない** (他人のデータが見えない権限 の自己参照再帰で全滅していた実績あり)</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
@@ -28912,7 +30323,7 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>SA03-021</t>
+          <t>SA03-029</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -28922,27 +30333,27 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>表示</t>
+          <t>整合性</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>無料プランに死にボタンを置かない</t>
+          <t>ポリシーが自分の表を参照していない</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>無料プラン</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>1. プランを開く</t>
+          <t>1. pg_policies を検査する</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>解約の導線が出ていない（押しても何も起きない口を作らない）</t>
+          <t>自分の表への副問い合わせを含むポリシーが 0 件 (あれば Postgres が必ず再帰で落とす)。owner 判定は SECURITY DEFINER 関数に出ている</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
@@ -28955,7 +30366,7 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>SA03-022</t>
+          <t>SA03-020</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
@@ -28970,7 +30381,7 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>解約の条件が押す前に読める</t>
+          <t>契約者にやめる口が出る</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
@@ -28985,7 +30396,7 @@
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>期間末まで使えること・日割り返金が無いことが、押す前に書いてある</t>
+          <t>「プランの管理・解約」が出ている</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
@@ -28998,7 +30409,7 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>SA03-023</t>
+          <t>SA03-021</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
@@ -29008,27 +30419,27 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>インタラクション</t>
+          <t>表示</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>押した結果が必ず返る</t>
+          <t>無料プランに死にボタンを置かない</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>Pro 契約中</t>
+          <t>無料プラン</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>1. 解約を押す</t>
+          <t>1. プランを開く</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>手続き画面へ進むか、進めない理由が画面に出る（黙って何も起きない、を作らない）</t>
+          <t>解約の導線が出ていない（押しても何も起きない口を作らない）</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
@@ -29041,7 +30452,7 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>SA03-024</t>
+          <t>SA03-022</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
@@ -29051,27 +30462,27 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>エラー</t>
+          <t>表示</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>契約が無いのに叩かれたとき</t>
+          <t>解約の条件が押す前に読める</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>契約なし</t>
+          <t>Pro 契約中</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>1. 解約の口を叩く</t>
+          <t>1. プランを開く</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>正直に断る（誤って手続き画面へ進めない）</t>
+          <t>期間末まで使えること・日割り返金が無いことが、押す前に書いてある</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
@@ -29084,7 +30495,7 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>SA03-025</t>
+          <t>SA03-023</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
@@ -29094,17 +30505,17 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>エラー</t>
+          <t>インタラクション</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>決済連携が未設定のとき</t>
+          <t>押した結果が必ず返る</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>未設定</t>
+          <t>Pro 契約中</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -29114,7 +30525,7 @@
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>「未接続」ではなく「未設定」であることが理由として区別して出る（GAP-206）</t>
+          <t>手続き画面へ進むか、進めない理由が画面に出る（黙って何も起きない、を作らない）</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
@@ -29127,45 +30538,131 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
+          <t>SA03-024</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>ワークスペース設定画面</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>契約が無いのに叩かれたとき</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>契約なし</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>1. 解約の口を叩く</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>正直に断る（誤って手続き画面へ進めない）</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>SA03-025</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>ワークスペース設定画面</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>決済連携が未設定のとき</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>未設定</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>1. 解約を押す</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>「未接続」ではなく「未設定」であることが理由として区別して出る（GAP-206）</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
           <t>SA03-026</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>ワークスペース設定画面</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>整合性</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D26" s="4" t="inlineStr">
         <is>
           <t>表示価格が実装と一致</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="E26" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F24" s="4" t="inlineStr">
+      <c r="F26" s="4" t="inlineStr">
         <is>
           <t>1. 画面と規約と実装定数を突き合わせる</t>
         </is>
       </c>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="G26" s="4" t="inlineStr">
         <is>
           <t>月額の金額が 3 か所で一致する（片方だけ古い、を作らない）</t>
         </is>
       </c>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="I24" s="4" t="inlineStr"/>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
